--- a/Financial Analysis/MA.xlsx
+++ b/Financial Analysis/MA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Desktop\Financial Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{134DACCA-ED80-4B88-8368-FEE38481CAE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FC489AC-CE50-4BE7-8EAB-308612A3A929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{5EE3D269-52EC-4F93-A9AE-4AAFACF544BD}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{5EE3D269-52EC-4F93-A9AE-4AAFACF544BD}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -733,17 +733,17 @@
         <v>0</v>
       </c>
       <c r="D3" s="10">
-        <v>559.39</v>
+        <v>568.04</v>
       </c>
       <c r="E3" s="3">
-        <v>45751</v>
+        <v>45804</v>
       </c>
       <c r="F3" s="3">
         <f ca="1">TODAY()</f>
-        <v>45781</v>
+        <v>45804</v>
       </c>
       <c r="G3" s="3">
-        <v>45771</v>
+        <v>45862</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -764,7 +764,7 @@
       </c>
       <c r="D5" s="1">
         <f>D3*D4</f>
-        <v>507982.05899999995</v>
+        <v>515837.12399999989</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -806,7 +806,7 @@
       </c>
       <c r="D9" s="1">
         <f>D5-D8</f>
-        <v>518890.05899999995</v>
+        <v>526745.12399999984</v>
       </c>
     </row>
   </sheetData>
@@ -3305,51 +3305,51 @@
         <v>929.6</v>
       </c>
       <c r="Y18" s="1">
-        <f t="shared" ref="Y18:AJ18" si="37">904.9+6.8</f>
+        <f t="shared" ref="Y18" si="37">904.9+6.8</f>
         <v>911.69999999999993</v>
       </c>
       <c r="Z18" s="1">
-        <f>901.3+6.8</f>
+        <f t="shared" ref="Z18:AJ18" si="38">901.3+6.8</f>
         <v>908.09999999999991</v>
       </c>
       <c r="AA18" s="1">
-        <f>901.3+6.8</f>
+        <f t="shared" si="38"/>
         <v>908.09999999999991</v>
       </c>
       <c r="AB18" s="1">
-        <f>901.3+6.8</f>
+        <f t="shared" si="38"/>
         <v>908.09999999999991</v>
       </c>
       <c r="AC18" s="1">
-        <f>901.3+6.8</f>
+        <f t="shared" si="38"/>
         <v>908.09999999999991</v>
       </c>
       <c r="AD18" s="1">
-        <f>901.3+6.8</f>
+        <f t="shared" si="38"/>
         <v>908.09999999999991</v>
       </c>
       <c r="AE18" s="1">
-        <f>901.3+6.8</f>
+        <f t="shared" si="38"/>
         <v>908.09999999999991</v>
       </c>
       <c r="AF18" s="1">
-        <f>901.3+6.8</f>
+        <f t="shared" si="38"/>
         <v>908.09999999999991</v>
       </c>
       <c r="AG18" s="1">
-        <f>901.3+6.8</f>
+        <f t="shared" si="38"/>
         <v>908.09999999999991</v>
       </c>
       <c r="AH18" s="1">
-        <f>901.3+6.8</f>
+        <f t="shared" si="38"/>
         <v>908.09999999999991</v>
       </c>
       <c r="AI18" s="1">
-        <f>901.3+6.8</f>
+        <f t="shared" si="38"/>
         <v>908.09999999999991</v>
       </c>
       <c r="AJ18" s="1">
-        <f>901.3+6.8</f>
+        <f t="shared" si="38"/>
         <v>908.09999999999991</v>
       </c>
     </row>
@@ -3358,135 +3358,135 @@
         <v>23</v>
       </c>
       <c r="C19" s="5">
-        <f t="shared" ref="C19:L19" si="38">C17/C18</f>
+        <f t="shared" ref="C19:L19" si="39">C17/C18</f>
         <v>2.830249569707401</v>
       </c>
       <c r="D19" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>2.447289156626506</v>
       </c>
       <c r="E19" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>2.6882530120481927</v>
       </c>
       <c r="F19" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>2.7162220309810672</v>
       </c>
       <c r="G19" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>2.5398020654044751</v>
       </c>
       <c r="H19" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>3.060456110154905</v>
       </c>
       <c r="I19" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>3.4401893287435454</v>
       </c>
       <c r="J19" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>3.0023666092943202</v>
       </c>
       <c r="K19" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>3.2390275387263339</v>
       </c>
       <c r="L19" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>3.5047332185886404</v>
       </c>
       <c r="M19" s="5">
-        <f t="shared" ref="M19:N19" si="39">M17/M18</f>
+        <f t="shared" ref="M19:N19" si="40">M17/M18</f>
         <v>3.554853469876893</v>
       </c>
       <c r="N19" s="5">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>3.6656794998354725</v>
       </c>
       <c r="O19" s="5">
-        <f t="shared" ref="O19:R19" si="40">O17/O18</f>
+        <f t="shared" ref="O19:R19" si="41">O17/O18</f>
         <v>3.6119370113423637</v>
       </c>
       <c r="P19" s="5">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>3.9812580993282691</v>
       </c>
       <c r="Q19" s="5">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>4.117218412069156</v>
       </c>
       <c r="R19" s="5">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>3.9625715780200443</v>
       </c>
       <c r="T19" s="5">
-        <f t="shared" ref="T19:Z19" si="41">T17/T18</f>
+        <f t="shared" ref="T19:Z19" si="42">T17/T18</f>
         <v>8.7327882960413081</v>
       </c>
       <c r="U19" s="5">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>6.8965146299483644</v>
       </c>
       <c r="V19" s="5">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>9.3448795180722897</v>
       </c>
       <c r="W19" s="5">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>10.682013769363166</v>
       </c>
       <c r="X19" s="5">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>12.042814113597245</v>
       </c>
       <c r="Y19" s="5">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>14.120873094219592</v>
       </c>
       <c r="Z19" s="5">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>15.672985100759828</v>
       </c>
       <c r="AA19" s="5">
-        <f t="shared" ref="AA19:AJ19" si="42">AA17/AA18</f>
+        <f t="shared" ref="AA19:AJ19" si="43">AA17/AA18</f>
         <v>18.556163607532209</v>
       </c>
       <c r="AB19" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>20.067095045391479</v>
       </c>
       <c r="AC19" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>21.290264868376614</v>
       </c>
       <c r="AD19" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>22.370323734324206</v>
       </c>
       <c r="AE19" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>23.277012571349044</v>
       </c>
       <c r="AF19" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>23.983458574340798</v>
       </c>
       <c r="AG19" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>24.711238469741122</v>
       </c>
       <c r="AH19" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>25.460995084568637</v>
       </c>
       <c r="AI19" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>26.233390586857464</v>
       </c>
       <c r="AJ19" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>27.029107067011779</v>
       </c>
     </row>
@@ -3503,47 +3503,47 @@
         <v>0.11244435842848843</v>
       </c>
       <c r="H21" s="8">
-        <f t="shared" ref="H21:N21" si="43">H3/D3-1</f>
+        <f t="shared" ref="H21:N21" si="44">H3/D3-1</f>
         <v>0.14044024013098055</v>
       </c>
       <c r="I21" s="8">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0.13498957609451012</v>
       </c>
       <c r="J21" s="8">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0.12566615093690903</v>
       </c>
       <c r="K21" s="8">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0.10438413361169108</v>
       </c>
       <c r="L21" s="8">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0.11038443132876052</v>
       </c>
       <c r="M21" s="8">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0.1279657125363538</v>
       </c>
       <c r="N21" s="8">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0.14370800244349424</v>
       </c>
       <c r="O21" s="8">
-        <f t="shared" ref="O21" si="44">O3/K3-1</f>
+        <f t="shared" ref="O21" si="45">O3/K3-1</f>
         <v>0.14209199747952117</v>
       </c>
       <c r="P21" s="8">
-        <f t="shared" ref="P21" si="45">P3/L3-1</f>
+        <f t="shared" ref="P21" si="46">P3/L3-1</f>
         <v>0.12000000000000011</v>
       </c>
       <c r="Q21" s="8">
-        <f t="shared" ref="Q21" si="46">Q3/M3-1</f>
+        <f t="shared" ref="Q21" si="47">Q3/M3-1</f>
         <v>0.12000000000000011</v>
       </c>
       <c r="R21" s="8">
-        <f t="shared" ref="R21" si="47">R3/N3-1</f>
+        <f t="shared" ref="R21" si="48">R3/N3-1</f>
         <v>0.10000000000000009</v>
       </c>
       <c r="T21" s="8"/>
@@ -3552,63 +3552,63 @@
         <v>-9.3703725641177571E-2</v>
       </c>
       <c r="V21" s="8">
-        <f t="shared" ref="V21:AJ21" si="48">V3/U3-1</f>
+        <f t="shared" ref="V21:AJ21" si="49">V3/U3-1</f>
         <v>0.23416770145742105</v>
       </c>
       <c r="W21" s="8">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0.17755772082185972</v>
       </c>
       <c r="X21" s="8">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0.1286594414714215</v>
       </c>
       <c r="Y21" s="8">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0.12228065981353087</v>
       </c>
       <c r="Z21" s="8">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0.11966130578336354</v>
       </c>
       <c r="AA21" s="8">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AB21" s="8">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>8.0000000000000071E-2</v>
       </c>
       <c r="AC21" s="8">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>6.0000000000000053E-2</v>
       </c>
       <c r="AD21" s="8">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AE21" s="8">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AF21" s="8">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AG21" s="8">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AH21" s="8">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AI21" s="8">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AJ21" s="8">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>3.0000000000000027E-2</v>
       </c>
     </row>
@@ -3617,19 +3617,19 @@
         <v>39</v>
       </c>
       <c r="C22" s="8">
-        <f t="shared" ref="C22:F22" si="49">C5/C3</f>
+        <f t="shared" ref="C22:F22" si="50">C5/C3</f>
         <v>0.64311979872266301</v>
       </c>
       <c r="D22" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0.64580680371111521</v>
       </c>
       <c r="E22" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0.64054899235580265</v>
       </c>
       <c r="F22" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0.61870379920921437</v>
       </c>
       <c r="G22" s="8">
@@ -3637,115 +3637,115 @@
         <v>0.64457202505219202</v>
       </c>
       <c r="H22" s="8">
-        <f t="shared" ref="H22:N22" si="50">H5/H3</f>
+        <f t="shared" ref="H22:N22" si="51">H5/H3</f>
         <v>0.64906683681607913</v>
       </c>
       <c r="I22" s="8">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0.65023725700290835</v>
       </c>
       <c r="J22" s="8">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0.63362858888210138</v>
       </c>
       <c r="K22" s="8">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0.63988657844990549</v>
       </c>
       <c r="L22" s="8">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0.65263611550064649</v>
       </c>
       <c r="M22" s="8">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0.62762925770118061</v>
       </c>
       <c r="N22" s="8">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0.63346241153692084</v>
       </c>
       <c r="O22" s="8">
-        <f t="shared" ref="O22:R22" si="51">O5/O3</f>
+        <f t="shared" ref="O22:R22" si="52">O5/O3</f>
         <v>0.65200000000000002</v>
       </c>
       <c r="P22" s="8">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>0.64000000000000012</v>
       </c>
       <c r="Q22" s="8">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>0.63</v>
       </c>
       <c r="R22" s="8">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>0.63</v>
       </c>
       <c r="T22" s="8">
-        <f t="shared" ref="T22:AJ22" si="52">T5/T3</f>
+        <f t="shared" ref="T22:AJ22" si="53">T5/T3</f>
         <v>0.65865071373571049</v>
       </c>
       <c r="U22" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0.61375073524606238</v>
       </c>
       <c r="V22" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0.62470874814657906</v>
       </c>
       <c r="W22" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0.63673157350362009</v>
       </c>
       <c r="X22" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0.64431428799107504</v>
       </c>
       <c r="Y22" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0.63812262576774237</v>
       </c>
       <c r="Z22" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0.63752955053507721</v>
       </c>
       <c r="AA22" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0.64</v>
       </c>
       <c r="AB22" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0.64</v>
       </c>
       <c r="AC22" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0.64</v>
       </c>
       <c r="AD22" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0.64</v>
       </c>
       <c r="AE22" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0.64</v>
       </c>
       <c r="AF22" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0.64</v>
       </c>
       <c r="AG22" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0.64</v>
       </c>
       <c r="AH22" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0.64</v>
       </c>
       <c r="AI22" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0.64</v>
       </c>
       <c r="AJ22" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0.64</v>
       </c>
     </row>
@@ -3754,19 +3754,19 @@
         <v>40</v>
       </c>
       <c r="C23" s="8">
-        <f t="shared" ref="C23:F23" si="53">C6/C3</f>
+        <f t="shared" ref="C23:F23" si="54">C6/C3</f>
         <v>3.5029998064640994E-2</v>
       </c>
       <c r="D23" s="8">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>3.8202655994178644E-2</v>
       </c>
       <c r="E23" s="8">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>3.1619179986101462E-2</v>
       </c>
       <c r="F23" s="8">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>3.7132542547705004E-2</v>
       </c>
       <c r="G23" s="8">
@@ -3774,115 +3774,115 @@
         <v>2.9053583855254E-2</v>
       </c>
       <c r="H23" s="8">
-        <f t="shared" ref="H23:N23" si="54">H6/H3</f>
+        <f t="shared" ref="H23:N23" si="55">H6/H3</f>
         <v>3.2062529909076411E-2</v>
       </c>
       <c r="I23" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>2.9542323587938159E-2</v>
       </c>
       <c r="J23" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>4.0317654245571169E-2</v>
       </c>
       <c r="K23" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>1.8273471959672338E-2</v>
       </c>
       <c r="L23" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>2.6432983766700186E-2</v>
       </c>
       <c r="M23" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>2.9854797123083185E-2</v>
       </c>
       <c r="N23" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>3.9391106956870078E-2</v>
       </c>
       <c r="O23" s="8">
-        <f t="shared" ref="O23:R23" si="55">O6/O3</f>
+        <f t="shared" ref="O23:R23" si="56">O6/O3</f>
         <v>2.0965517241379312E-2</v>
       </c>
       <c r="P23" s="8">
-        <f t="shared" si="55"/>
-        <v>0.03</v>
-      </c>
-      <c r="Q23" s="8">
-        <f t="shared" si="55"/>
-        <v>0.03</v>
-      </c>
-      <c r="R23" s="8">
-        <f t="shared" si="55"/>
-        <v>0.04</v>
-      </c>
-      <c r="T23" s="8">
-        <f t="shared" ref="T23:AJ23" si="56">T6/T3</f>
-        <v>5.5321921459456261E-2</v>
-      </c>
-      <c r="U23" s="8">
-        <f t="shared" si="56"/>
-        <v>4.2938370041173776E-2</v>
-      </c>
-      <c r="V23" s="8">
-        <f t="shared" si="56"/>
-        <v>4.7394619783944082E-2</v>
-      </c>
-      <c r="W23" s="8">
-        <f t="shared" si="56"/>
-        <v>3.5481404865764267E-2</v>
-      </c>
-      <c r="X23" s="8">
-        <f t="shared" si="56"/>
-        <v>3.2871145111164235E-2</v>
-      </c>
-      <c r="Y23" s="8">
-        <f t="shared" si="56"/>
-        <v>2.893456882167075E-2</v>
-      </c>
-      <c r="Z23" s="8">
-        <f t="shared" si="56"/>
-        <v>3.0535204122076894E-2</v>
-      </c>
-      <c r="AA23" s="8">
         <f t="shared" si="56"/>
         <v>0.03</v>
       </c>
-      <c r="AB23" s="8">
-        <f t="shared" si="56"/>
-        <v>2.9999999999999995E-2</v>
-      </c>
-      <c r="AC23" s="8">
+      <c r="Q23" s="8">
         <f t="shared" si="56"/>
         <v>0.03</v>
       </c>
+      <c r="R23" s="8">
+        <f t="shared" si="56"/>
+        <v>0.04</v>
+      </c>
+      <c r="T23" s="8">
+        <f t="shared" ref="T23:AJ23" si="57">T6/T3</f>
+        <v>5.5321921459456261E-2</v>
+      </c>
+      <c r="U23" s="8">
+        <f t="shared" si="57"/>
+        <v>4.2938370041173776E-2</v>
+      </c>
+      <c r="V23" s="8">
+        <f t="shared" si="57"/>
+        <v>4.7394619783944082E-2</v>
+      </c>
+      <c r="W23" s="8">
+        <f t="shared" si="57"/>
+        <v>3.5481404865764267E-2</v>
+      </c>
+      <c r="X23" s="8">
+        <f t="shared" si="57"/>
+        <v>3.2871145111164235E-2</v>
+      </c>
+      <c r="Y23" s="8">
+        <f t="shared" si="57"/>
+        <v>2.893456882167075E-2</v>
+      </c>
+      <c r="Z23" s="8">
+        <f t="shared" si="57"/>
+        <v>3.0535204122076894E-2</v>
+      </c>
+      <c r="AA23" s="8">
+        <f t="shared" si="57"/>
+        <v>0.03</v>
+      </c>
+      <c r="AB23" s="8">
+        <f t="shared" si="57"/>
+        <v>2.9999999999999995E-2</v>
+      </c>
+      <c r="AC23" s="8">
+        <f t="shared" si="57"/>
+        <v>0.03</v>
+      </c>
       <c r="AD23" s="8">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>3.0000000000000002E-2</v>
       </c>
       <c r="AE23" s="8">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>2.9999999999999995E-2</v>
       </c>
       <c r="AF23" s="8">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0.03</v>
       </c>
       <c r="AG23" s="8">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0.03</v>
       </c>
       <c r="AH23" s="8">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0.03</v>
       </c>
       <c r="AI23" s="8">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0.03</v>
       </c>
       <c r="AJ23" s="8">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0.03</v>
       </c>
       <c r="AL23" t="s">
@@ -3905,47 +3905,47 @@
         <v>-5.2083333333333703E-3</v>
       </c>
       <c r="H24" s="8">
-        <f t="shared" ref="H24:N24" si="57">H7/D7-1</f>
+        <f t="shared" ref="H24:N24" si="58">H7/D7-1</f>
         <v>1.5873015873015817E-2</v>
       </c>
       <c r="I24" s="8">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>0.14054054054054044</v>
       </c>
       <c r="J24" s="8">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>0.11413043478260865</v>
       </c>
       <c r="K24" s="8">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>0.13089005235602102</v>
       </c>
       <c r="L24" s="8">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>0.171875</v>
       </c>
       <c r="M24" s="8">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>6.6350710900473953E-2</v>
       </c>
       <c r="N24" s="8">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>0.12682926829268282</v>
       </c>
       <c r="O24" s="8">
-        <f t="shared" ref="O24" si="58">O7/K7-1</f>
+        <f t="shared" ref="O24" si="59">O7/K7-1</f>
         <v>0.27314814814814814</v>
       </c>
       <c r="P24" s="8">
-        <f t="shared" ref="P24" si="59">P7/L7-1</f>
+        <f t="shared" ref="P24" si="60">P7/L7-1</f>
         <v>0.10000000000000009</v>
       </c>
       <c r="Q24" s="8">
-        <f t="shared" ref="Q24" si="60">Q7/M7-1</f>
+        <f t="shared" ref="Q24" si="61">Q7/M7-1</f>
         <v>0.10000000000000009</v>
       </c>
       <c r="R24" s="8">
-        <f t="shared" ref="R24" si="61">R7/N7-1</f>
+        <f t="shared" ref="R24" si="62">R7/N7-1</f>
         <v>8.0000000000000071E-2</v>
       </c>
       <c r="T24" s="8"/>
@@ -3954,63 +3954,63 @@
         <v>0.11111111111111116</v>
       </c>
       <c r="V24" s="8">
-        <f t="shared" ref="V24:AJ24" si="62">V7/U7-1</f>
+        <f t="shared" ref="V24:AJ24" si="63">V7/U7-1</f>
         <v>0.25172413793103443</v>
       </c>
       <c r="W24" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>3.3057851239669311E-2</v>
       </c>
       <c r="X24" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>6.5333333333333243E-2</v>
       </c>
       <c r="Y24" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>0.12265331664580725</v>
       </c>
       <c r="Z24" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>0.13654403567447049</v>
       </c>
       <c r="AA24" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>-1</v>
       </c>
       <c r="AB24" s="8" t="e">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AC24" s="8" t="e">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AD24" s="8" t="e">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AE24" s="8" t="e">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AF24" s="8" t="e">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AG24" s="8" t="e">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH24" s="8" t="e">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI24" s="8" t="e">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AJ24" s="8" t="e">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL24" t="s">
@@ -4025,19 +4025,19 @@
         <v>42</v>
       </c>
       <c r="C25" s="8">
-        <f t="shared" ref="C25:F25" si="63">C8/C3</f>
+        <f t="shared" ref="C25:F25" si="64">C8/C3</f>
         <v>0</v>
       </c>
       <c r="D25" s="8">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>2.4195015462979808E-2</v>
       </c>
       <c r="E25" s="8">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>3.6136205698401667E-2</v>
       </c>
       <c r="F25" s="8">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>2.5786487880350697E-3</v>
       </c>
       <c r="G25" s="8">
@@ -4045,115 +4045,115 @@
         <v>3.6708420320111346E-2</v>
       </c>
       <c r="H25" s="8">
-        <f t="shared" ref="H25:N25" si="64">H8/H3</f>
+        <f t="shared" ref="H25:N25" si="65">H8/H3</f>
         <v>3.1903014834901897E-3</v>
       </c>
       <c r="I25" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="J25" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>4.7037263286499695E-2</v>
       </c>
       <c r="K25" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>1.9848771266540641E-2</v>
       </c>
       <c r="L25" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>1.4078437006177273E-2</v>
       </c>
       <c r="M25" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>2.388383769846655E-2</v>
       </c>
       <c r="N25" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>3.7388169314995327E-2</v>
       </c>
       <c r="O25" s="8">
-        <f t="shared" ref="O25:R25" si="65">O8/O3</f>
+        <f t="shared" ref="O25:R25" si="66">O8/O3</f>
         <v>2.0827586206896551E-2</v>
       </c>
       <c r="P25" s="8">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>2.0000000000000004E-2</v>
       </c>
       <c r="Q25" s="8">
-        <f t="shared" si="65"/>
-        <v>0.02</v>
-      </c>
-      <c r="R25" s="8">
-        <f t="shared" si="65"/>
-        <v>0.04</v>
-      </c>
-      <c r="T25" s="8">
-        <f t="shared" ref="T25:AJ25" si="66">T8/T3</f>
-        <v>0</v>
-      </c>
-      <c r="U25" s="8">
-        <f t="shared" si="66"/>
-        <v>4.7709300045748644E-3</v>
-      </c>
-      <c r="V25" s="8">
-        <f t="shared" si="66"/>
-        <v>4.977758949375132E-3</v>
-      </c>
-      <c r="W25" s="8">
-        <f t="shared" si="66"/>
-        <v>1.6009353779736474E-2</v>
-      </c>
-      <c r="X25" s="8">
-        <f t="shared" si="66"/>
-        <v>2.1475814805960634E-2</v>
-      </c>
-      <c r="Y25" s="8">
-        <f t="shared" si="66"/>
-        <v>2.4141726133418539E-2</v>
-      </c>
-      <c r="Z25" s="8">
-        <f t="shared" si="66"/>
-        <v>2.5414443123265958E-2</v>
-      </c>
-      <c r="AA25" s="8">
         <f t="shared" si="66"/>
         <v>0.02</v>
       </c>
+      <c r="R25" s="8">
+        <f t="shared" si="66"/>
+        <v>0.04</v>
+      </c>
+      <c r="T25" s="8">
+        <f t="shared" ref="T25:AJ25" si="67">T8/T3</f>
+        <v>0</v>
+      </c>
+      <c r="U25" s="8">
+        <f t="shared" si="67"/>
+        <v>4.7709300045748644E-3</v>
+      </c>
+      <c r="V25" s="8">
+        <f t="shared" si="67"/>
+        <v>4.977758949375132E-3</v>
+      </c>
+      <c r="W25" s="8">
+        <f t="shared" si="67"/>
+        <v>1.6009353779736474E-2</v>
+      </c>
+      <c r="X25" s="8">
+        <f t="shared" si="67"/>
+        <v>2.1475814805960634E-2</v>
+      </c>
+      <c r="Y25" s="8">
+        <f t="shared" si="67"/>
+        <v>2.4141726133418539E-2</v>
+      </c>
+      <c r="Z25" s="8">
+        <f t="shared" si="67"/>
+        <v>2.5414443123265958E-2</v>
+      </c>
+      <c r="AA25" s="8">
+        <f t="shared" si="67"/>
+        <v>0.02</v>
+      </c>
       <c r="AB25" s="8">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0.02</v>
       </c>
       <c r="AC25" s="8">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0.02</v>
       </c>
       <c r="AD25" s="8">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0.02</v>
       </c>
       <c r="AE25" s="8">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0.02</v>
       </c>
       <c r="AF25" s="8">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0.02</v>
       </c>
       <c r="AG25" s="8">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0.02</v>
       </c>
       <c r="AH25" s="8">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0.02</v>
       </c>
       <c r="AI25" s="8">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0.02</v>
       </c>
       <c r="AJ25" s="8">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0.02</v>
       </c>
       <c r="AL25" t="s">
@@ -4169,19 +4169,19 @@
         <v>43</v>
       </c>
       <c r="C26" s="8">
-        <f t="shared" ref="C26:F26" si="67">C9/C3</f>
+        <f t="shared" ref="C26:F26" si="68">C9/C3</f>
         <v>0.57093090768337529</v>
       </c>
       <c r="D26" s="8">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>0.54902674185919598</v>
       </c>
       <c r="E26" s="8">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>0.54065323141070187</v>
       </c>
       <c r="F26" s="8">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>0.54736118274024415</v>
       </c>
       <c r="G26" s="8">
@@ -4189,115 +4189,115 @@
         <v>0.54558107167710512</v>
       </c>
       <c r="H26" s="8">
-        <f t="shared" ref="H26:N26" si="68">H9/H3</f>
+        <f t="shared" ref="H26:N26" si="69">H9/H3</f>
         <v>0.58318711118200672</v>
       </c>
       <c r="I26" s="8">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>0.58839736721261293</v>
       </c>
       <c r="J26" s="8">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>0.51496640195479537</v>
       </c>
       <c r="K26" s="8">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>0.56773787019533717</v>
       </c>
       <c r="L26" s="8">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>0.57980175262174971</v>
       </c>
       <c r="M26" s="8">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>0.54335730764011403</v>
       </c>
       <c r="N26" s="8">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>0.52583789558018423</v>
       </c>
       <c r="O26" s="8">
-        <f t="shared" ref="O26:R26" si="69">O9/O3</f>
+        <f t="shared" ref="O26:R26" si="70">O9/O3</f>
         <v>0.57227586206896552</v>
       </c>
       <c r="P26" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>0.55825425328873113</v>
       </c>
       <c r="Q26" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>0.55001192253261744</v>
       </c>
       <c r="R26" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>0.51971558285485386</v>
       </c>
       <c r="T26" s="8">
-        <f t="shared" ref="T26:AJ26" si="70">T9/T3</f>
+        <f t="shared" ref="T26:AJ26" si="71">T9/T3</f>
         <v>0.57241011668542319</v>
       </c>
       <c r="U26" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>0.52813541598588332</v>
       </c>
       <c r="V26" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>0.53389112476170308</v>
       </c>
       <c r="W26" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>0.55151324369294419</v>
       </c>
       <c r="X26" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>0.55813212208144081</v>
       </c>
       <c r="Y26" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>0.55320055383959954</v>
       </c>
       <c r="Z26" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>0.54925394213238199</v>
       </c>
       <c r="AA26" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>0.59000000000000008</v>
       </c>
       <c r="AB26" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>0.59</v>
       </c>
       <c r="AC26" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>0.59</v>
       </c>
       <c r="AD26" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>0.59000000000000008</v>
       </c>
       <c r="AE26" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>0.59000000000000008</v>
       </c>
       <c r="AF26" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>0.59</v>
       </c>
       <c r="AG26" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>0.59</v>
       </c>
       <c r="AH26" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>0.59</v>
       </c>
       <c r="AI26" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>0.59</v>
       </c>
       <c r="AJ26" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>0.59</v>
       </c>
       <c r="AL26" t="s">
@@ -4313,19 +4313,19 @@
         <v>44</v>
       </c>
       <c r="C27" s="8">
-        <f t="shared" ref="C27:F27" si="71">C15/C3</f>
+        <f t="shared" ref="C27:F27" si="72">C15/C3</f>
         <v>0.53667505322237274</v>
       </c>
       <c r="D27" s="8">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0.50900491177005636</v>
       </c>
       <c r="E27" s="8">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0.53370396108408613</v>
       </c>
       <c r="F27" s="8">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0.53102974041602202</v>
       </c>
       <c r="G27" s="8">
@@ -4333,115 +4333,115 @@
         <v>0.49634655532359079</v>
       </c>
       <c r="H27" s="8">
-        <f t="shared" ref="H27:N27" si="72">H15/H3</f>
+        <f t="shared" ref="H27:N27" si="73">H15/H3</f>
         <v>0.59084383474238311</v>
       </c>
       <c r="I27" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>0.57569263737945808</v>
       </c>
       <c r="J27" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>0.50717776420281002</v>
       </c>
       <c r="K27" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>0.56049149338374293</v>
       </c>
       <c r="L27" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>0.56586697313604373</v>
       </c>
       <c r="M27" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>0.52463020762654367</v>
       </c>
       <c r="N27" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>0.51956202430231002</v>
       </c>
       <c r="O27" s="8">
-        <f t="shared" ref="O27:R27" si="73">O15/O3</f>
+        <f t="shared" ref="O27:R27" si="74">O15/O3</f>
         <v>0.55600000000000005</v>
       </c>
       <c r="P27" s="8">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>0.54556365054282019</v>
       </c>
       <c r="Q27" s="8">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>0.53295688502025862</v>
       </c>
       <c r="R27" s="8">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>0.51389613857900696</v>
       </c>
       <c r="T27" s="8">
-        <f t="shared" ref="T27:AJ27" si="74">T15/T3</f>
+        <f t="shared" ref="T27:AJ27" si="75">T15/T3</f>
         <v>0.57637860569803945</v>
       </c>
       <c r="U27" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>0.50715639500686227</v>
       </c>
       <c r="V27" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>0.54580597331073921</v>
       </c>
       <c r="W27" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>0.52758915321311328</v>
       </c>
       <c r="X27" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>0.54342975535899274</v>
       </c>
       <c r="Y27" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>0.54155572123406825</v>
       </c>
       <c r="Z27" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>0.53639179389615532</v>
       </c>
       <c r="AA27" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>0.57825931034482758</v>
       </c>
       <c r="AB27" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>0.5790221706562253</v>
       </c>
       <c r="AC27" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>0.57954329364736734</v>
       </c>
       <c r="AD27" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>0.57994631090108661</v>
       </c>
       <c r="AE27" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>0.58024234944691655</v>
       </c>
       <c r="AF27" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>0.58043924500775268</v>
       </c>
       <c r="AG27" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>0.58063370732877129</v>
       </c>
       <c r="AH27" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>0.58082577522683732</v>
       </c>
       <c r="AI27" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>0.58101548669943348</v>
       </c>
       <c r="AJ27" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>0.58120287894550393</v>
       </c>
       <c r="AL27" t="s">
@@ -4457,19 +4457,19 @@
         <v>21</v>
       </c>
       <c r="C28" s="8">
-        <f t="shared" ref="C28:F28" si="75">C16/C15</f>
+        <f t="shared" ref="C28:F28" si="76">C16/C15</f>
         <v>5.120807789397764E-2</v>
       </c>
       <c r="D28" s="8">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>0.18691922802001429</v>
       </c>
       <c r="E28" s="8">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>0.1865234375</v>
       </c>
       <c r="F28" s="8">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>0.18258336031078018</v>
       </c>
       <c r="G28" s="8">
@@ -4477,115 +4477,115 @@
         <v>0.17245005257623555</v>
       </c>
       <c r="H28" s="8">
-        <f t="shared" ref="H28:N28" si="76">H16/H15</f>
+        <f t="shared" ref="H28:N28" si="77">H16/H15</f>
         <v>0.23191144708423325</v>
       </c>
       <c r="I28" s="8">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>0.14969423025791012</v>
       </c>
       <c r="J28" s="8">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>0.15959048479373683</v>
       </c>
       <c r="K28" s="8">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>0.1537380550871276</v>
       </c>
       <c r="L28" s="8">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>0.17288651942117289</v>
       </c>
       <c r="M28" s="8">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>0.15597516813243661</v>
       </c>
       <c r="N28" s="8">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>0.14109483423284502</v>
       </c>
       <c r="O28" s="8">
-        <f t="shared" ref="O28:R28" si="77">O16/O15</f>
+        <f t="shared" ref="O28:R28" si="78">O16/O15</f>
         <v>0.18630612751178369</v>
       </c>
       <c r="P28" s="8">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>0.15</v>
       </c>
       <c r="Q28" s="8">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>0.15</v>
       </c>
       <c r="R28" s="8">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>0.15</v>
       </c>
       <c r="T28" s="8">
-        <f t="shared" ref="T28:AJ28" si="78">T16/T15</f>
+        <f t="shared" ref="T28:AJ28" si="79">T16/T15</f>
         <v>0.16575891480834445</v>
       </c>
       <c r="U28" s="8">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>0.173840206185567</v>
       </c>
       <c r="V28" s="8">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>0.15717473561657128</v>
       </c>
       <c r="W28" s="8">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>0.15359699965905216</v>
       </c>
       <c r="X28" s="8">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>0.17919202287557739</v>
       </c>
       <c r="Y28" s="8">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>0.15602464927232201</v>
       </c>
       <c r="Z28" s="8">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>0.15865133916168569</v>
       </c>
       <c r="AA28" s="8">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>0.16</v>
       </c>
       <c r="AB28" s="8">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>0.16</v>
       </c>
       <c r="AC28" s="8">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>0.16</v>
       </c>
       <c r="AD28" s="8">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>0.16</v>
       </c>
       <c r="AE28" s="8">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>0.16</v>
       </c>
       <c r="AF28" s="8">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>0.16</v>
       </c>
       <c r="AG28" s="8">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>0.16</v>
       </c>
       <c r="AH28" s="8">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>0.16</v>
       </c>
       <c r="AI28" s="8">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>0.16000000000000003</v>
       </c>
       <c r="AJ28" s="8">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>0.16</v>
       </c>
       <c r="AL28" t="s">
@@ -4601,19 +4601,19 @@
         <v>45</v>
       </c>
       <c r="C29" s="8">
-        <f t="shared" ref="C29:F29" si="79">C17/C3</f>
+        <f t="shared" ref="C29:F29" si="80">C17/C3</f>
         <v>0.50919295529320685</v>
       </c>
       <c r="D29" s="8">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>0.41386210660360195</v>
       </c>
       <c r="E29" s="8">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>0.43415566365531622</v>
       </c>
       <c r="F29" s="8">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>0.43407254598590339</v>
       </c>
       <c r="G29" s="8">
@@ -4621,115 +4621,115 @@
         <v>0.41075156576200417</v>
       </c>
       <c r="H29" s="8">
-        <f t="shared" ref="H29:N29" si="80">H17/H3</f>
+        <f t="shared" ref="H29:N29" si="81">H17/H3</f>
         <v>0.45382038602647951</v>
       </c>
       <c r="I29" s="8">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>0.48951477116179398</v>
       </c>
       <c r="J29" s="8">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>0.42623701893708005</v>
       </c>
       <c r="K29" s="8">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>0.47432262129804664</v>
       </c>
       <c r="L29" s="8">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>0.46803620169515875</v>
       </c>
       <c r="M29" s="8">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>0.44280092278463834</v>
       </c>
       <c r="N29" s="8">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>0.44625450660969423</v>
       </c>
       <c r="O29" s="8">
-        <f t="shared" ref="O29:R29" si="81">O17/O3</f>
+        <f t="shared" ref="O29:R29" si="82">O17/O3</f>
         <v>0.45241379310344826</v>
       </c>
       <c r="P29" s="8">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>0.46372910296139724</v>
       </c>
       <c r="Q29" s="8">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>0.45301335226721984</v>
       </c>
       <c r="R29" s="8">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>0.43681171779215594</v>
       </c>
       <c r="T29" s="8">
-        <f t="shared" ref="T29:AJ29" si="82">T17/T3</f>
+        <f t="shared" ref="T29:AJ29" si="83">T17/T3</f>
         <v>0.48083871349878576</v>
       </c>
       <c r="U29" s="8">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>0.41899222273054049</v>
       </c>
       <c r="V29" s="8">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>0.46001906375767848</v>
       </c>
       <c r="W29" s="8">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>0.44655304222691911</v>
       </c>
       <c r="X29" s="8">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>0.44605147820543467</v>
       </c>
       <c r="Y29" s="8">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>0.45705967976710332</v>
       </c>
       <c r="Z29" s="8">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>0.45129251747919136</v>
       </c>
       <c r="AA29" s="8">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>0.48573782068965515</v>
       </c>
       <c r="AB29" s="8">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>0.48637862335122922</v>
       </c>
       <c r="AC29" s="8">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>0.48681636666378858</v>
       </c>
       <c r="AD29" s="8">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>0.48715490115691273</v>
       </c>
       <c r="AE29" s="8">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>0.48740357353540992</v>
       </c>
       <c r="AF29" s="8">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>0.48756896580651227</v>
       </c>
       <c r="AG29" s="8">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>0.48773231415616791</v>
       </c>
       <c r="AH29" s="8">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>0.48789365119054334</v>
       </c>
       <c r="AI29" s="8">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>0.48805300882752406</v>
       </c>
       <c r="AJ29" s="8">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>0.48821041831422329</v>
       </c>
       <c r="AL29" t="s">
@@ -4737,7 +4737,7 @@
       </c>
       <c r="AM29" s="10">
         <f>Main!D3</f>
-        <v>559.39</v>
+        <v>568.04</v>
       </c>
     </row>
     <row r="30" spans="1:146" x14ac:dyDescent="0.3">
@@ -4746,7 +4746,7 @@
       </c>
       <c r="AM30" s="9">
         <f>AM28/AM29-1</f>
-        <v>-0.35142924937740316</v>
+        <v>-0.36130555561091737</v>
       </c>
     </row>
     <row r="31" spans="1:146" x14ac:dyDescent="0.3">

--- a/Financial Analysis/MA.xlsx
+++ b/Financial Analysis/MA.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FC489AC-CE50-4BE7-8EAB-308612A3A929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B9104A0-D0CC-42DE-8F61-5A0CA24CF7C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{5EE3D269-52EC-4F93-A9AE-4AAFACF544BD}"/>
   </bookViews>
@@ -308,14 +308,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>83820</xdr:rowOff>
     </xdr:to>
@@ -332,7 +332,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10058400" y="0"/>
+          <a:off x="10660380" y="0"/>
           <a:ext cx="0" cy="6118860"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -733,17 +733,17 @@
         <v>0</v>
       </c>
       <c r="D3" s="10">
-        <v>568.04</v>
+        <v>575.01</v>
       </c>
       <c r="E3" s="3">
-        <v>45804</v>
+        <v>45869</v>
       </c>
       <c r="F3" s="3">
         <f ca="1">TODAY()</f>
-        <v>45804</v>
+        <v>45869</v>
       </c>
       <c r="G3" s="3">
-        <v>45862</v>
+        <v>45953</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -751,11 +751,11 @@
         <v>1</v>
       </c>
       <c r="D4" s="1">
-        <f>901.3+6.8</f>
-        <v>908.09999999999991</v>
+        <f>897.3+6.7</f>
+        <v>904</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
@@ -764,7 +764,7 @@
       </c>
       <c r="D5" s="1">
         <f>D3*D4</f>
-        <v>515837.12399999989</v>
+        <v>519809.04</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -772,11 +772,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="1">
-        <f>7575+319</f>
-        <v>7894</v>
+        <f>9031+336</f>
+        <v>9367</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
@@ -784,11 +784,11 @@
         <v>5</v>
       </c>
       <c r="D7" s="1">
-        <f>18802</f>
-        <v>18802</v>
+        <f>18970</f>
+        <v>18970</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
@@ -797,7 +797,7 @@
       </c>
       <c r="D8" s="1">
         <f>D6-D7</f>
-        <v>-10908</v>
+        <v>-9603</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
@@ -806,7 +806,7 @@
       </c>
       <c r="D9" s="1">
         <f>D5-D8</f>
-        <v>526745.12399999984</v>
+        <v>529412.04</v>
       </c>
     </row>
   </sheetData>
@@ -970,16 +970,15 @@
         <v>7250</v>
       </c>
       <c r="P3" s="7">
-        <f>L3*1.12</f>
-        <v>7796.3200000000006</v>
+        <v>8133</v>
       </c>
       <c r="Q3" s="7">
-        <f>M3*1.12</f>
-        <v>8253.2800000000007</v>
+        <f>M3*1.14</f>
+        <v>8400.66</v>
       </c>
       <c r="R3" s="7">
-        <f>N3*1.1</f>
-        <v>8237.9000000000015</v>
+        <f>N3*1.14</f>
+        <v>8537.4599999999991</v>
       </c>
       <c r="T3" s="7">
         <v>16883</v>
@@ -1004,47 +1003,47 @@
       </c>
       <c r="Z3" s="7">
         <f>SUM(O3:R3)</f>
-        <v>31537.5</v>
+        <v>32321.119999999999</v>
       </c>
       <c r="AA3" s="7">
-        <f>Z3*1.1</f>
-        <v>34691.25</v>
+        <f>Z3*1.12</f>
+        <v>36199.654399999999</v>
       </c>
       <c r="AB3" s="7">
-        <f>AA3*1.08</f>
-        <v>37466.550000000003</v>
+        <f>AA3*1.09</f>
+        <v>39457.623296000005</v>
       </c>
       <c r="AC3" s="7">
-        <f>AB3*1.06</f>
-        <v>39714.543000000005</v>
+        <f>AB3*1.07</f>
+        <v>42219.65692672001</v>
       </c>
       <c r="AD3" s="7">
         <f>AC3*1.05</f>
-        <v>41700.270150000004</v>
+        <v>44330.639773056013</v>
       </c>
       <c r="AE3" s="7">
         <f>AD3*1.04</f>
-        <v>43368.280956000002</v>
+        <v>46103.865363978257</v>
       </c>
       <c r="AF3" s="7">
         <f>AE3*1.03</f>
-        <v>44669.329384680001</v>
+        <v>47486.981324897606</v>
       </c>
       <c r="AG3" s="7">
         <f t="shared" ref="AG3:AJ3" si="0">AF3*1.03</f>
-        <v>46009.409266220398</v>
+        <v>48911.590764644534</v>
       </c>
       <c r="AH3" s="7">
         <f t="shared" si="0"/>
-        <v>47389.691544207009</v>
+        <v>50378.938487583873</v>
       </c>
       <c r="AI3" s="7">
         <f t="shared" si="0"/>
-        <v>48811.38229053322</v>
+        <v>51890.306642211392</v>
       </c>
       <c r="AJ3" s="7">
         <f t="shared" si="0"/>
-        <v>50275.723759249217</v>
+        <v>53447.015841477732</v>
       </c>
     </row>
     <row r="4" spans="1:36" x14ac:dyDescent="0.3">
@@ -1091,16 +1090,15 @@
         <v>2523</v>
       </c>
       <c r="P4" s="1">
-        <f t="shared" ref="P4" si="1">P3-P5</f>
-        <v>2806.6751999999997</v>
+        <v>2766</v>
       </c>
       <c r="Q4" s="1">
-        <f t="shared" ref="Q4" si="2">Q3-Q5</f>
-        <v>3053.7136</v>
+        <f t="shared" ref="Q4" si="1">Q3-Q5</f>
+        <v>3024.2375999999995</v>
       </c>
       <c r="R4" s="1">
-        <f t="shared" ref="R4" si="3">R3-R5</f>
-        <v>3048.0230000000001</v>
+        <f t="shared" ref="R4" si="2">R3-R5</f>
+        <v>3158.8602000000001</v>
       </c>
       <c r="T4" s="1">
         <v>5763</v>
@@ -1125,47 +1123,47 @@
       </c>
       <c r="Z4" s="1">
         <f>SUM(O4:R4)</f>
-        <v>11431.411800000002</v>
+        <v>11472.0978</v>
       </c>
       <c r="AA4" s="1">
-        <f t="shared" ref="AA4:AJ4" si="4">AA3-AA5</f>
-        <v>12488.849999999999</v>
+        <f t="shared" ref="AA4:AJ4" si="3">AA3-AA5</f>
+        <v>12669.87904</v>
       </c>
       <c r="AB4" s="1">
-        <f t="shared" si="4"/>
-        <v>13487.958000000002</v>
+        <f t="shared" si="3"/>
+        <v>13415.591920639999</v>
       </c>
       <c r="AC4" s="1">
-        <f t="shared" si="4"/>
-        <v>14297.235480000003</v>
+        <f t="shared" si="3"/>
+        <v>14354.683355084802</v>
       </c>
       <c r="AD4" s="1">
-        <f t="shared" si="4"/>
-        <v>15012.097254</v>
+        <f t="shared" si="3"/>
+        <v>15072.417522839041</v>
       </c>
       <c r="AE4" s="1">
-        <f t="shared" si="4"/>
-        <v>15612.581144160002</v>
+        <f t="shared" si="3"/>
+        <v>15675.314223752604</v>
       </c>
       <c r="AF4" s="1">
-        <f t="shared" si="4"/>
-        <v>16080.958578484799</v>
+        <f t="shared" si="3"/>
+        <v>16145.573650465183</v>
       </c>
       <c r="AG4" s="1">
-        <f t="shared" si="4"/>
-        <v>16563.387335839343</v>
+        <f t="shared" si="3"/>
+        <v>16629.940859979139</v>
       </c>
       <c r="AH4" s="1">
-        <f t="shared" si="4"/>
-        <v>17060.288955914522</v>
+        <f t="shared" si="3"/>
+        <v>17128.839085778513</v>
       </c>
       <c r="AI4" s="1">
-        <f t="shared" si="4"/>
-        <v>17572.097624591959</v>
+        <f t="shared" si="3"/>
+        <v>17642.704258351871</v>
       </c>
       <c r="AJ4" s="1">
-        <f t="shared" si="4"/>
-        <v>18099.260553329717</v>
+        <f t="shared" si="3"/>
+        <v>18171.985386102424</v>
       </c>
     </row>
     <row r="5" spans="1:36" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -1174,136 +1172,136 @@
         <v>12</v>
       </c>
       <c r="C5" s="7">
-        <f t="shared" ref="C5:O5" si="5">C3-C4</f>
+        <f t="shared" ref="C5:P5" si="4">C3-C4</f>
         <v>3323</v>
       </c>
       <c r="D5" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>3550</v>
       </c>
       <c r="E5" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>3687</v>
       </c>
       <c r="F5" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>3599</v>
       </c>
       <c r="G5" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>3705</v>
       </c>
       <c r="H5" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>4069</v>
       </c>
       <c r="I5" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>4248</v>
       </c>
       <c r="J5" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>4149</v>
       </c>
       <c r="K5" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>4062</v>
       </c>
       <c r="L5" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>4543</v>
       </c>
       <c r="M5" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>4625</v>
       </c>
       <c r="N5" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>4744</v>
       </c>
       <c r="O5" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>4727</v>
       </c>
       <c r="P5" s="7">
-        <f>P3*0.64</f>
-        <v>4989.6448000000009</v>
+        <f t="shared" si="4"/>
+        <v>5367</v>
       </c>
       <c r="Q5" s="7">
-        <f>Q3*0.63</f>
-        <v>5199.5664000000006</v>
+        <f>Q3*0.64</f>
+        <v>5376.4224000000004</v>
       </c>
       <c r="R5" s="7">
         <f>R3*0.63</f>
-        <v>5189.8770000000013</v>
+        <v>5378.599799999999</v>
       </c>
       <c r="T5" s="7">
-        <f t="shared" ref="T5:Z5" si="6">T3-T4</f>
+        <f t="shared" ref="T5:Z5" si="5">T3-T4</f>
         <v>11120</v>
       </c>
       <c r="U5" s="7">
+        <f t="shared" si="5"/>
+        <v>9391</v>
+      </c>
+      <c r="V5" s="7">
+        <f t="shared" si="5"/>
+        <v>11797</v>
+      </c>
+      <c r="W5" s="7">
+        <f t="shared" si="5"/>
+        <v>14159</v>
+      </c>
+      <c r="X5" s="7">
+        <f t="shared" si="5"/>
+        <v>16171</v>
+      </c>
+      <c r="Y5" s="7">
+        <f t="shared" si="5"/>
+        <v>17974</v>
+      </c>
+      <c r="Z5" s="7">
+        <f t="shared" si="5"/>
+        <v>20849.022199999999</v>
+      </c>
+      <c r="AA5" s="7">
+        <f>AA3*0.65</f>
+        <v>23529.77536</v>
+      </c>
+      <c r="AB5" s="7">
+        <f>AB3*0.66</f>
+        <v>26042.031375360006</v>
+      </c>
+      <c r="AC5" s="7">
+        <f t="shared" ref="AC5:AJ5" si="6">AC3*0.66</f>
+        <v>27864.973571635208</v>
+      </c>
+      <c r="AD5" s="7">
         <f t="shared" si="6"/>
-        <v>9391</v>
-      </c>
-      <c r="V5" s="7">
+        <v>29258.222250216972</v>
+      </c>
+      <c r="AE5" s="7">
         <f t="shared" si="6"/>
-        <v>11797</v>
-      </c>
-      <c r="W5" s="7">
+        <v>30428.551140225652</v>
+      </c>
+      <c r="AF5" s="7">
         <f t="shared" si="6"/>
-        <v>14159</v>
-      </c>
-      <c r="X5" s="7">
+        <v>31341.407674432423</v>
+      </c>
+      <c r="AG5" s="7">
         <f t="shared" si="6"/>
-        <v>16171</v>
-      </c>
-      <c r="Y5" s="7">
+        <v>32281.649904665395</v>
+      </c>
+      <c r="AH5" s="7">
         <f t="shared" si="6"/>
-        <v>17974</v>
-      </c>
-      <c r="Z5" s="7">
+        <v>33250.099401805361</v>
+      </c>
+      <c r="AI5" s="7">
         <f t="shared" si="6"/>
-        <v>20106.088199999998</v>
-      </c>
-      <c r="AA5" s="7">
-        <f t="shared" ref="AA5:AJ5" si="7">AA3*0.64</f>
-        <v>22202.400000000001</v>
-      </c>
-      <c r="AB5" s="7">
-        <f t="shared" si="7"/>
-        <v>23978.592000000001</v>
-      </c>
-      <c r="AC5" s="7">
-        <f t="shared" si="7"/>
-        <v>25417.307520000002</v>
-      </c>
-      <c r="AD5" s="7">
-        <f t="shared" si="7"/>
-        <v>26688.172896000004</v>
-      </c>
-      <c r="AE5" s="7">
-        <f t="shared" si="7"/>
-        <v>27755.699811840001</v>
-      </c>
-      <c r="AF5" s="7">
-        <f t="shared" si="7"/>
-        <v>28588.370806195202</v>
-      </c>
-      <c r="AG5" s="7">
-        <f t="shared" si="7"/>
-        <v>29446.021930381055</v>
-      </c>
-      <c r="AH5" s="7">
-        <f t="shared" si="7"/>
-        <v>30329.402588292487</v>
-      </c>
-      <c r="AI5" s="7">
-        <f t="shared" si="7"/>
-        <v>31239.284665941261</v>
+        <v>34247.602383859521</v>
       </c>
       <c r="AJ5" s="7">
-        <f t="shared" si="7"/>
-        <v>32176.463205919499</v>
+        <f t="shared" si="6"/>
+        <v>35275.030455375309</v>
       </c>
     </row>
     <row r="6" spans="1:36" x14ac:dyDescent="0.3">
@@ -1350,16 +1348,15 @@
         <v>152</v>
       </c>
       <c r="P6" s="1">
-        <f>P3*0.03</f>
-        <v>233.8896</v>
+        <v>213</v>
       </c>
       <c r="Q6" s="1">
         <f>Q3*0.03</f>
-        <v>247.5984</v>
+        <v>252.01979999999998</v>
       </c>
       <c r="R6" s="1">
         <f>R3*0.04</f>
-        <v>329.51600000000008</v>
+        <v>341.49839999999995</v>
       </c>
       <c r="T6" s="1">
         <v>934</v>
@@ -1384,47 +1381,47 @@
       </c>
       <c r="Z6" s="1">
         <f>SUM(O6:R6)</f>
-        <v>963.00400000000002</v>
+        <v>958.51819999999998</v>
       </c>
       <c r="AA6" s="1">
-        <f t="shared" ref="AA6:AJ6" si="8">AA3*0.03</f>
-        <v>1040.7375</v>
+        <f t="shared" ref="AA6:AJ6" si="7">AA3*0.03</f>
+        <v>1085.989632</v>
       </c>
       <c r="AB6" s="1">
-        <f t="shared" si="8"/>
-        <v>1123.9965</v>
+        <f t="shared" si="7"/>
+        <v>1183.7286988800001</v>
       </c>
       <c r="AC6" s="1">
-        <f t="shared" si="8"/>
-        <v>1191.4362900000001</v>
+        <f t="shared" si="7"/>
+        <v>1266.5897078016003</v>
       </c>
       <c r="AD6" s="1">
-        <f t="shared" si="8"/>
-        <v>1251.0081045000002</v>
+        <f t="shared" si="7"/>
+        <v>1329.9191931916803</v>
       </c>
       <c r="AE6" s="1">
-        <f t="shared" si="8"/>
-        <v>1301.0484286799999</v>
+        <f t="shared" si="7"/>
+        <v>1383.1159609193476</v>
       </c>
       <c r="AF6" s="1">
-        <f t="shared" si="8"/>
-        <v>1340.0798815404</v>
+        <f t="shared" si="7"/>
+        <v>1424.609439746928</v>
       </c>
       <c r="AG6" s="1">
-        <f t="shared" si="8"/>
-        <v>1380.2822779866119</v>
+        <f t="shared" si="7"/>
+        <v>1467.3477229393359</v>
       </c>
       <c r="AH6" s="1">
-        <f t="shared" si="8"/>
-        <v>1421.6907463262103</v>
+        <f t="shared" si="7"/>
+        <v>1511.3681546275161</v>
       </c>
       <c r="AI6" s="1">
-        <f t="shared" si="8"/>
-        <v>1464.3414687159966</v>
+        <f t="shared" si="7"/>
+        <v>1556.7091992663418</v>
       </c>
       <c r="AJ6" s="1">
-        <f t="shared" si="8"/>
-        <v>1508.2717127774765</v>
+        <f t="shared" si="7"/>
+        <v>1603.410475244332</v>
       </c>
     </row>
     <row r="7" spans="1:36" x14ac:dyDescent="0.3">
@@ -1471,16 +1468,15 @@
         <v>275</v>
       </c>
       <c r="P7" s="1">
-        <f t="shared" ref="P7:Q7" si="9">L7*1.1</f>
-        <v>247.50000000000003</v>
+        <v>281</v>
       </c>
       <c r="Q7" s="1">
-        <f t="shared" si="9"/>
-        <v>247.50000000000003</v>
+        <f>M7*1.25</f>
+        <v>281.25</v>
       </c>
       <c r="R7" s="1">
-        <f>N7*1.08</f>
-        <v>249.48000000000002</v>
+        <f>N7*1.25</f>
+        <v>288.75</v>
       </c>
       <c r="T7" s="1">
         <v>522</v>
@@ -1505,7 +1501,7 @@
       </c>
       <c r="Z7" s="1">
         <f>SUM(O7:R7)</f>
-        <v>1019.48</v>
+        <v>1126</v>
       </c>
       <c r="AA7" s="1"/>
       <c r="AB7" s="1"/>
@@ -1562,16 +1558,15 @@
         <v>151</v>
       </c>
       <c r="P8" s="1">
-        <f t="shared" ref="P8:Q8" si="10">P3*0.02</f>
-        <v>155.92640000000003</v>
+        <v>96</v>
       </c>
       <c r="Q8" s="1">
-        <f t="shared" si="10"/>
-        <v>165.06560000000002</v>
+        <f t="shared" ref="Q8" si="8">Q3*0.02</f>
+        <v>168.01320000000001</v>
       </c>
       <c r="R8" s="1">
         <f>R3*0.04</f>
-        <v>329.51600000000008</v>
+        <v>341.49839999999995</v>
       </c>
       <c r="T8" s="1">
         <v>0</v>
@@ -1596,47 +1591,47 @@
       </c>
       <c r="Z8" s="1">
         <f>SUM(O8:R8)</f>
-        <v>801.50800000000015</v>
+        <v>756.51159999999993</v>
       </c>
       <c r="AA8" s="1">
-        <f t="shared" ref="AA8:AJ8" si="11">AA3*0.02</f>
-        <v>693.82500000000005</v>
+        <f t="shared" ref="AA8:AJ8" si="9">AA3*0.02</f>
+        <v>723.99308800000006</v>
       </c>
       <c r="AB8" s="1">
-        <f t="shared" si="11"/>
-        <v>749.33100000000002</v>
+        <f t="shared" si="9"/>
+        <v>789.15246592000017</v>
       </c>
       <c r="AC8" s="1">
-        <f t="shared" si="11"/>
-        <v>794.29086000000007</v>
+        <f t="shared" si="9"/>
+        <v>844.39313853440024</v>
       </c>
       <c r="AD8" s="1">
-        <f t="shared" si="11"/>
-        <v>834.00540300000011</v>
+        <f t="shared" si="9"/>
+        <v>886.6127954611203</v>
       </c>
       <c r="AE8" s="1">
-        <f t="shared" si="11"/>
-        <v>867.36561912000002</v>
+        <f t="shared" si="9"/>
+        <v>922.07730727956516</v>
       </c>
       <c r="AF8" s="1">
-        <f t="shared" si="11"/>
-        <v>893.38658769360006</v>
+        <f t="shared" si="9"/>
+        <v>949.73962649795214</v>
       </c>
       <c r="AG8" s="1">
-        <f t="shared" si="11"/>
-        <v>920.18818532440798</v>
+        <f t="shared" si="9"/>
+        <v>978.2318152928907</v>
       </c>
       <c r="AH8" s="1">
-        <f t="shared" si="11"/>
-        <v>947.79383088414022</v>
+        <f t="shared" si="9"/>
+        <v>1007.5787697516774</v>
       </c>
       <c r="AI8" s="1">
-        <f t="shared" si="11"/>
-        <v>976.2276458106644</v>
+        <f t="shared" si="9"/>
+        <v>1037.8061328442279</v>
       </c>
       <c r="AJ8" s="1">
-        <f t="shared" si="11"/>
-        <v>1005.5144751849843</v>
+        <f t="shared" si="9"/>
+        <v>1068.9403168295546</v>
       </c>
     </row>
     <row r="9" spans="1:36" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -1645,137 +1640,137 @@
         <v>16</v>
       </c>
       <c r="C9" s="7">
-        <f t="shared" ref="C9:K9" si="12">C5-C6-C7-C8</f>
+        <f t="shared" ref="C9:K9" si="10">C5-C6-C7-C8</f>
         <v>2950</v>
       </c>
       <c r="D9" s="7">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>3018</v>
       </c>
       <c r="E9" s="7">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>3112</v>
       </c>
       <c r="F9" s="7">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>3184</v>
       </c>
       <c r="G9" s="7">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>3136</v>
       </c>
       <c r="H9" s="7">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>3656</v>
       </c>
       <c r="I9" s="7">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>3844</v>
       </c>
       <c r="J9" s="7">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>3372</v>
       </c>
       <c r="K9" s="7">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>3604</v>
       </c>
       <c r="L9" s="7">
-        <f t="shared" ref="L9:R9" si="13">L5-L6-L7-L8</f>
+        <f t="shared" ref="L9:R9" si="11">L5-L6-L7-L8</f>
         <v>4036</v>
       </c>
       <c r="M9" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>4004</v>
       </c>
       <c r="N9" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>3938</v>
       </c>
       <c r="O9" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>4149</v>
       </c>
       <c r="P9" s="7">
-        <f t="shared" si="13"/>
-        <v>4352.3288000000002</v>
+        <f t="shared" si="11"/>
+        <v>4777</v>
       </c>
       <c r="Q9" s="7">
-        <f t="shared" si="13"/>
-        <v>4539.4024000000009</v>
+        <f t="shared" si="11"/>
+        <v>4675.1394</v>
       </c>
       <c r="R9" s="7">
-        <f t="shared" si="13"/>
-        <v>4281.3650000000016</v>
+        <f t="shared" si="11"/>
+        <v>4406.8529999999992</v>
       </c>
       <c r="S9" s="7"/>
       <c r="T9" s="7">
-        <f t="shared" ref="T9:Z9" si="14">T5-T6-T7-T8</f>
+        <f t="shared" ref="T9:Z9" si="12">T5-T6-T7-T8</f>
         <v>9664</v>
       </c>
       <c r="U9" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>8081</v>
       </c>
       <c r="V9" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>10082</v>
       </c>
       <c r="W9" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>12264</v>
       </c>
       <c r="X9" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>14008</v>
       </c>
       <c r="Y9" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>15582</v>
       </c>
       <c r="Z9" s="7">
-        <f t="shared" si="14"/>
-        <v>17322.096199999996</v>
+        <f t="shared" si="12"/>
+        <v>18007.992399999999</v>
       </c>
       <c r="AA9" s="7">
-        <f t="shared" ref="AA9:AJ9" si="15">AA5-AA6-AA7-AA8</f>
-        <v>20467.837500000001</v>
+        <f t="shared" ref="AA9:AJ9" si="13">AA5-AA6-AA7-AA8</f>
+        <v>21719.79264</v>
       </c>
       <c r="AB9" s="7">
-        <f t="shared" si="15"/>
-        <v>22105.264500000001</v>
+        <f t="shared" si="13"/>
+        <v>24069.150210560005</v>
       </c>
       <c r="AC9" s="7">
-        <f t="shared" si="15"/>
-        <v>23431.58037</v>
+        <f t="shared" si="13"/>
+        <v>25753.990725299209</v>
       </c>
       <c r="AD9" s="7">
-        <f t="shared" si="15"/>
-        <v>24603.159388500004</v>
+        <f t="shared" si="13"/>
+        <v>27041.69026156417</v>
       </c>
       <c r="AE9" s="7">
-        <f t="shared" si="15"/>
-        <v>25587.285764040003</v>
+        <f t="shared" si="13"/>
+        <v>28123.35787202674</v>
       </c>
       <c r="AF9" s="7">
-        <f t="shared" si="15"/>
-        <v>26354.904336961201</v>
+        <f t="shared" si="13"/>
+        <v>28967.058608187544</v>
       </c>
       <c r="AG9" s="7">
-        <f t="shared" si="15"/>
-        <v>27145.551467070036</v>
+        <f t="shared" si="13"/>
+        <v>29836.07036643317</v>
       </c>
       <c r="AH9" s="7">
-        <f t="shared" si="15"/>
-        <v>27959.918011082136</v>
+        <f t="shared" si="13"/>
+        <v>30731.152477426167</v>
       </c>
       <c r="AI9" s="7">
-        <f t="shared" si="15"/>
-        <v>28798.7155514146</v>
+        <f t="shared" si="13"/>
+        <v>31653.087051748953</v>
       </c>
       <c r="AJ9" s="7">
-        <f t="shared" si="15"/>
-        <v>29662.677017957038</v>
+        <f t="shared" si="13"/>
+        <v>32602.679663301424</v>
       </c>
     </row>
     <row r="10" spans="1:36" x14ac:dyDescent="0.3">
@@ -1822,15 +1817,14 @@
         <v>-88</v>
       </c>
       <c r="P10" s="1">
-        <f t="shared" ref="P10:R13" si="16">L10*1.02</f>
-        <v>-61.2</v>
+        <v>-70</v>
       </c>
       <c r="Q10" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" ref="Q10:R13" si="14">M10*1.02</f>
         <v>-77.52</v>
       </c>
       <c r="R10" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>-97.92</v>
       </c>
       <c r="T10" s="1">
@@ -1851,52 +1845,52 @@
         <v>-274</v>
       </c>
       <c r="Y10" s="1">
-        <f t="shared" ref="Y10:Y13" si="17">SUM(K10:N10)</f>
+        <f t="shared" ref="Y10:Y13" si="15">SUM(K10:N10)</f>
         <v>-327</v>
       </c>
       <c r="Z10" s="1">
         <f>SUM(O10:R10)</f>
-        <v>-324.64</v>
+        <v>-333.44</v>
       </c>
       <c r="AA10" s="1">
         <f>Z10*1.03</f>
-        <v>-334.37919999999997</v>
+        <v>-343.44319999999999</v>
       </c>
       <c r="AB10" s="1">
-        <f t="shared" ref="AB10:AJ10" si="18">AA10*1.03</f>
-        <v>-344.41057599999999</v>
+        <f t="shared" ref="AB10:AJ10" si="16">AA10*1.03</f>
+        <v>-353.74649599999998</v>
       </c>
       <c r="AC10" s="1">
-        <f t="shared" si="18"/>
-        <v>-354.74289327999998</v>
+        <f t="shared" si="16"/>
+        <v>-364.35889087999999</v>
       </c>
       <c r="AD10" s="1">
-        <f t="shared" si="18"/>
-        <v>-365.38518007839997</v>
+        <f t="shared" si="16"/>
+        <v>-375.2896576064</v>
       </c>
       <c r="AE10" s="1">
-        <f t="shared" si="18"/>
-        <v>-376.34673548075199</v>
+        <f t="shared" si="16"/>
+        <v>-386.54834733459199</v>
       </c>
       <c r="AF10" s="1">
-        <f t="shared" si="18"/>
-        <v>-387.63713754517454</v>
+        <f t="shared" si="16"/>
+        <v>-398.14479775462979</v>
       </c>
       <c r="AG10" s="1">
-        <f t="shared" si="18"/>
-        <v>-399.2662516715298</v>
+        <f t="shared" si="16"/>
+        <v>-410.08914168726869</v>
       </c>
       <c r="AH10" s="1">
-        <f t="shared" si="18"/>
-        <v>-411.24423922167568</v>
+        <f t="shared" si="16"/>
+        <v>-422.39181593788675</v>
       </c>
       <c r="AI10" s="1">
-        <f t="shared" si="18"/>
-        <v>-423.58156639832595</v>
+        <f t="shared" si="16"/>
+        <v>-435.06357041602337</v>
       </c>
       <c r="AJ10" s="1">
-        <f t="shared" si="18"/>
-        <v>-436.28901339027573</v>
+        <f t="shared" si="16"/>
+        <v>-448.11547752850407</v>
       </c>
     </row>
     <row r="11" spans="1:36" x14ac:dyDescent="0.3">
@@ -1943,15 +1937,14 @@
         <v>29</v>
       </c>
       <c r="P11" s="1">
-        <f t="shared" si="16"/>
-        <v>13.26</v>
+        <v>-4</v>
       </c>
       <c r="Q11" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>63.24</v>
       </c>
       <c r="R11" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>-40.799999999999997</v>
       </c>
       <c r="T11" s="1">
@@ -1972,12 +1965,12 @@
         <v>61</v>
       </c>
       <c r="Y11" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>29</v>
       </c>
       <c r="Z11" s="1">
         <f>SUM(O11:R11)</f>
-        <v>64.7</v>
+        <v>47.440000000000012</v>
       </c>
       <c r="AA11" s="1">
         <v>40</v>
@@ -2054,15 +2047,14 @@
         <v>182</v>
       </c>
       <c r="P12" s="1">
-        <f t="shared" si="16"/>
-        <v>156.06</v>
+        <v>195</v>
       </c>
       <c r="Q12" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>162.18</v>
       </c>
       <c r="R12" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>187.68</v>
       </c>
       <c r="T12" s="1">
@@ -2083,52 +2075,52 @@
         <v>575</v>
       </c>
       <c r="Y12" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>646</v>
       </c>
       <c r="Z12" s="1">
         <f>SUM(O12:R12)</f>
-        <v>687.92000000000007</v>
+        <v>726.86000000000013</v>
       </c>
       <c r="AA12" s="1">
         <f>Z12*1.02</f>
-        <v>701.67840000000012</v>
+        <v>741.39720000000011</v>
       </c>
       <c r="AB12" s="1">
-        <f t="shared" ref="AB12:AJ12" si="19">AA12*1.02</f>
-        <v>715.71196800000018</v>
+        <f t="shared" ref="AB12:AJ12" si="17">AA12*1.02</f>
+        <v>756.22514400000011</v>
       </c>
       <c r="AC12" s="1">
-        <f t="shared" si="19"/>
-        <v>730.02620736000017</v>
+        <f t="shared" si="17"/>
+        <v>771.34964688000014</v>
       </c>
       <c r="AD12" s="1">
-        <f t="shared" si="19"/>
-        <v>744.62673150720013</v>
+        <f t="shared" si="17"/>
+        <v>786.7766398176002</v>
       </c>
       <c r="AE12" s="1">
-        <f t="shared" si="19"/>
-        <v>759.51926613734418</v>
+        <f t="shared" si="17"/>
+        <v>802.5121726139522</v>
       </c>
       <c r="AF12" s="1">
-        <f t="shared" si="19"/>
-        <v>774.7096514600911</v>
+        <f t="shared" si="17"/>
+        <v>818.56241606623121</v>
       </c>
       <c r="AG12" s="1">
-        <f t="shared" si="19"/>
-        <v>790.20384448929292</v>
+        <f t="shared" si="17"/>
+        <v>834.93366438755584</v>
       </c>
       <c r="AH12" s="1">
-        <f t="shared" si="19"/>
-        <v>806.00792137907877</v>
+        <f t="shared" si="17"/>
+        <v>851.63233767530699</v>
       </c>
       <c r="AI12" s="1">
-        <f t="shared" si="19"/>
-        <v>822.12807980666037</v>
+        <f t="shared" si="17"/>
+        <v>868.66498442881311</v>
       </c>
       <c r="AJ12" s="1">
-        <f t="shared" si="19"/>
-        <v>838.57064140279363</v>
+        <f t="shared" si="17"/>
+        <v>886.03828411738937</v>
       </c>
     </row>
     <row r="13" spans="1:36" x14ac:dyDescent="0.3">
@@ -2175,15 +2167,14 @@
         <v>-5</v>
       </c>
       <c r="P13" s="1">
-        <f t="shared" si="16"/>
-        <v>-9.18</v>
+        <v>-16</v>
       </c>
       <c r="Q13" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>-7.1400000000000006</v>
       </c>
       <c r="R13" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>-1.02</v>
       </c>
       <c r="T13" s="1">
@@ -2204,12 +2195,12 @@
         <v>7</v>
       </c>
       <c r="Y13" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>-20</v>
       </c>
       <c r="Z13" s="1">
         <f>SUM(O13:R13)</f>
-        <v>-22.34</v>
+        <v>-29.16</v>
       </c>
       <c r="AA13" s="1">
         <v>0</v>
@@ -2247,136 +2238,136 @@
         <v>25</v>
       </c>
       <c r="C14" s="1">
-        <f t="shared" ref="C14:N14" si="20">SUM(C10:C13)</f>
+        <f t="shared" ref="C14:N14" si="18">SUM(C10:C13)</f>
         <v>177</v>
       </c>
       <c r="D14" s="1">
+        <f t="shared" si="18"/>
+        <v>220</v>
+      </c>
+      <c r="E14" s="1">
+        <f t="shared" si="18"/>
+        <v>40</v>
+      </c>
+      <c r="F14" s="1">
+        <f t="shared" si="18"/>
+        <v>95</v>
+      </c>
+      <c r="G14" s="1">
+        <f t="shared" si="18"/>
+        <v>283</v>
+      </c>
+      <c r="H14" s="1">
+        <f t="shared" si="18"/>
+        <v>-48</v>
+      </c>
+      <c r="I14" s="1">
+        <f t="shared" si="18"/>
+        <v>83</v>
+      </c>
+      <c r="J14" s="1">
+        <f t="shared" si="18"/>
+        <v>51</v>
+      </c>
+      <c r="K14" s="1">
+        <f t="shared" si="18"/>
+        <v>46</v>
+      </c>
+      <c r="L14" s="1">
+        <f t="shared" si="18"/>
+        <v>97</v>
+      </c>
+      <c r="M14" s="1">
+        <f t="shared" si="18"/>
+        <v>138</v>
+      </c>
+      <c r="N14" s="1">
+        <f t="shared" si="18"/>
+        <v>47</v>
+      </c>
+      <c r="O14" s="1">
+        <f t="shared" ref="O14:R14" si="19">SUM(O10:O13)</f>
+        <v>118</v>
+      </c>
+      <c r="P14" s="1">
+        <f t="shared" si="19"/>
+        <v>105</v>
+      </c>
+      <c r="Q14" s="1">
+        <f t="shared" si="19"/>
+        <v>140.76</v>
+      </c>
+      <c r="R14" s="1">
+        <f t="shared" si="19"/>
+        <v>47.940000000000005</v>
+      </c>
+      <c r="T14" s="1">
+        <f t="shared" ref="T14:AJ14" si="20">SUM(T10:T13)</f>
+        <v>-67</v>
+      </c>
+      <c r="U14" s="1">
         <f t="shared" si="20"/>
-        <v>220</v>
-      </c>
-      <c r="E14" s="1">
+        <v>321</v>
+      </c>
+      <c r="V14" s="1">
         <f t="shared" si="20"/>
-        <v>40</v>
-      </c>
-      <c r="F14" s="1">
+        <v>-225</v>
+      </c>
+      <c r="W14" s="1">
         <f t="shared" si="20"/>
-        <v>95</v>
-      </c>
-      <c r="G14" s="1">
+        <v>532</v>
+      </c>
+      <c r="X14" s="1">
         <f t="shared" si="20"/>
-        <v>283</v>
-      </c>
-      <c r="H14" s="1">
+        <v>369</v>
+      </c>
+      <c r="Y14" s="1">
         <f t="shared" si="20"/>
-        <v>-48</v>
-      </c>
-      <c r="I14" s="1">
+        <v>328</v>
+      </c>
+      <c r="Z14" s="1">
         <f t="shared" si="20"/>
-        <v>83</v>
-      </c>
-      <c r="J14" s="1">
+        <v>411.7000000000001</v>
+      </c>
+      <c r="AA14" s="1">
         <f t="shared" si="20"/>
-        <v>51</v>
-      </c>
-      <c r="K14" s="1">
+        <v>437.95400000000012</v>
+      </c>
+      <c r="AB14" s="1">
         <f t="shared" si="20"/>
-        <v>46</v>
-      </c>
-      <c r="L14" s="1">
+        <v>442.47864800000013</v>
+      </c>
+      <c r="AC14" s="1">
         <f t="shared" si="20"/>
-        <v>97</v>
-      </c>
-      <c r="M14" s="1">
+        <v>446.99075600000015</v>
+      </c>
+      <c r="AD14" s="1">
         <f t="shared" si="20"/>
-        <v>138</v>
-      </c>
-      <c r="N14" s="1">
+        <v>451.4869822112002</v>
+      </c>
+      <c r="AE14" s="1">
         <f t="shared" si="20"/>
-        <v>47</v>
-      </c>
-      <c r="O14" s="1">
-        <f t="shared" ref="O14:R14" si="21">SUM(O10:O13)</f>
-        <v>118</v>
-      </c>
-      <c r="P14" s="1">
-        <f t="shared" si="21"/>
-        <v>98.94</v>
-      </c>
-      <c r="Q14" s="1">
-        <f t="shared" si="21"/>
-        <v>140.76</v>
-      </c>
-      <c r="R14" s="1">
-        <f t="shared" si="21"/>
-        <v>47.940000000000005</v>
-      </c>
-      <c r="T14" s="1">
-        <f t="shared" ref="T14:AJ14" si="22">SUM(T10:T13)</f>
-        <v>-67</v>
-      </c>
-      <c r="U14" s="1">
-        <f t="shared" si="22"/>
-        <v>321</v>
-      </c>
-      <c r="V14" s="1">
-        <f t="shared" si="22"/>
-        <v>-225</v>
-      </c>
-      <c r="W14" s="1">
-        <f t="shared" si="22"/>
-        <v>532</v>
-      </c>
-      <c r="X14" s="1">
-        <f t="shared" si="22"/>
-        <v>369</v>
-      </c>
-      <c r="Y14" s="1">
-        <f t="shared" si="22"/>
-        <v>328</v>
-      </c>
-      <c r="Z14" s="1">
-        <f t="shared" si="22"/>
-        <v>405.6400000000001</v>
-      </c>
-      <c r="AA14" s="1">
-        <f t="shared" si="22"/>
-        <v>407.29920000000016</v>
-      </c>
-      <c r="AB14" s="1">
-        <f t="shared" si="22"/>
-        <v>411.30139200000019</v>
-      </c>
-      <c r="AC14" s="1">
-        <f t="shared" si="22"/>
-        <v>415.2833140800002</v>
-      </c>
-      <c r="AD14" s="1">
-        <f t="shared" si="22"/>
-        <v>419.24155142880016</v>
-      </c>
-      <c r="AE14" s="1">
-        <f t="shared" si="22"/>
-        <v>423.17253065659219</v>
+        <v>455.96382527936021</v>
       </c>
       <c r="AF14" s="1">
-        <f t="shared" si="22"/>
-        <v>427.07251391491656</v>
+        <f t="shared" si="20"/>
+        <v>460.41761831160142</v>
       </c>
       <c r="AG14" s="1">
-        <f t="shared" si="22"/>
-        <v>430.93759281776312</v>
+        <f t="shared" si="20"/>
+        <v>464.84452270028714</v>
       </c>
       <c r="AH14" s="1">
-        <f t="shared" si="22"/>
-        <v>434.76368215740308</v>
+        <f t="shared" si="20"/>
+        <v>469.24052173742024</v>
       </c>
       <c r="AI14" s="1">
-        <f t="shared" si="22"/>
-        <v>438.54651340833442</v>
+        <f t="shared" si="20"/>
+        <v>473.60141401278975</v>
       </c>
       <c r="AJ14" s="1">
-        <f t="shared" si="22"/>
-        <v>442.2816280125179</v>
+        <f t="shared" si="20"/>
+        <v>477.92280658888529</v>
       </c>
     </row>
     <row r="15" spans="1:36" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -2385,136 +2376,136 @@
         <v>20</v>
       </c>
       <c r="C15" s="7">
-        <f t="shared" ref="C15:N15" si="23">C9-C14</f>
+        <f t="shared" ref="C15:N15" si="21">C9-C14</f>
         <v>2773</v>
       </c>
       <c r="D15" s="7">
+        <f t="shared" si="21"/>
+        <v>2798</v>
+      </c>
+      <c r="E15" s="7">
+        <f t="shared" si="21"/>
+        <v>3072</v>
+      </c>
+      <c r="F15" s="7">
+        <f t="shared" si="21"/>
+        <v>3089</v>
+      </c>
+      <c r="G15" s="7">
+        <f t="shared" si="21"/>
+        <v>2853</v>
+      </c>
+      <c r="H15" s="7">
+        <f t="shared" si="21"/>
+        <v>3704</v>
+      </c>
+      <c r="I15" s="7">
+        <f t="shared" si="21"/>
+        <v>3761</v>
+      </c>
+      <c r="J15" s="7">
+        <f t="shared" si="21"/>
+        <v>3321</v>
+      </c>
+      <c r="K15" s="7">
+        <f t="shared" si="21"/>
+        <v>3558</v>
+      </c>
+      <c r="L15" s="7">
+        <f t="shared" si="21"/>
+        <v>3939</v>
+      </c>
+      <c r="M15" s="7">
+        <f t="shared" si="21"/>
+        <v>3866</v>
+      </c>
+      <c r="N15" s="7">
+        <f t="shared" si="21"/>
+        <v>3891</v>
+      </c>
+      <c r="O15" s="7">
+        <f t="shared" ref="O15:R15" si="22">O9-O14</f>
+        <v>4031</v>
+      </c>
+      <c r="P15" s="7">
+        <f t="shared" si="22"/>
+        <v>4672</v>
+      </c>
+      <c r="Q15" s="7">
+        <f t="shared" si="22"/>
+        <v>4534.3793999999998</v>
+      </c>
+      <c r="R15" s="7">
+        <f t="shared" si="22"/>
+        <v>4358.9129999999996</v>
+      </c>
+      <c r="T15" s="7">
+        <f t="shared" ref="T15:AJ15" si="23">T9-T14</f>
+        <v>9731</v>
+      </c>
+      <c r="U15" s="7">
         <f t="shared" si="23"/>
-        <v>2798</v>
-      </c>
-      <c r="E15" s="7">
+        <v>7760</v>
+      </c>
+      <c r="V15" s="7">
         <f t="shared" si="23"/>
-        <v>3072</v>
-      </c>
-      <c r="F15" s="7">
+        <v>10307</v>
+      </c>
+      <c r="W15" s="7">
         <f t="shared" si="23"/>
-        <v>3089</v>
-      </c>
-      <c r="G15" s="7">
+        <v>11732</v>
+      </c>
+      <c r="X15" s="7">
         <f t="shared" si="23"/>
-        <v>2853</v>
-      </c>
-      <c r="H15" s="7">
+        <v>13639</v>
+      </c>
+      <c r="Y15" s="7">
         <f t="shared" si="23"/>
-        <v>3704</v>
-      </c>
-      <c r="I15" s="7">
+        <v>15254</v>
+      </c>
+      <c r="Z15" s="7">
         <f t="shared" si="23"/>
-        <v>3761</v>
-      </c>
-      <c r="J15" s="7">
+        <v>17596.292399999998</v>
+      </c>
+      <c r="AA15" s="7">
         <f t="shared" si="23"/>
-        <v>3321</v>
-      </c>
-      <c r="K15" s="7">
+        <v>21281.838639999998</v>
+      </c>
+      <c r="AB15" s="7">
         <f t="shared" si="23"/>
-        <v>3558</v>
-      </c>
-      <c r="L15" s="7">
+        <v>23626.671562560005</v>
+      </c>
+      <c r="AC15" s="7">
         <f t="shared" si="23"/>
-        <v>3939</v>
-      </c>
-      <c r="M15" s="7">
+        <v>25306.99996929921</v>
+      </c>
+      <c r="AD15" s="7">
         <f t="shared" si="23"/>
-        <v>3866</v>
-      </c>
-      <c r="N15" s="7">
+        <v>26590.203279352969</v>
+      </c>
+      <c r="AE15" s="7">
         <f t="shared" si="23"/>
-        <v>3891</v>
-      </c>
-      <c r="O15" s="7">
-        <f t="shared" ref="O15:R15" si="24">O9-O14</f>
-        <v>4031</v>
-      </c>
-      <c r="P15" s="7">
-        <f t="shared" si="24"/>
-        <v>4253.3888000000006</v>
-      </c>
-      <c r="Q15" s="7">
-        <f t="shared" si="24"/>
-        <v>4398.6424000000006</v>
-      </c>
-      <c r="R15" s="7">
-        <f t="shared" si="24"/>
-        <v>4233.425000000002</v>
-      </c>
-      <c r="T15" s="7">
-        <f t="shared" ref="T15:AJ15" si="25">T9-T14</f>
-        <v>9731</v>
-      </c>
-      <c r="U15" s="7">
-        <f t="shared" si="25"/>
-        <v>7760</v>
-      </c>
-      <c r="V15" s="7">
-        <f t="shared" si="25"/>
-        <v>10307</v>
-      </c>
-      <c r="W15" s="7">
-        <f t="shared" si="25"/>
-        <v>11732</v>
-      </c>
-      <c r="X15" s="7">
-        <f t="shared" si="25"/>
-        <v>13639</v>
-      </c>
-      <c r="Y15" s="7">
-        <f t="shared" si="25"/>
-        <v>15254</v>
-      </c>
-      <c r="Z15" s="7">
-        <f t="shared" si="25"/>
-        <v>16916.456199999997</v>
-      </c>
-      <c r="AA15" s="7">
-        <f t="shared" si="25"/>
-        <v>20060.5383</v>
-      </c>
-      <c r="AB15" s="7">
-        <f t="shared" si="25"/>
-        <v>21693.963108</v>
-      </c>
-      <c r="AC15" s="7">
-        <f t="shared" si="25"/>
-        <v>23016.29705592</v>
-      </c>
-      <c r="AD15" s="7">
-        <f t="shared" si="25"/>
-        <v>24183.917837071203</v>
-      </c>
-      <c r="AE15" s="7">
-        <f t="shared" si="25"/>
-        <v>25164.11323338341</v>
+        <v>27667.39404674738</v>
       </c>
       <c r="AF15" s="7">
-        <f t="shared" si="25"/>
-        <v>25927.831823046283</v>
+        <f t="shared" si="23"/>
+        <v>28506.640989875945</v>
       </c>
       <c r="AG15" s="7">
-        <f t="shared" si="25"/>
-        <v>26714.613874252274</v>
+        <f t="shared" si="23"/>
+        <v>29371.225843732882</v>
       </c>
       <c r="AH15" s="7">
-        <f t="shared" si="25"/>
-        <v>27525.154328924735</v>
+        <f t="shared" si="23"/>
+        <v>30261.911955688745</v>
       </c>
       <c r="AI15" s="7">
-        <f t="shared" si="25"/>
-        <v>28360.169038006265</v>
+        <f t="shared" si="23"/>
+        <v>31179.485637736165</v>
       </c>
       <c r="AJ15" s="7">
-        <f t="shared" si="25"/>
-        <v>29220.395389944519</v>
+        <f t="shared" si="23"/>
+        <v>32124.756856712538</v>
       </c>
     </row>
     <row r="16" spans="1:36" x14ac:dyDescent="0.3">
@@ -2561,16 +2552,15 @@
         <v>751</v>
       </c>
       <c r="P16" s="1">
-        <f t="shared" ref="P16:R16" si="26">P15*0.15</f>
-        <v>638.00832000000003</v>
+        <v>971</v>
       </c>
       <c r="Q16" s="1">
-        <f t="shared" si="26"/>
-        <v>659.79636000000005</v>
+        <f>Q15*0.18</f>
+        <v>816.18829199999993</v>
       </c>
       <c r="R16" s="1">
-        <f t="shared" si="26"/>
-        <v>635.0137500000003</v>
+        <f>R15*0.18</f>
+        <v>784.60433999999987</v>
       </c>
       <c r="T16" s="1">
         <v>1613</v>
@@ -2595,47 +2585,47 @@
       </c>
       <c r="Z16" s="1">
         <f>SUM(O16:R16)</f>
-        <v>2683.8184300000003</v>
+        <v>3322.7926319999997</v>
       </c>
       <c r="AA16" s="1">
-        <f t="shared" ref="AA16:AJ16" si="27">AA15*0.16</f>
-        <v>3209.6861280000003</v>
+        <f>AA15*0.18</f>
+        <v>3830.7309551999997</v>
       </c>
       <c r="AB16" s="1">
-        <f t="shared" si="27"/>
-        <v>3471.03409728</v>
+        <f t="shared" ref="AB16:AJ16" si="24">AB15*0.18</f>
+        <v>4252.8008812608005</v>
       </c>
       <c r="AC16" s="1">
-        <f t="shared" si="27"/>
-        <v>3682.6075289472001</v>
+        <f t="shared" si="24"/>
+        <v>4555.2599944738577</v>
       </c>
       <c r="AD16" s="1">
-        <f t="shared" si="27"/>
-        <v>3869.4268539313925</v>
+        <f t="shared" si="24"/>
+        <v>4786.2365902835345</v>
       </c>
       <c r="AE16" s="1">
-        <f t="shared" si="27"/>
-        <v>4026.258117341346</v>
+        <f t="shared" si="24"/>
+        <v>4980.1309284145282</v>
       </c>
       <c r="AF16" s="1">
-        <f t="shared" si="27"/>
-        <v>4148.4530916874055</v>
+        <f t="shared" si="24"/>
+        <v>5131.1953781776701</v>
       </c>
       <c r="AG16" s="1">
-        <f t="shared" si="27"/>
-        <v>4274.3382198803638</v>
+        <f t="shared" si="24"/>
+        <v>5286.8206518719189</v>
       </c>
       <c r="AH16" s="1">
-        <f t="shared" si="27"/>
-        <v>4404.0246926279578</v>
+        <f t="shared" si="24"/>
+        <v>5447.1441520239741</v>
       </c>
       <c r="AI16" s="1">
-        <f t="shared" si="27"/>
-        <v>4537.6270460810028</v>
+        <f t="shared" si="24"/>
+        <v>5612.307414792509</v>
       </c>
       <c r="AJ16" s="1">
-        <f t="shared" si="27"/>
-        <v>4675.2632623911231</v>
+        <f t="shared" si="24"/>
+        <v>5782.4562342082563</v>
       </c>
     </row>
     <row r="17" spans="1:146" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -2644,576 +2634,576 @@
         <v>22</v>
       </c>
       <c r="C17" s="7">
-        <f t="shared" ref="C17:L17" si="28">C15-C16</f>
+        <f t="shared" ref="C17:L17" si="25">C15-C16</f>
         <v>2631</v>
       </c>
       <c r="D17" s="7">
+        <f t="shared" si="25"/>
+        <v>2275</v>
+      </c>
+      <c r="E17" s="7">
+        <f t="shared" si="25"/>
+        <v>2499</v>
+      </c>
+      <c r="F17" s="7">
+        <f t="shared" si="25"/>
+        <v>2525</v>
+      </c>
+      <c r="G17" s="7">
+        <f t="shared" si="25"/>
+        <v>2361</v>
+      </c>
+      <c r="H17" s="7">
+        <f t="shared" si="25"/>
+        <v>2845</v>
+      </c>
+      <c r="I17" s="7">
+        <f t="shared" si="25"/>
+        <v>3198</v>
+      </c>
+      <c r="J17" s="7">
+        <f t="shared" si="25"/>
+        <v>2791</v>
+      </c>
+      <c r="K17" s="7">
+        <f t="shared" si="25"/>
+        <v>3011</v>
+      </c>
+      <c r="L17" s="7">
+        <f t="shared" si="25"/>
+        <v>3258</v>
+      </c>
+      <c r="M17" s="7">
+        <f t="shared" ref="M17:N17" si="26">M15-M16</f>
+        <v>3263</v>
+      </c>
+      <c r="N17" s="7">
+        <f t="shared" si="26"/>
+        <v>3342</v>
+      </c>
+      <c r="O17" s="7">
+        <f t="shared" ref="O17:R17" si="27">O15-O16</f>
+        <v>3280</v>
+      </c>
+      <c r="P17" s="7">
+        <f t="shared" si="27"/>
+        <v>3701</v>
+      </c>
+      <c r="Q17" s="7">
+        <f t="shared" si="27"/>
+        <v>3718.191108</v>
+      </c>
+      <c r="R17" s="7">
+        <f t="shared" si="27"/>
+        <v>3574.3086599999997</v>
+      </c>
+      <c r="T17" s="7">
+        <f t="shared" ref="T17:Z17" si="28">T15-T16</f>
+        <v>8118</v>
+      </c>
+      <c r="U17" s="7">
         <f t="shared" si="28"/>
-        <v>2275</v>
-      </c>
-      <c r="E17" s="7">
+        <v>6411</v>
+      </c>
+      <c r="V17" s="7">
         <f t="shared" si="28"/>
-        <v>2499</v>
-      </c>
-      <c r="F17" s="7">
+        <v>8687</v>
+      </c>
+      <c r="W17" s="7">
         <f t="shared" si="28"/>
-        <v>2525</v>
-      </c>
-      <c r="G17" s="7">
+        <v>9930</v>
+      </c>
+      <c r="X17" s="7">
         <f t="shared" si="28"/>
-        <v>2361</v>
-      </c>
-      <c r="H17" s="7">
+        <v>11195</v>
+      </c>
+      <c r="Y17" s="7">
         <f t="shared" si="28"/>
-        <v>2845</v>
-      </c>
-      <c r="I17" s="7">
+        <v>12874</v>
+      </c>
+      <c r="Z17" s="7">
         <f t="shared" si="28"/>
-        <v>3198</v>
-      </c>
-      <c r="J17" s="7">
-        <f t="shared" si="28"/>
-        <v>2791</v>
-      </c>
-      <c r="K17" s="7">
-        <f t="shared" si="28"/>
-        <v>3011</v>
-      </c>
-      <c r="L17" s="7">
-        <f t="shared" si="28"/>
-        <v>3258</v>
-      </c>
-      <c r="M17" s="7">
-        <f t="shared" ref="M17:N17" si="29">M15-M16</f>
-        <v>3263</v>
-      </c>
-      <c r="N17" s="7">
+        <v>14273.499767999998</v>
+      </c>
+      <c r="AA17" s="7">
+        <f t="shared" ref="AA17:AJ17" si="29">AA15-AA16</f>
+        <v>17451.107684799998</v>
+      </c>
+      <c r="AB17" s="7">
         <f t="shared" si="29"/>
-        <v>3342</v>
-      </c>
-      <c r="O17" s="7">
-        <f t="shared" ref="O17:R17" si="30">O15-O16</f>
-        <v>3280</v>
-      </c>
-      <c r="P17" s="7">
-        <f t="shared" si="30"/>
-        <v>3615.3804800000007</v>
-      </c>
-      <c r="Q17" s="7">
-        <f t="shared" si="30"/>
-        <v>3738.8460400000004</v>
-      </c>
-      <c r="R17" s="7">
-        <f t="shared" si="30"/>
-        <v>3598.4112500000019</v>
-      </c>
-      <c r="T17" s="7">
-        <f t="shared" ref="T17:Z17" si="31">T15-T16</f>
-        <v>8118</v>
-      </c>
-      <c r="U17" s="7">
-        <f t="shared" si="31"/>
-        <v>6411</v>
-      </c>
-      <c r="V17" s="7">
-        <f t="shared" si="31"/>
-        <v>8687</v>
-      </c>
-      <c r="W17" s="7">
-        <f t="shared" si="31"/>
-        <v>9930</v>
-      </c>
-      <c r="X17" s="7">
-        <f t="shared" si="31"/>
-        <v>11195</v>
-      </c>
-      <c r="Y17" s="7">
-        <f t="shared" si="31"/>
-        <v>12874</v>
-      </c>
-      <c r="Z17" s="7">
-        <f t="shared" si="31"/>
-        <v>14232.637769999998</v>
-      </c>
-      <c r="AA17" s="7">
-        <f t="shared" ref="AA17:AJ17" si="32">AA15-AA16</f>
-        <v>16850.852171999999</v>
-      </c>
-      <c r="AB17" s="7">
-        <f t="shared" si="32"/>
-        <v>18222.929010719999</v>
+        <v>19373.870681299202</v>
       </c>
       <c r="AC17" s="7">
-        <f t="shared" si="32"/>
-        <v>19333.689526972801</v>
+        <f t="shared" si="29"/>
+        <v>20751.739974825352</v>
       </c>
       <c r="AD17" s="7">
-        <f t="shared" si="32"/>
-        <v>20314.490983139811</v>
+        <f t="shared" si="29"/>
+        <v>21803.966689069435</v>
       </c>
       <c r="AE17" s="7">
-        <f t="shared" si="32"/>
-        <v>21137.855116042065</v>
+        <f t="shared" si="29"/>
+        <v>22687.263118332852</v>
       </c>
       <c r="AF17" s="7">
-        <f t="shared" si="32"/>
-        <v>21779.378731358876</v>
+        <f t="shared" si="29"/>
+        <v>23375.445611698276</v>
       </c>
       <c r="AG17" s="7">
-        <f t="shared" si="32"/>
-        <v>22440.275654371912</v>
+        <f t="shared" si="29"/>
+        <v>24084.405191860962</v>
       </c>
       <c r="AH17" s="7">
-        <f t="shared" si="32"/>
-        <v>23121.129636296777</v>
+        <f t="shared" si="29"/>
+        <v>24814.76780366477</v>
       </c>
       <c r="AI17" s="7">
-        <f t="shared" si="32"/>
-        <v>23822.54199192526</v>
+        <f t="shared" si="29"/>
+        <v>25567.178222943658</v>
       </c>
       <c r="AJ17" s="7">
-        <f t="shared" si="32"/>
-        <v>24545.132127553396</v>
+        <f t="shared" si="29"/>
+        <v>26342.300622504281</v>
       </c>
       <c r="AK17" s="6">
         <f>AJ17+(AJ17*$AM$23)</f>
-        <v>24299.680806277862</v>
+        <v>26078.877616279238</v>
       </c>
       <c r="AL17" s="6">
-        <f t="shared" ref="AL17:CW17" si="33">AK17+(AK17*$AM$23)</f>
-        <v>24056.683998215085</v>
+        <f t="shared" ref="AL17:CW17" si="30">AK17+(AK17*$AM$23)</f>
+        <v>25818.088840116445</v>
       </c>
       <c r="AM17" s="6">
-        <f t="shared" si="33"/>
-        <v>23816.117158232933</v>
+        <f t="shared" si="30"/>
+        <v>25559.907951715279</v>
       </c>
       <c r="AN17" s="6">
-        <f t="shared" si="33"/>
-        <v>23577.955986650602</v>
+        <f t="shared" si="30"/>
+        <v>25304.308872198126</v>
       </c>
       <c r="AO17" s="6">
-        <f t="shared" si="33"/>
-        <v>23342.176426784095</v>
+        <f t="shared" si="30"/>
+        <v>25051.265783476145</v>
       </c>
       <c r="AP17" s="6">
-        <f t="shared" si="33"/>
-        <v>23108.754662516254</v>
+        <f t="shared" si="30"/>
+        <v>24800.753125641382</v>
       </c>
       <c r="AQ17" s="6">
-        <f t="shared" si="33"/>
-        <v>22877.66711589109</v>
+        <f t="shared" si="30"/>
+        <v>24552.745594384967</v>
       </c>
       <c r="AR17" s="6">
-        <f t="shared" si="33"/>
-        <v>22648.89044473218</v>
+        <f t="shared" si="30"/>
+        <v>24307.218138441116</v>
       </c>
       <c r="AS17" s="6">
-        <f t="shared" si="33"/>
-        <v>22422.40154028486</v>
+        <f t="shared" si="30"/>
+        <v>24064.145957056706</v>
       </c>
       <c r="AT17" s="6">
-        <f t="shared" si="33"/>
-        <v>22198.177524882012</v>
+        <f t="shared" si="30"/>
+        <v>23823.504497486138</v>
       </c>
       <c r="AU17" s="6">
-        <f t="shared" si="33"/>
-        <v>21976.195749633192</v>
+        <f t="shared" si="30"/>
+        <v>23585.269452511275</v>
       </c>
       <c r="AV17" s="6">
-        <f t="shared" si="33"/>
-        <v>21756.433792136861</v>
+        <f t="shared" si="30"/>
+        <v>23349.416757986161</v>
       </c>
       <c r="AW17" s="6">
-        <f t="shared" si="33"/>
-        <v>21538.869454215492</v>
+        <f t="shared" si="30"/>
+        <v>23115.922590406299</v>
       </c>
       <c r="AX17" s="6">
-        <f t="shared" si="33"/>
-        <v>21323.480759673337</v>
+        <f t="shared" si="30"/>
+        <v>22884.763364502236</v>
       </c>
       <c r="AY17" s="6">
-        <f t="shared" si="33"/>
-        <v>21110.245952076602</v>
+        <f t="shared" si="30"/>
+        <v>22655.915730857214</v>
       </c>
       <c r="AZ17" s="6">
-        <f t="shared" si="33"/>
-        <v>20899.143492555835</v>
+        <f t="shared" si="30"/>
+        <v>22429.356573548641</v>
       </c>
       <c r="BA17" s="6">
-        <f t="shared" si="33"/>
-        <v>20690.152057630276</v>
+        <f t="shared" si="30"/>
+        <v>22205.063007813154</v>
       </c>
       <c r="BB17" s="6">
-        <f t="shared" si="33"/>
-        <v>20483.250537053973</v>
+        <f t="shared" si="30"/>
+        <v>21983.012377735024</v>
       </c>
       <c r="BC17" s="6">
-        <f t="shared" si="33"/>
-        <v>20278.418031683432</v>
+        <f t="shared" si="30"/>
+        <v>21763.182253957675</v>
       </c>
       <c r="BD17" s="6">
-        <f t="shared" si="33"/>
-        <v>20075.633851366598</v>
+        <f t="shared" si="30"/>
+        <v>21545.550431418098</v>
       </c>
       <c r="BE17" s="6">
-        <f t="shared" si="33"/>
-        <v>19874.877512852931</v>
+        <f t="shared" si="30"/>
+        <v>21330.094927103917</v>
       </c>
       <c r="BF17" s="6">
-        <f t="shared" si="33"/>
-        <v>19676.128737724401</v>
+        <f t="shared" si="30"/>
+        <v>21116.793977832876</v>
       </c>
       <c r="BG17" s="6">
-        <f t="shared" si="33"/>
-        <v>19479.367450347156</v>
+        <f t="shared" si="30"/>
+        <v>20905.626038054546</v>
       </c>
       <c r="BH17" s="6">
-        <f t="shared" si="33"/>
-        <v>19284.573775843684</v>
+        <f t="shared" si="30"/>
+        <v>20696.569777674002</v>
       </c>
       <c r="BI17" s="6">
-        <f t="shared" si="33"/>
-        <v>19091.728038085246</v>
+        <f t="shared" si="30"/>
+        <v>20489.604079897261</v>
       </c>
       <c r="BJ17" s="6">
-        <f t="shared" si="33"/>
-        <v>18900.810757704392</v>
+        <f t="shared" si="30"/>
+        <v>20284.708039098288</v>
       </c>
       <c r="BK17" s="6">
-        <f t="shared" si="33"/>
-        <v>18711.802650127349</v>
+        <f t="shared" si="30"/>
+        <v>20081.860958707304</v>
       </c>
       <c r="BL17" s="6">
-        <f t="shared" si="33"/>
-        <v>18524.684623626075</v>
+        <f t="shared" si="30"/>
+        <v>19881.042349120231</v>
       </c>
       <c r="BM17" s="6">
-        <f t="shared" si="33"/>
-        <v>18339.437777389816</v>
+        <f t="shared" si="30"/>
+        <v>19682.231925629028</v>
       </c>
       <c r="BN17" s="6">
-        <f t="shared" si="33"/>
-        <v>18156.043399615919</v>
+        <f t="shared" si="30"/>
+        <v>19485.409606372737</v>
       </c>
       <c r="BO17" s="6">
-        <f t="shared" si="33"/>
-        <v>17974.482965619762</v>
+        <f t="shared" si="30"/>
+        <v>19290.555510309012</v>
       </c>
       <c r="BP17" s="6">
-        <f t="shared" si="33"/>
-        <v>17794.738135963566</v>
+        <f t="shared" si="30"/>
+        <v>19097.649955205921</v>
       </c>
       <c r="BQ17" s="6">
-        <f t="shared" si="33"/>
-        <v>17616.790754603931</v>
+        <f t="shared" si="30"/>
+        <v>18906.673455653861</v>
       </c>
       <c r="BR17" s="6">
-        <f t="shared" si="33"/>
-        <v>17440.622847057894</v>
+        <f t="shared" si="30"/>
+        <v>18717.606721097323</v>
       </c>
       <c r="BS17" s="6">
-        <f t="shared" si="33"/>
-        <v>17266.216618587314</v>
+        <f t="shared" si="30"/>
+        <v>18530.430653886349</v>
       </c>
       <c r="BT17" s="6">
-        <f t="shared" si="33"/>
-        <v>17093.55445240144</v>
+        <f t="shared" si="30"/>
+        <v>18345.126347347486</v>
       </c>
       <c r="BU17" s="6">
-        <f t="shared" si="33"/>
-        <v>16922.618907877426</v>
+        <f t="shared" si="30"/>
+        <v>18161.675083874012</v>
       </c>
       <c r="BV17" s="6">
-        <f t="shared" si="33"/>
-        <v>16753.392718798652</v>
+        <f t="shared" si="30"/>
+        <v>17980.058333035271</v>
       </c>
       <c r="BW17" s="6">
-        <f t="shared" si="33"/>
-        <v>16585.858791610666</v>
+        <f t="shared" si="30"/>
+        <v>17800.257749704917</v>
       </c>
       <c r="BX17" s="6">
-        <f t="shared" si="33"/>
-        <v>16420.000203694559</v>
+        <f t="shared" si="30"/>
+        <v>17622.255172207868</v>
       </c>
       <c r="BY17" s="6">
-        <f t="shared" si="33"/>
-        <v>16255.800201657614</v>
+        <f t="shared" si="30"/>
+        <v>17446.032620485788</v>
       </c>
       <c r="BZ17" s="6">
-        <f t="shared" si="33"/>
-        <v>16093.242199641038</v>
+        <f t="shared" si="30"/>
+        <v>17271.57229428093</v>
       </c>
       <c r="CA17" s="6">
-        <f t="shared" si="33"/>
-        <v>15932.309777644627</v>
+        <f t="shared" si="30"/>
+        <v>17098.856571338121</v>
       </c>
       <c r="CB17" s="6">
-        <f t="shared" si="33"/>
-        <v>15772.98667986818</v>
+        <f t="shared" si="30"/>
+        <v>16927.868005624739</v>
       </c>
       <c r="CC17" s="6">
-        <f t="shared" si="33"/>
-        <v>15615.256813069498</v>
+        <f t="shared" si="30"/>
+        <v>16758.589325568493</v>
       </c>
       <c r="CD17" s="6">
-        <f t="shared" si="33"/>
-        <v>15459.104244938802</v>
+        <f t="shared" si="30"/>
+        <v>16591.003432312809</v>
       </c>
       <c r="CE17" s="6">
-        <f t="shared" si="33"/>
-        <v>15304.513202489414</v>
+        <f t="shared" si="30"/>
+        <v>16425.09339798968</v>
       </c>
       <c r="CF17" s="6">
-        <f t="shared" si="33"/>
-        <v>15151.46807046452</v>
+        <f t="shared" si="30"/>
+        <v>16260.842464009784</v>
       </c>
       <c r="CG17" s="6">
-        <f t="shared" si="33"/>
-        <v>14999.953389759874</v>
+        <f t="shared" si="30"/>
+        <v>16098.234039369687</v>
       </c>
       <c r="CH17" s="6">
-        <f t="shared" si="33"/>
-        <v>14849.953855862275</v>
+        <f t="shared" si="30"/>
+        <v>15937.25169897599</v>
       </c>
       <c r="CI17" s="6">
-        <f t="shared" si="33"/>
-        <v>14701.454317303653</v>
+        <f t="shared" si="30"/>
+        <v>15777.879181986229</v>
       </c>
       <c r="CJ17" s="6">
-        <f t="shared" si="33"/>
-        <v>14554.439774130617</v>
+        <f t="shared" si="30"/>
+        <v>15620.100390166366</v>
       </c>
       <c r="CK17" s="6">
-        <f t="shared" si="33"/>
-        <v>14408.89537638931</v>
+        <f t="shared" si="30"/>
+        <v>15463.899386264702</v>
       </c>
       <c r="CL17" s="6">
-        <f t="shared" si="33"/>
-        <v>14264.806422625417</v>
+        <f t="shared" si="30"/>
+        <v>15309.260392402055</v>
       </c>
       <c r="CM17" s="6">
-        <f t="shared" si="33"/>
-        <v>14122.158358399163</v>
+        <f t="shared" si="30"/>
+        <v>15156.167788478035</v>
       </c>
       <c r="CN17" s="6">
-        <f t="shared" si="33"/>
-        <v>13980.936774815171</v>
+        <f t="shared" si="30"/>
+        <v>15004.606110593255</v>
       </c>
       <c r="CO17" s="6">
-        <f t="shared" si="33"/>
-        <v>13841.127407067019</v>
+        <f t="shared" si="30"/>
+        <v>14854.560049487322</v>
       </c>
       <c r="CP17" s="6">
-        <f t="shared" si="33"/>
-        <v>13702.716132996349</v>
+        <f t="shared" si="30"/>
+        <v>14706.014448992448</v>
       </c>
       <c r="CQ17" s="6">
-        <f t="shared" si="33"/>
-        <v>13565.688971666386</v>
+        <f t="shared" si="30"/>
+        <v>14558.954304502524</v>
       </c>
       <c r="CR17" s="6">
-        <f t="shared" si="33"/>
-        <v>13430.032081949723</v>
+        <f t="shared" si="30"/>
+        <v>14413.364761457498</v>
       </c>
       <c r="CS17" s="6">
-        <f t="shared" si="33"/>
-        <v>13295.731761130226</v>
+        <f t="shared" si="30"/>
+        <v>14269.231113842923</v>
       </c>
       <c r="CT17" s="6">
-        <f t="shared" si="33"/>
-        <v>13162.774443518923</v>
+        <f t="shared" si="30"/>
+        <v>14126.538802704494</v>
       </c>
       <c r="CU17" s="6">
-        <f t="shared" si="33"/>
-        <v>13031.146699083734</v>
+        <f t="shared" si="30"/>
+        <v>13985.273414677449</v>
       </c>
       <c r="CV17" s="6">
-        <f t="shared" si="33"/>
-        <v>12900.835232092897</v>
+        <f t="shared" si="30"/>
+        <v>13845.420680530675</v>
       </c>
       <c r="CW17" s="6">
-        <f t="shared" si="33"/>
-        <v>12771.826879771968</v>
+        <f t="shared" si="30"/>
+        <v>13706.966473725368</v>
       </c>
       <c r="CX17" s="6">
-        <f t="shared" ref="CX17:EP17" si="34">CW17+(CW17*$AM$23)</f>
-        <v>12644.108610974248</v>
+        <f t="shared" ref="CX17:EP17" si="31">CW17+(CW17*$AM$23)</f>
+        <v>13569.896808988115</v>
       </c>
       <c r="CY17" s="6">
-        <f t="shared" si="34"/>
-        <v>12517.667524864506</v>
+        <f t="shared" si="31"/>
+        <v>13434.197840898234</v>
       </c>
       <c r="CZ17" s="6">
-        <f t="shared" si="34"/>
-        <v>12392.49084961586</v>
+        <f t="shared" si="31"/>
+        <v>13299.855862489252</v>
       </c>
       <c r="DA17" s="6">
-        <f t="shared" si="34"/>
-        <v>12268.565941119701</v>
+        <f t="shared" si="31"/>
+        <v>13166.857303864359</v>
       </c>
       <c r="DB17" s="6">
-        <f t="shared" si="34"/>
-        <v>12145.880281708503</v>
+        <f t="shared" si="31"/>
+        <v>13035.188730825716</v>
       </c>
       <c r="DC17" s="6">
-        <f t="shared" si="34"/>
-        <v>12024.421478891418</v>
+        <f t="shared" si="31"/>
+        <v>12904.836843517458</v>
       </c>
       <c r="DD17" s="6">
-        <f t="shared" si="34"/>
-        <v>11904.177264102504</v>
+        <f t="shared" si="31"/>
+        <v>12775.788475082283</v>
       </c>
       <c r="DE17" s="6">
-        <f t="shared" si="34"/>
-        <v>11785.135491461479</v>
+        <f t="shared" si="31"/>
+        <v>12648.03059033146</v>
       </c>
       <c r="DF17" s="6">
-        <f t="shared" si="34"/>
-        <v>11667.284136546863</v>
+        <f t="shared" si="31"/>
+        <v>12521.550284428145</v>
       </c>
       <c r="DG17" s="6">
-        <f t="shared" si="34"/>
-        <v>11550.611295181394</v>
+        <f t="shared" si="31"/>
+        <v>12396.334781583864</v>
       </c>
       <c r="DH17" s="6">
-        <f t="shared" si="34"/>
-        <v>11435.105182229579</v>
+        <f t="shared" si="31"/>
+        <v>12272.371433768025</v>
       </c>
       <c r="DI17" s="6">
-        <f t="shared" si="34"/>
-        <v>11320.754130407284</v>
+        <f t="shared" si="31"/>
+        <v>12149.647719430344</v>
       </c>
       <c r="DJ17" s="6">
-        <f t="shared" si="34"/>
-        <v>11207.546589103211</v>
+        <f t="shared" si="31"/>
+        <v>12028.151242236041</v>
       </c>
       <c r="DK17" s="6">
-        <f t="shared" si="34"/>
-        <v>11095.471123212179</v>
+        <f t="shared" si="31"/>
+        <v>11907.869729813681</v>
       </c>
       <c r="DL17" s="6">
-        <f t="shared" si="34"/>
-        <v>10984.516411980057</v>
+        <f t="shared" si="31"/>
+        <v>11788.791032515544</v>
       </c>
       <c r="DM17" s="6">
-        <f t="shared" si="34"/>
-        <v>10874.671247860257</v>
+        <f t="shared" si="31"/>
+        <v>11670.90312219039</v>
       </c>
       <c r="DN17" s="6">
-        <f t="shared" si="34"/>
-        <v>10765.924535381655</v>
+        <f t="shared" si="31"/>
+        <v>11554.194090968485</v>
       </c>
       <c r="DO17" s="6">
-        <f t="shared" si="34"/>
-        <v>10658.265290027839</v>
+        <f t="shared" si="31"/>
+        <v>11438.652150058801</v>
       </c>
       <c r="DP17" s="6">
-        <f t="shared" si="34"/>
-        <v>10551.68263712756</v>
+        <f t="shared" si="31"/>
+        <v>11324.265628558212</v>
       </c>
       <c r="DQ17" s="6">
-        <f t="shared" si="34"/>
-        <v>10446.165810756285</v>
+        <f t="shared" si="31"/>
+        <v>11211.022972272631</v>
       </c>
       <c r="DR17" s="6">
-        <f t="shared" si="34"/>
-        <v>10341.704152648723</v>
+        <f t="shared" si="31"/>
+        <v>11098.912742549905</v>
       </c>
       <c r="DS17" s="6">
-        <f t="shared" si="34"/>
-        <v>10238.287111122236</v>
+        <f t="shared" si="31"/>
+        <v>10987.923615124406</v>
       </c>
       <c r="DT17" s="6">
-        <f t="shared" si="34"/>
-        <v>10135.904240011014</v>
+        <f t="shared" si="31"/>
+        <v>10878.044378973162</v>
       </c>
       <c r="DU17" s="6">
-        <f t="shared" si="34"/>
-        <v>10034.545197610903</v>
+        <f t="shared" si="31"/>
+        <v>10769.26393518343</v>
       </c>
       <c r="DV17" s="6">
-        <f t="shared" si="34"/>
-        <v>9934.1997456347945</v>
+        <f t="shared" si="31"/>
+        <v>10661.571295831594</v>
       </c>
       <c r="DW17" s="6">
-        <f t="shared" si="34"/>
-        <v>9834.8577481784469</v>
+        <f t="shared" si="31"/>
+        <v>10554.955582873279</v>
       </c>
       <c r="DX17" s="6">
-        <f t="shared" si="34"/>
-        <v>9736.5091706966632</v>
+        <f t="shared" si="31"/>
+        <v>10449.406027044546</v>
       </c>
       <c r="DY17" s="6">
-        <f t="shared" si="34"/>
-        <v>9639.1440789896969</v>
+        <f t="shared" si="31"/>
+        <v>10344.911966774102</v>
       </c>
       <c r="DZ17" s="6">
-        <f t="shared" si="34"/>
-        <v>9542.7526381997995</v>
+        <f t="shared" si="31"/>
+        <v>10241.462847106361</v>
       </c>
       <c r="EA17" s="6">
-        <f t="shared" si="34"/>
-        <v>9447.3251118178014</v>
+        <f t="shared" si="31"/>
+        <v>10139.048218635297</v>
       </c>
       <c r="EB17" s="6">
-        <f t="shared" si="34"/>
-        <v>9352.851860699624</v>
+        <f t="shared" si="31"/>
+        <v>10037.657736448944</v>
       </c>
       <c r="EC17" s="6">
-        <f t="shared" si="34"/>
-        <v>9259.3233420926281</v>
+        <f t="shared" si="31"/>
+        <v>9937.281159084454</v>
       </c>
       <c r="ED17" s="6">
-        <f t="shared" si="34"/>
-        <v>9166.7301086717016</v>
+        <f t="shared" si="31"/>
+        <v>9837.9083474936087</v>
       </c>
       <c r="EE17" s="6">
-        <f t="shared" si="34"/>
-        <v>9075.0628075849854</v>
+        <f t="shared" si="31"/>
+        <v>9739.5292640186726</v>
       </c>
       <c r="EF17" s="6">
-        <f t="shared" si="34"/>
-        <v>8984.3121795091356</v>
+        <f t="shared" si="31"/>
+        <v>9642.1339713784855</v>
       </c>
       <c r="EG17" s="6">
-        <f t="shared" si="34"/>
-        <v>8894.4690577140445</v>
+        <f t="shared" si="31"/>
+        <v>9545.7126316647009</v>
       </c>
       <c r="EH17" s="6">
-        <f t="shared" si="34"/>
-        <v>8805.5243671369044</v>
+        <f t="shared" si="31"/>
+        <v>9450.2555053480537</v>
       </c>
       <c r="EI17" s="6">
-        <f t="shared" si="34"/>
-        <v>8717.4691234655347</v>
+        <f t="shared" si="31"/>
+        <v>9355.7529502945727</v>
       </c>
       <c r="EJ17" s="6">
-        <f t="shared" si="34"/>
-        <v>8630.2944322308795</v>
+        <f t="shared" si="31"/>
+        <v>9262.1954207916278</v>
       </c>
       <c r="EK17" s="6">
-        <f t="shared" si="34"/>
-        <v>8543.99148790857</v>
+        <f t="shared" si="31"/>
+        <v>9169.5734665837117</v>
       </c>
       <c r="EL17" s="6">
-        <f t="shared" si="34"/>
-        <v>8458.5515730294846</v>
+        <f t="shared" si="31"/>
+        <v>9077.8777319178753</v>
       </c>
       <c r="EM17" s="6">
-        <f t="shared" si="34"/>
-        <v>8373.9660572991907</v>
+        <f t="shared" si="31"/>
+        <v>8987.0989545986959</v>
       </c>
       <c r="EN17" s="6">
-        <f t="shared" si="34"/>
-        <v>8290.2263967261988</v>
+        <f t="shared" si="31"/>
+        <v>8897.2279650527089</v>
       </c>
       <c r="EO17" s="6">
-        <f t="shared" si="34"/>
-        <v>8207.3241327589367</v>
+        <f t="shared" si="31"/>
+        <v>8808.2556854021823</v>
       </c>
       <c r="EP17" s="6">
-        <f t="shared" si="34"/>
-        <v>8125.2508914313476</v>
+        <f t="shared" si="31"/>
+        <v>8720.1731285481601</v>
       </c>
     </row>
     <row r="18" spans="1:146" x14ac:dyDescent="0.3">
@@ -3221,43 +3211,43 @@
         <v>1</v>
       </c>
       <c r="C18" s="1">
-        <f t="shared" ref="C18:L18" si="35">922.5+7.1</f>
+        <f t="shared" ref="C18:L18" si="32">922.5+7.1</f>
         <v>929.6</v>
       </c>
       <c r="D18" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="32"/>
         <v>929.6</v>
       </c>
       <c r="E18" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="32"/>
         <v>929.6</v>
       </c>
       <c r="F18" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="32"/>
         <v>929.6</v>
       </c>
       <c r="G18" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="32"/>
         <v>929.6</v>
       </c>
       <c r="H18" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="32"/>
         <v>929.6</v>
       </c>
       <c r="I18" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="32"/>
         <v>929.6</v>
       </c>
       <c r="J18" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="32"/>
         <v>929.6</v>
       </c>
       <c r="K18" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="32"/>
         <v>929.6</v>
       </c>
       <c r="L18" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="32"/>
         <v>929.6</v>
       </c>
       <c r="M18" s="1">
@@ -3273,84 +3263,84 @@
         <v>908.09999999999991</v>
       </c>
       <c r="P18" s="1">
-        <f>901.3+6.8</f>
-        <v>908.09999999999991</v>
+        <f>897.3+6.7</f>
+        <v>904</v>
       </c>
       <c r="Q18" s="1">
-        <f>901.3+6.8</f>
-        <v>908.09999999999991</v>
+        <f>897.3+6.7</f>
+        <v>904</v>
       </c>
       <c r="R18" s="1">
-        <f>901.3+6.8</f>
-        <v>908.09999999999991</v>
+        <f>897.3+6.7</f>
+        <v>904</v>
       </c>
       <c r="T18" s="1">
-        <f t="shared" ref="T18:X18" si="36">922.5+7.1</f>
+        <f t="shared" ref="T18:X18" si="33">922.5+7.1</f>
         <v>929.6</v>
       </c>
       <c r="U18" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="33"/>
         <v>929.6</v>
       </c>
       <c r="V18" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="33"/>
         <v>929.6</v>
       </c>
       <c r="W18" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="33"/>
         <v>929.6</v>
       </c>
       <c r="X18" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="33"/>
         <v>929.6</v>
       </c>
       <c r="Y18" s="1">
-        <f t="shared" ref="Y18" si="37">904.9+6.8</f>
+        <f t="shared" ref="Y18" si="34">904.9+6.8</f>
         <v>911.69999999999993</v>
       </c>
       <c r="Z18" s="1">
-        <f t="shared" ref="Z18:AJ18" si="38">901.3+6.8</f>
-        <v>908.09999999999991</v>
+        <f t="shared" ref="Z18:AJ18" si="35">897.3+6.7</f>
+        <v>904</v>
       </c>
       <c r="AA18" s="1">
-        <f t="shared" si="38"/>
-        <v>908.09999999999991</v>
+        <f t="shared" si="35"/>
+        <v>904</v>
       </c>
       <c r="AB18" s="1">
-        <f t="shared" si="38"/>
-        <v>908.09999999999991</v>
+        <f t="shared" si="35"/>
+        <v>904</v>
       </c>
       <c r="AC18" s="1">
-        <f t="shared" si="38"/>
-        <v>908.09999999999991</v>
+        <f t="shared" si="35"/>
+        <v>904</v>
       </c>
       <c r="AD18" s="1">
-        <f t="shared" si="38"/>
-        <v>908.09999999999991</v>
+        <f t="shared" si="35"/>
+        <v>904</v>
       </c>
       <c r="AE18" s="1">
-        <f t="shared" si="38"/>
-        <v>908.09999999999991</v>
+        <f t="shared" si="35"/>
+        <v>904</v>
       </c>
       <c r="AF18" s="1">
-        <f t="shared" si="38"/>
-        <v>908.09999999999991</v>
+        <f t="shared" si="35"/>
+        <v>904</v>
       </c>
       <c r="AG18" s="1">
-        <f t="shared" si="38"/>
-        <v>908.09999999999991</v>
+        <f t="shared" si="35"/>
+        <v>904</v>
       </c>
       <c r="AH18" s="1">
-        <f t="shared" si="38"/>
-        <v>908.09999999999991</v>
+        <f t="shared" si="35"/>
+        <v>904</v>
       </c>
       <c r="AI18" s="1">
-        <f t="shared" si="38"/>
-        <v>908.09999999999991</v>
+        <f t="shared" si="35"/>
+        <v>904</v>
       </c>
       <c r="AJ18" s="1">
-        <f t="shared" si="38"/>
-        <v>908.09999999999991</v>
+        <f t="shared" si="35"/>
+        <v>904</v>
       </c>
     </row>
     <row r="19" spans="1:146" x14ac:dyDescent="0.3">
@@ -3358,136 +3348,136 @@
         <v>23</v>
       </c>
       <c r="C19" s="5">
-        <f t="shared" ref="C19:L19" si="39">C17/C18</f>
+        <f t="shared" ref="C19:L19" si="36">C17/C18</f>
         <v>2.830249569707401</v>
       </c>
       <c r="D19" s="5">
+        <f t="shared" si="36"/>
+        <v>2.447289156626506</v>
+      </c>
+      <c r="E19" s="5">
+        <f t="shared" si="36"/>
+        <v>2.6882530120481927</v>
+      </c>
+      <c r="F19" s="5">
+        <f t="shared" si="36"/>
+        <v>2.7162220309810672</v>
+      </c>
+      <c r="G19" s="5">
+        <f t="shared" si="36"/>
+        <v>2.5398020654044751</v>
+      </c>
+      <c r="H19" s="5">
+        <f t="shared" si="36"/>
+        <v>3.060456110154905</v>
+      </c>
+      <c r="I19" s="5">
+        <f t="shared" si="36"/>
+        <v>3.4401893287435454</v>
+      </c>
+      <c r="J19" s="5">
+        <f t="shared" si="36"/>
+        <v>3.0023666092943202</v>
+      </c>
+      <c r="K19" s="5">
+        <f t="shared" si="36"/>
+        <v>3.2390275387263339</v>
+      </c>
+      <c r="L19" s="5">
+        <f t="shared" si="36"/>
+        <v>3.5047332185886404</v>
+      </c>
+      <c r="M19" s="5">
+        <f t="shared" ref="M19:N19" si="37">M17/M18</f>
+        <v>3.554853469876893</v>
+      </c>
+      <c r="N19" s="5">
+        <f t="shared" si="37"/>
+        <v>3.6656794998354725</v>
+      </c>
+      <c r="O19" s="5">
+        <f t="shared" ref="O19:R19" si="38">O17/O18</f>
+        <v>3.6119370113423637</v>
+      </c>
+      <c r="P19" s="5">
+        <f t="shared" si="38"/>
+        <v>4.0940265486725664</v>
+      </c>
+      <c r="Q19" s="5">
+        <f t="shared" si="38"/>
+        <v>4.1130432610619465</v>
+      </c>
+      <c r="R19" s="5">
+        <f t="shared" si="38"/>
+        <v>3.9538812610619467</v>
+      </c>
+      <c r="T19" s="5">
+        <f t="shared" ref="T19:Z19" si="39">T17/T18</f>
+        <v>8.7327882960413081</v>
+      </c>
+      <c r="U19" s="5">
         <f t="shared" si="39"/>
-        <v>2.447289156626506</v>
-      </c>
-      <c r="E19" s="5">
+        <v>6.8965146299483644</v>
+      </c>
+      <c r="V19" s="5">
         <f t="shared" si="39"/>
-        <v>2.6882530120481927</v>
-      </c>
-      <c r="F19" s="5">
+        <v>9.3448795180722897</v>
+      </c>
+      <c r="W19" s="5">
         <f t="shared" si="39"/>
-        <v>2.7162220309810672</v>
-      </c>
-      <c r="G19" s="5">
+        <v>10.682013769363166</v>
+      </c>
+      <c r="X19" s="5">
         <f t="shared" si="39"/>
-        <v>2.5398020654044751</v>
-      </c>
-      <c r="H19" s="5">
+        <v>12.042814113597245</v>
+      </c>
+      <c r="Y19" s="5">
         <f t="shared" si="39"/>
-        <v>3.060456110154905</v>
-      </c>
-      <c r="I19" s="5">
+        <v>14.120873094219592</v>
+      </c>
+      <c r="Z19" s="5">
         <f t="shared" si="39"/>
-        <v>3.4401893287435454</v>
-      </c>
-      <c r="J19" s="5">
-        <f t="shared" si="39"/>
-        <v>3.0023666092943202</v>
-      </c>
-      <c r="K19" s="5">
-        <f t="shared" si="39"/>
-        <v>3.2390275387263339</v>
-      </c>
-      <c r="L19" s="5">
-        <f t="shared" si="39"/>
-        <v>3.5047332185886404</v>
-      </c>
-      <c r="M19" s="5">
-        <f t="shared" ref="M19:N19" si="40">M17/M18</f>
-        <v>3.554853469876893</v>
-      </c>
-      <c r="N19" s="5">
+        <v>15.789269654867255</v>
+      </c>
+      <c r="AA19" s="5">
+        <f t="shared" ref="AA19:AJ19" si="40">AA17/AA18</f>
+        <v>19.30432266017699</v>
+      </c>
+      <c r="AB19" s="5">
         <f t="shared" si="40"/>
-        <v>3.6656794998354725</v>
-      </c>
-      <c r="O19" s="5">
-        <f t="shared" ref="O19:R19" si="41">O17/O18</f>
-        <v>3.6119370113423637</v>
-      </c>
-      <c r="P19" s="5">
-        <f t="shared" si="41"/>
-        <v>3.9812580993282691</v>
-      </c>
-      <c r="Q19" s="5">
-        <f t="shared" si="41"/>
-        <v>4.117218412069156</v>
-      </c>
-      <c r="R19" s="5">
-        <f t="shared" si="41"/>
-        <v>3.9625715780200443</v>
-      </c>
-      <c r="T19" s="5">
-        <f t="shared" ref="T19:Z19" si="42">T17/T18</f>
-        <v>8.7327882960413081</v>
-      </c>
-      <c r="U19" s="5">
-        <f t="shared" si="42"/>
-        <v>6.8965146299483644</v>
-      </c>
-      <c r="V19" s="5">
-        <f t="shared" si="42"/>
-        <v>9.3448795180722897</v>
-      </c>
-      <c r="W19" s="5">
-        <f t="shared" si="42"/>
-        <v>10.682013769363166</v>
-      </c>
-      <c r="X19" s="5">
-        <f t="shared" si="42"/>
-        <v>12.042814113597245</v>
-      </c>
-      <c r="Y19" s="5">
-        <f t="shared" si="42"/>
-        <v>14.120873094219592</v>
-      </c>
-      <c r="Z19" s="5">
-        <f t="shared" si="42"/>
-        <v>15.672985100759828</v>
-      </c>
-      <c r="AA19" s="5">
-        <f t="shared" ref="AA19:AJ19" si="43">AA17/AA18</f>
-        <v>18.556163607532209</v>
-      </c>
-      <c r="AB19" s="5">
-        <f t="shared" si="43"/>
-        <v>20.067095045391479</v>
+        <v>21.431272877543364</v>
       </c>
       <c r="AC19" s="5">
-        <f t="shared" si="43"/>
-        <v>21.290264868376614</v>
+        <f t="shared" si="40"/>
+        <v>22.955464573921848</v>
       </c>
       <c r="AD19" s="5">
-        <f t="shared" si="43"/>
-        <v>22.370323734324206</v>
+        <f t="shared" si="40"/>
+        <v>24.119432178174154</v>
       </c>
       <c r="AE19" s="5">
-        <f t="shared" si="43"/>
-        <v>23.277012571349044</v>
+        <f t="shared" si="40"/>
+        <v>25.096529998155809</v>
       </c>
       <c r="AF19" s="5">
-        <f t="shared" si="43"/>
-        <v>23.983458574340798</v>
+        <f t="shared" si="40"/>
+        <v>25.857793818250308</v>
       </c>
       <c r="AG19" s="5">
-        <f t="shared" si="43"/>
-        <v>24.711238469741122</v>
+        <f t="shared" si="40"/>
+        <v>26.642041141439119</v>
       </c>
       <c r="AH19" s="5">
-        <f t="shared" si="43"/>
-        <v>25.460995084568637</v>
+        <f t="shared" si="40"/>
+        <v>27.449964384584923</v>
       </c>
       <c r="AI19" s="5">
-        <f t="shared" si="43"/>
-        <v>26.233390586857464</v>
+        <f t="shared" si="40"/>
+        <v>28.282276795291658</v>
       </c>
       <c r="AJ19" s="5">
-        <f t="shared" si="43"/>
-        <v>27.029107067011779</v>
+        <f t="shared" si="40"/>
+        <v>29.139713077991463</v>
       </c>
     </row>
     <row r="21" spans="1:146" x14ac:dyDescent="0.3">
@@ -3503,48 +3493,48 @@
         <v>0.11244435842848843</v>
       </c>
       <c r="H21" s="8">
-        <f t="shared" ref="H21:N21" si="44">H3/D3-1</f>
+        <f t="shared" ref="H21:N21" si="41">H3/D3-1</f>
         <v>0.14044024013098055</v>
       </c>
       <c r="I21" s="8">
-        <f t="shared" si="44"/>
+        <f t="shared" si="41"/>
         <v>0.13498957609451012</v>
       </c>
       <c r="J21" s="8">
-        <f t="shared" si="44"/>
+        <f t="shared" si="41"/>
         <v>0.12566615093690903</v>
       </c>
       <c r="K21" s="8">
-        <f t="shared" si="44"/>
+        <f t="shared" si="41"/>
         <v>0.10438413361169108</v>
       </c>
       <c r="L21" s="8">
-        <f t="shared" si="44"/>
+        <f t="shared" si="41"/>
         <v>0.11038443132876052</v>
       </c>
       <c r="M21" s="8">
-        <f t="shared" si="44"/>
+        <f t="shared" si="41"/>
         <v>0.1279657125363538</v>
       </c>
       <c r="N21" s="8">
-        <f t="shared" si="44"/>
+        <f t="shared" si="41"/>
         <v>0.14370800244349424</v>
       </c>
       <c r="O21" s="8">
-        <f t="shared" ref="O21" si="45">O3/K3-1</f>
+        <f t="shared" ref="O21" si="42">O3/K3-1</f>
         <v>0.14209199747952117</v>
       </c>
       <c r="P21" s="8">
-        <f t="shared" ref="P21" si="46">P3/L3-1</f>
-        <v>0.12000000000000011</v>
+        <f t="shared" ref="P21" si="43">P3/L3-1</f>
+        <v>0.1683666139922424</v>
       </c>
       <c r="Q21" s="8">
-        <f t="shared" ref="Q21" si="47">Q3/M3-1</f>
-        <v>0.12000000000000011</v>
+        <f t="shared" ref="Q21" si="44">Q3/M3-1</f>
+        <v>0.1399999999999999</v>
       </c>
       <c r="R21" s="8">
-        <f t="shared" ref="R21" si="48">R3/N3-1</f>
-        <v>0.10000000000000009</v>
+        <f t="shared" ref="R21" si="45">R3/N3-1</f>
+        <v>0.1399999999999999</v>
       </c>
       <c r="T21" s="8"/>
       <c r="U21" s="8">
@@ -3552,63 +3542,63 @@
         <v>-9.3703725641177571E-2</v>
       </c>
       <c r="V21" s="8">
-        <f t="shared" ref="V21:AJ21" si="49">V3/U3-1</f>
+        <f t="shared" ref="V21:AJ21" si="46">V3/U3-1</f>
         <v>0.23416770145742105</v>
       </c>
       <c r="W21" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="46"/>
         <v>0.17755772082185972</v>
       </c>
       <c r="X21" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="46"/>
         <v>0.1286594414714215</v>
       </c>
       <c r="Y21" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="46"/>
         <v>0.12228065981353087</v>
       </c>
       <c r="Z21" s="8">
-        <f t="shared" si="49"/>
-        <v>0.11966130578336354</v>
+        <f t="shared" si="46"/>
+        <v>0.14748180494905383</v>
       </c>
       <c r="AA21" s="8">
-        <f t="shared" si="49"/>
-        <v>0.10000000000000009</v>
+        <f t="shared" si="46"/>
+        <v>0.12000000000000011</v>
       </c>
       <c r="AB21" s="8">
-        <f t="shared" si="49"/>
-        <v>8.0000000000000071E-2</v>
+        <f t="shared" si="46"/>
+        <v>9.000000000000008E-2</v>
       </c>
       <c r="AC21" s="8">
-        <f t="shared" si="49"/>
-        <v>6.0000000000000053E-2</v>
+        <f t="shared" si="46"/>
+        <v>7.0000000000000062E-2</v>
       </c>
       <c r="AD21" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="46"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AE21" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="46"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AF21" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="46"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AG21" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="46"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AH21" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="46"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AI21" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="46"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AJ21" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="46"/>
         <v>3.0000000000000027E-2</v>
       </c>
     </row>
@@ -3617,19 +3607,19 @@
         <v>39</v>
       </c>
       <c r="C22" s="8">
-        <f t="shared" ref="C22:F22" si="50">C5/C3</f>
+        <f t="shared" ref="C22:F22" si="47">C5/C3</f>
         <v>0.64311979872266301</v>
       </c>
       <c r="D22" s="8">
-        <f t="shared" si="50"/>
+        <f t="shared" si="47"/>
         <v>0.64580680371111521</v>
       </c>
       <c r="E22" s="8">
-        <f t="shared" si="50"/>
+        <f t="shared" si="47"/>
         <v>0.64054899235580265</v>
       </c>
       <c r="F22" s="8">
-        <f t="shared" si="50"/>
+        <f t="shared" si="47"/>
         <v>0.61870379920921437</v>
       </c>
       <c r="G22" s="8">
@@ -3637,116 +3627,116 @@
         <v>0.64457202505219202</v>
       </c>
       <c r="H22" s="8">
-        <f t="shared" ref="H22:N22" si="51">H5/H3</f>
+        <f t="shared" ref="H22:N22" si="48">H5/H3</f>
         <v>0.64906683681607913</v>
       </c>
       <c r="I22" s="8">
-        <f t="shared" si="51"/>
+        <f t="shared" si="48"/>
         <v>0.65023725700290835</v>
       </c>
       <c r="J22" s="8">
-        <f t="shared" si="51"/>
+        <f t="shared" si="48"/>
         <v>0.63362858888210138</v>
       </c>
       <c r="K22" s="8">
-        <f t="shared" si="51"/>
+        <f t="shared" si="48"/>
         <v>0.63988657844990549</v>
       </c>
       <c r="L22" s="8">
-        <f t="shared" si="51"/>
+        <f t="shared" si="48"/>
         <v>0.65263611550064649</v>
       </c>
       <c r="M22" s="8">
-        <f t="shared" si="51"/>
+        <f t="shared" si="48"/>
         <v>0.62762925770118061</v>
       </c>
       <c r="N22" s="8">
-        <f t="shared" si="51"/>
+        <f t="shared" si="48"/>
         <v>0.63346241153692084</v>
       </c>
       <c r="O22" s="8">
-        <f t="shared" ref="O22:R22" si="52">O5/O3</f>
+        <f t="shared" ref="O22:R22" si="49">O5/O3</f>
         <v>0.65200000000000002</v>
       </c>
       <c r="P22" s="8">
-        <f t="shared" si="52"/>
-        <v>0.64000000000000012</v>
+        <f t="shared" si="49"/>
+        <v>0.65990409443009956</v>
       </c>
       <c r="Q22" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="49"/>
+        <v>0.64</v>
+      </c>
+      <c r="R22" s="8">
+        <f t="shared" si="49"/>
         <v>0.63</v>
       </c>
-      <c r="R22" s="8">
-        <f t="shared" si="52"/>
-        <v>0.63</v>
-      </c>
       <c r="T22" s="8">
-        <f t="shared" ref="T22:AJ22" si="53">T5/T3</f>
+        <f t="shared" ref="T22:AJ22" si="50">T5/T3</f>
         <v>0.65865071373571049</v>
       </c>
       <c r="U22" s="8">
-        <f t="shared" si="53"/>
+        <f t="shared" si="50"/>
         <v>0.61375073524606238</v>
       </c>
       <c r="V22" s="8">
-        <f t="shared" si="53"/>
+        <f t="shared" si="50"/>
         <v>0.62470874814657906</v>
       </c>
       <c r="W22" s="8">
-        <f t="shared" si="53"/>
+        <f t="shared" si="50"/>
         <v>0.63673157350362009</v>
       </c>
       <c r="X22" s="8">
-        <f t="shared" si="53"/>
+        <f t="shared" si="50"/>
         <v>0.64431428799107504</v>
       </c>
       <c r="Y22" s="8">
-        <f t="shared" si="53"/>
+        <f t="shared" si="50"/>
         <v>0.63812262576774237</v>
       </c>
       <c r="Z22" s="8">
-        <f t="shared" si="53"/>
-        <v>0.63752955053507721</v>
+        <f t="shared" si="50"/>
+        <v>0.64505877890370134</v>
       </c>
       <c r="AA22" s="8">
-        <f t="shared" si="53"/>
-        <v>0.64</v>
+        <f t="shared" si="50"/>
+        <v>0.65</v>
       </c>
       <c r="AB22" s="8">
-        <f t="shared" si="53"/>
-        <v>0.64</v>
+        <f t="shared" si="50"/>
+        <v>0.66</v>
       </c>
       <c r="AC22" s="8">
-        <f t="shared" si="53"/>
-        <v>0.64</v>
+        <f t="shared" si="50"/>
+        <v>0.66</v>
       </c>
       <c r="AD22" s="8">
-        <f t="shared" si="53"/>
-        <v>0.64</v>
+        <f t="shared" si="50"/>
+        <v>0.66</v>
       </c>
       <c r="AE22" s="8">
-        <f t="shared" si="53"/>
-        <v>0.64</v>
+        <f t="shared" si="50"/>
+        <v>0.66</v>
       </c>
       <c r="AF22" s="8">
-        <f t="shared" si="53"/>
-        <v>0.64</v>
+        <f t="shared" si="50"/>
+        <v>0.66</v>
       </c>
       <c r="AG22" s="8">
-        <f t="shared" si="53"/>
-        <v>0.64</v>
+        <f t="shared" si="50"/>
+        <v>0.66</v>
       </c>
       <c r="AH22" s="8">
-        <f t="shared" si="53"/>
-        <v>0.64</v>
+        <f t="shared" si="50"/>
+        <v>0.66000000000000014</v>
       </c>
       <c r="AI22" s="8">
-        <f t="shared" si="53"/>
-        <v>0.64</v>
+        <f t="shared" si="50"/>
+        <v>0.66</v>
       </c>
       <c r="AJ22" s="8">
-        <f t="shared" si="53"/>
-        <v>0.64</v>
+        <f t="shared" si="50"/>
+        <v>0.66000000000000014</v>
       </c>
     </row>
     <row r="23" spans="1:146" x14ac:dyDescent="0.3">
@@ -3754,19 +3744,19 @@
         <v>40</v>
       </c>
       <c r="C23" s="8">
-        <f t="shared" ref="C23:F23" si="54">C6/C3</f>
+        <f t="shared" ref="C23:F23" si="51">C6/C3</f>
         <v>3.5029998064640994E-2</v>
       </c>
       <c r="D23" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="51"/>
         <v>3.8202655994178644E-2</v>
       </c>
       <c r="E23" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="51"/>
         <v>3.1619179986101462E-2</v>
       </c>
       <c r="F23" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="51"/>
         <v>3.7132542547705004E-2</v>
       </c>
       <c r="G23" s="8">
@@ -3774,116 +3764,116 @@
         <v>2.9053583855254E-2</v>
       </c>
       <c r="H23" s="8">
-        <f t="shared" ref="H23:N23" si="55">H6/H3</f>
+        <f t="shared" ref="H23:N23" si="52">H6/H3</f>
         <v>3.2062529909076411E-2</v>
       </c>
       <c r="I23" s="8">
-        <f t="shared" si="55"/>
+        <f t="shared" si="52"/>
         <v>2.9542323587938159E-2</v>
       </c>
       <c r="J23" s="8">
-        <f t="shared" si="55"/>
+        <f t="shared" si="52"/>
         <v>4.0317654245571169E-2</v>
       </c>
       <c r="K23" s="8">
-        <f t="shared" si="55"/>
+        <f t="shared" si="52"/>
         <v>1.8273471959672338E-2</v>
       </c>
       <c r="L23" s="8">
-        <f t="shared" si="55"/>
+        <f t="shared" si="52"/>
         <v>2.6432983766700186E-2</v>
       </c>
       <c r="M23" s="8">
-        <f t="shared" si="55"/>
+        <f t="shared" si="52"/>
         <v>2.9854797123083185E-2</v>
       </c>
       <c r="N23" s="8">
-        <f t="shared" si="55"/>
+        <f t="shared" si="52"/>
         <v>3.9391106956870078E-2</v>
       </c>
       <c r="O23" s="8">
-        <f t="shared" ref="O23:R23" si="56">O6/O3</f>
+        <f t="shared" ref="O23:R23" si="53">O6/O3</f>
         <v>2.0965517241379312E-2</v>
       </c>
       <c r="P23" s="8">
-        <f t="shared" si="56"/>
+        <f t="shared" si="53"/>
+        <v>2.6189597934341571E-2</v>
+      </c>
+      <c r="Q23" s="8">
+        <f t="shared" si="53"/>
         <v>0.03</v>
       </c>
-      <c r="Q23" s="8">
-        <f t="shared" si="56"/>
+      <c r="R23" s="8">
+        <f t="shared" si="53"/>
+        <v>0.04</v>
+      </c>
+      <c r="T23" s="8">
+        <f t="shared" ref="T23:AJ23" si="54">T6/T3</f>
+        <v>5.5321921459456261E-2</v>
+      </c>
+      <c r="U23" s="8">
+        <f t="shared" si="54"/>
+        <v>4.2938370041173776E-2</v>
+      </c>
+      <c r="V23" s="8">
+        <f t="shared" si="54"/>
+        <v>4.7394619783944082E-2</v>
+      </c>
+      <c r="W23" s="8">
+        <f t="shared" si="54"/>
+        <v>3.5481404865764267E-2</v>
+      </c>
+      <c r="X23" s="8">
+        <f t="shared" si="54"/>
+        <v>3.2871145111164235E-2</v>
+      </c>
+      <c r="Y23" s="8">
+        <f t="shared" si="54"/>
+        <v>2.893456882167075E-2</v>
+      </c>
+      <c r="Z23" s="8">
+        <f t="shared" si="54"/>
+        <v>2.9656094838297682E-2</v>
+      </c>
+      <c r="AA23" s="8">
+        <f t="shared" si="54"/>
+        <v>3.0000000000000002E-2</v>
+      </c>
+      <c r="AB23" s="8">
+        <f t="shared" si="54"/>
         <v>0.03</v>
       </c>
-      <c r="R23" s="8">
-        <f t="shared" si="56"/>
-        <v>0.04</v>
-      </c>
-      <c r="T23" s="8">
-        <f t="shared" ref="T23:AJ23" si="57">T6/T3</f>
-        <v>5.5321921459456261E-2</v>
-      </c>
-      <c r="U23" s="8">
-        <f t="shared" si="57"/>
-        <v>4.2938370041173776E-2</v>
-      </c>
-      <c r="V23" s="8">
-        <f t="shared" si="57"/>
-        <v>4.7394619783944082E-2</v>
-      </c>
-      <c r="W23" s="8">
-        <f t="shared" si="57"/>
-        <v>3.5481404865764267E-2</v>
-      </c>
-      <c r="X23" s="8">
-        <f t="shared" si="57"/>
-        <v>3.2871145111164235E-2</v>
-      </c>
-      <c r="Y23" s="8">
-        <f t="shared" si="57"/>
-        <v>2.893456882167075E-2</v>
-      </c>
-      <c r="Z23" s="8">
-        <f t="shared" si="57"/>
-        <v>3.0535204122076894E-2</v>
-      </c>
-      <c r="AA23" s="8">
-        <f t="shared" si="57"/>
+      <c r="AC23" s="8">
+        <f t="shared" si="54"/>
         <v>0.03</v>
       </c>
-      <c r="AB23" s="8">
-        <f t="shared" si="57"/>
+      <c r="AD23" s="8">
+        <f t="shared" si="54"/>
+        <v>0.03</v>
+      </c>
+      <c r="AE23" s="8">
+        <f t="shared" si="54"/>
         <v>2.9999999999999995E-2</v>
       </c>
-      <c r="AC23" s="8">
-        <f t="shared" si="57"/>
+      <c r="AF23" s="8">
+        <f t="shared" si="54"/>
+        <v>2.9999999999999995E-2</v>
+      </c>
+      <c r="AG23" s="8">
+        <f t="shared" si="54"/>
         <v>0.03</v>
       </c>
-      <c r="AD23" s="8">
-        <f t="shared" si="57"/>
+      <c r="AH23" s="8">
+        <f t="shared" si="54"/>
+        <v>0.03</v>
+      </c>
+      <c r="AI23" s="8">
+        <f t="shared" si="54"/>
         <v>3.0000000000000002E-2</v>
       </c>
-      <c r="AE23" s="8">
-        <f t="shared" si="57"/>
-        <v>2.9999999999999995E-2</v>
-      </c>
-      <c r="AF23" s="8">
-        <f t="shared" si="57"/>
-        <v>0.03</v>
-      </c>
-      <c r="AG23" s="8">
-        <f t="shared" si="57"/>
-        <v>0.03</v>
-      </c>
-      <c r="AH23" s="8">
-        <f t="shared" si="57"/>
-        <v>0.03</v>
-      </c>
-      <c r="AI23" s="8">
-        <f t="shared" si="57"/>
-        <v>0.03</v>
-      </c>
       <c r="AJ23" s="8">
-        <f t="shared" si="57"/>
-        <v>0.03</v>
+        <f t="shared" si="54"/>
+        <v>3.0000000000000002E-2</v>
       </c>
       <c r="AL23" t="s">
         <v>46</v>
@@ -3905,48 +3895,48 @@
         <v>-5.2083333333333703E-3</v>
       </c>
       <c r="H24" s="8">
-        <f t="shared" ref="H24:N24" si="58">H7/D7-1</f>
+        <f t="shared" ref="H24:N24" si="55">H7/D7-1</f>
         <v>1.5873015873015817E-2</v>
       </c>
       <c r="I24" s="8">
-        <f t="shared" si="58"/>
+        <f t="shared" si="55"/>
         <v>0.14054054054054044</v>
       </c>
       <c r="J24" s="8">
-        <f t="shared" si="58"/>
+        <f t="shared" si="55"/>
         <v>0.11413043478260865</v>
       </c>
       <c r="K24" s="8">
-        <f t="shared" si="58"/>
+        <f t="shared" si="55"/>
         <v>0.13089005235602102</v>
       </c>
       <c r="L24" s="8">
-        <f t="shared" si="58"/>
+        <f t="shared" si="55"/>
         <v>0.171875</v>
       </c>
       <c r="M24" s="8">
-        <f t="shared" si="58"/>
+        <f t="shared" si="55"/>
         <v>6.6350710900473953E-2</v>
       </c>
       <c r="N24" s="8">
-        <f t="shared" si="58"/>
+        <f t="shared" si="55"/>
         <v>0.12682926829268282</v>
       </c>
       <c r="O24" s="8">
-        <f t="shared" ref="O24" si="59">O7/K7-1</f>
+        <f t="shared" ref="O24" si="56">O7/K7-1</f>
         <v>0.27314814814814814</v>
       </c>
       <c r="P24" s="8">
-        <f t="shared" ref="P24" si="60">P7/L7-1</f>
-        <v>0.10000000000000009</v>
+        <f t="shared" ref="P24" si="57">P7/L7-1</f>
+        <v>0.24888888888888894</v>
       </c>
       <c r="Q24" s="8">
-        <f t="shared" ref="Q24" si="61">Q7/M7-1</f>
-        <v>0.10000000000000009</v>
+        <f t="shared" ref="Q24" si="58">Q7/M7-1</f>
+        <v>0.25</v>
       </c>
       <c r="R24" s="8">
-        <f t="shared" ref="R24" si="62">R7/N7-1</f>
-        <v>8.0000000000000071E-2</v>
+        <f t="shared" ref="R24" si="59">R7/N7-1</f>
+        <v>0.25</v>
       </c>
       <c r="T24" s="8"/>
       <c r="U24" s="8">
@@ -3954,63 +3944,63 @@
         <v>0.11111111111111116</v>
       </c>
       <c r="V24" s="8">
-        <f t="shared" ref="V24:AJ24" si="63">V7/U7-1</f>
+        <f t="shared" ref="V24:AJ24" si="60">V7/U7-1</f>
         <v>0.25172413793103443</v>
       </c>
       <c r="W24" s="8">
-        <f t="shared" si="63"/>
+        <f t="shared" si="60"/>
         <v>3.3057851239669311E-2</v>
       </c>
       <c r="X24" s="8">
-        <f t="shared" si="63"/>
+        <f t="shared" si="60"/>
         <v>6.5333333333333243E-2</v>
       </c>
       <c r="Y24" s="8">
-        <f t="shared" si="63"/>
+        <f t="shared" si="60"/>
         <v>0.12265331664580725</v>
       </c>
       <c r="Z24" s="8">
-        <f t="shared" si="63"/>
-        <v>0.13654403567447049</v>
+        <f t="shared" si="60"/>
+        <v>0.25529542920847259</v>
       </c>
       <c r="AA24" s="8">
-        <f t="shared" si="63"/>
+        <f t="shared" si="60"/>
         <v>-1</v>
       </c>
       <c r="AB24" s="8" t="e">
-        <f t="shared" si="63"/>
+        <f t="shared" si="60"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AC24" s="8" t="e">
-        <f t="shared" si="63"/>
+        <f t="shared" si="60"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AD24" s="8" t="e">
-        <f t="shared" si="63"/>
+        <f t="shared" si="60"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AE24" s="8" t="e">
-        <f t="shared" si="63"/>
+        <f t="shared" si="60"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AF24" s="8" t="e">
-        <f t="shared" si="63"/>
+        <f t="shared" si="60"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AG24" s="8" t="e">
-        <f t="shared" si="63"/>
+        <f t="shared" si="60"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH24" s="8" t="e">
-        <f t="shared" si="63"/>
+        <f t="shared" si="60"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI24" s="8" t="e">
-        <f t="shared" si="63"/>
+        <f t="shared" si="60"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AJ24" s="8" t="e">
-        <f t="shared" si="63"/>
+        <f t="shared" si="60"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL24" t="s">
@@ -4025,19 +4015,19 @@
         <v>42</v>
       </c>
       <c r="C25" s="8">
-        <f t="shared" ref="C25:F25" si="64">C8/C3</f>
+        <f t="shared" ref="C25:F25" si="61">C8/C3</f>
         <v>0</v>
       </c>
       <c r="D25" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="61"/>
         <v>2.4195015462979808E-2</v>
       </c>
       <c r="E25" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="61"/>
         <v>3.6136205698401667E-2</v>
       </c>
       <c r="F25" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="61"/>
         <v>2.5786487880350697E-3</v>
       </c>
       <c r="G25" s="8">
@@ -4045,115 +4035,115 @@
         <v>3.6708420320111346E-2</v>
       </c>
       <c r="H25" s="8">
-        <f t="shared" ref="H25:N25" si="65">H8/H3</f>
+        <f t="shared" ref="H25:N25" si="62">H8/H3</f>
         <v>3.1903014834901897E-3</v>
       </c>
       <c r="I25" s="8">
-        <f t="shared" si="65"/>
+        <f t="shared" si="62"/>
         <v>0</v>
       </c>
       <c r="J25" s="8">
-        <f t="shared" si="65"/>
+        <f t="shared" si="62"/>
         <v>4.7037263286499695E-2</v>
       </c>
       <c r="K25" s="8">
-        <f t="shared" si="65"/>
+        <f t="shared" si="62"/>
         <v>1.9848771266540641E-2</v>
       </c>
       <c r="L25" s="8">
-        <f t="shared" si="65"/>
+        <f t="shared" si="62"/>
         <v>1.4078437006177273E-2</v>
       </c>
       <c r="M25" s="8">
-        <f t="shared" si="65"/>
+        <f t="shared" si="62"/>
         <v>2.388383769846655E-2</v>
       </c>
       <c r="N25" s="8">
-        <f t="shared" si="65"/>
+        <f t="shared" si="62"/>
         <v>3.7388169314995327E-2</v>
       </c>
       <c r="O25" s="8">
-        <f t="shared" ref="O25:R25" si="66">O8/O3</f>
+        <f t="shared" ref="O25:R25" si="63">O8/O3</f>
         <v>2.0827586206896551E-2</v>
       </c>
       <c r="P25" s="8">
-        <f t="shared" si="66"/>
-        <v>2.0000000000000004E-2</v>
+        <f t="shared" si="63"/>
+        <v>1.1803762449280709E-2</v>
       </c>
       <c r="Q25" s="8">
-        <f t="shared" si="66"/>
+        <f t="shared" si="63"/>
         <v>0.02</v>
       </c>
       <c r="R25" s="8">
-        <f t="shared" si="66"/>
+        <f t="shared" si="63"/>
         <v>0.04</v>
       </c>
       <c r="T25" s="8">
-        <f t="shared" ref="T25:AJ25" si="67">T8/T3</f>
+        <f t="shared" ref="T25:AJ25" si="64">T8/T3</f>
         <v>0</v>
       </c>
       <c r="U25" s="8">
-        <f t="shared" si="67"/>
+        <f t="shared" si="64"/>
         <v>4.7709300045748644E-3</v>
       </c>
       <c r="V25" s="8">
-        <f t="shared" si="67"/>
+        <f t="shared" si="64"/>
         <v>4.977758949375132E-3</v>
       </c>
       <c r="W25" s="8">
-        <f t="shared" si="67"/>
+        <f t="shared" si="64"/>
         <v>1.6009353779736474E-2</v>
       </c>
       <c r="X25" s="8">
-        <f t="shared" si="67"/>
+        <f t="shared" si="64"/>
         <v>2.1475814805960634E-2</v>
       </c>
       <c r="Y25" s="8">
-        <f t="shared" si="67"/>
+        <f t="shared" si="64"/>
         <v>2.4141726133418539E-2</v>
       </c>
       <c r="Z25" s="8">
-        <f t="shared" si="67"/>
-        <v>2.5414443123265958E-2</v>
+        <f t="shared" si="64"/>
+        <v>2.340610721410644E-2</v>
       </c>
       <c r="AA25" s="8">
-        <f t="shared" si="67"/>
+        <f t="shared" si="64"/>
         <v>0.02</v>
       </c>
       <c r="AB25" s="8">
-        <f t="shared" si="67"/>
+        <f t="shared" si="64"/>
         <v>0.02</v>
       </c>
       <c r="AC25" s="8">
-        <f t="shared" si="67"/>
+        <f t="shared" si="64"/>
         <v>0.02</v>
       </c>
       <c r="AD25" s="8">
-        <f t="shared" si="67"/>
+        <f t="shared" si="64"/>
         <v>0.02</v>
       </c>
       <c r="AE25" s="8">
-        <f t="shared" si="67"/>
+        <f t="shared" si="64"/>
         <v>0.02</v>
       </c>
       <c r="AF25" s="8">
-        <f t="shared" si="67"/>
+        <f t="shared" si="64"/>
         <v>0.02</v>
       </c>
       <c r="AG25" s="8">
-        <f t="shared" si="67"/>
+        <f t="shared" si="64"/>
         <v>0.02</v>
       </c>
       <c r="AH25" s="8">
-        <f t="shared" si="67"/>
+        <f t="shared" si="64"/>
         <v>0.02</v>
       </c>
       <c r="AI25" s="8">
-        <f t="shared" si="67"/>
+        <f t="shared" si="64"/>
         <v>0.02</v>
       </c>
       <c r="AJ25" s="8">
-        <f t="shared" si="67"/>
+        <f t="shared" si="64"/>
         <v>0.02</v>
       </c>
       <c r="AL25" t="s">
@@ -4161,7 +4151,7 @@
       </c>
       <c r="AM25" s="1">
         <f>NPV(AM24,Z17:EP17)</f>
-        <v>340370.30530844227</v>
+        <v>363636.47741468163</v>
       </c>
     </row>
     <row r="26" spans="1:146" x14ac:dyDescent="0.3">
@@ -4169,19 +4159,19 @@
         <v>43</v>
       </c>
       <c r="C26" s="8">
-        <f t="shared" ref="C26:F26" si="68">C9/C3</f>
+        <f t="shared" ref="C26:F26" si="65">C9/C3</f>
         <v>0.57093090768337529</v>
       </c>
       <c r="D26" s="8">
-        <f t="shared" si="68"/>
+        <f t="shared" si="65"/>
         <v>0.54902674185919598</v>
       </c>
       <c r="E26" s="8">
-        <f t="shared" si="68"/>
+        <f t="shared" si="65"/>
         <v>0.54065323141070187</v>
       </c>
       <c r="F26" s="8">
-        <f t="shared" si="68"/>
+        <f t="shared" si="65"/>
         <v>0.54736118274024415</v>
       </c>
       <c r="G26" s="8">
@@ -4189,123 +4179,123 @@
         <v>0.54558107167710512</v>
       </c>
       <c r="H26" s="8">
-        <f t="shared" ref="H26:N26" si="69">H9/H3</f>
+        <f t="shared" ref="H26:N26" si="66">H9/H3</f>
         <v>0.58318711118200672</v>
       </c>
       <c r="I26" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="66"/>
         <v>0.58839736721261293</v>
       </c>
       <c r="J26" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="66"/>
         <v>0.51496640195479537</v>
       </c>
       <c r="K26" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="66"/>
         <v>0.56773787019533717</v>
       </c>
       <c r="L26" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="66"/>
         <v>0.57980175262174971</v>
       </c>
       <c r="M26" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="66"/>
         <v>0.54335730764011403</v>
       </c>
       <c r="N26" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="66"/>
         <v>0.52583789558018423</v>
       </c>
       <c r="O26" s="8">
-        <f t="shared" ref="O26:R26" si="70">O9/O3</f>
+        <f t="shared" ref="O26:R26" si="67">O9/O3</f>
         <v>0.57227586206896552</v>
       </c>
       <c r="P26" s="8">
-        <f t="shared" si="70"/>
-        <v>0.55825425328873113</v>
+        <f t="shared" si="67"/>
+        <v>0.58736013771056195</v>
       </c>
       <c r="Q26" s="8">
-        <f t="shared" si="70"/>
-        <v>0.55001192253261744</v>
+        <f t="shared" si="67"/>
+        <v>0.55652048767596829</v>
       </c>
       <c r="R26" s="8">
-        <f t="shared" si="70"/>
-        <v>0.51971558285485386</v>
+        <f t="shared" si="67"/>
+        <v>0.51617846525781663</v>
       </c>
       <c r="T26" s="8">
-        <f t="shared" ref="T26:AJ26" si="71">T9/T3</f>
+        <f t="shared" ref="T26:AJ26" si="68">T9/T3</f>
         <v>0.57241011668542319</v>
       </c>
       <c r="U26" s="8">
-        <f t="shared" si="71"/>
+        <f t="shared" si="68"/>
         <v>0.52813541598588332</v>
       </c>
       <c r="V26" s="8">
-        <f t="shared" si="71"/>
+        <f t="shared" si="68"/>
         <v>0.53389112476170308</v>
       </c>
       <c r="W26" s="8">
-        <f t="shared" si="71"/>
+        <f t="shared" si="68"/>
         <v>0.55151324369294419</v>
       </c>
       <c r="X26" s="8">
-        <f t="shared" si="71"/>
+        <f t="shared" si="68"/>
         <v>0.55813212208144081</v>
       </c>
       <c r="Y26" s="8">
-        <f t="shared" si="71"/>
+        <f t="shared" si="68"/>
         <v>0.55320055383959954</v>
       </c>
       <c r="Z26" s="8">
-        <f t="shared" si="71"/>
-        <v>0.54925394213238199</v>
+        <f t="shared" si="68"/>
+        <v>0.55715867519442397</v>
       </c>
       <c r="AA26" s="8">
-        <f t="shared" si="71"/>
-        <v>0.59000000000000008</v>
+        <f t="shared" si="68"/>
+        <v>0.6</v>
       </c>
       <c r="AB26" s="8">
-        <f t="shared" si="71"/>
-        <v>0.59</v>
+        <f t="shared" si="68"/>
+        <v>0.61</v>
       </c>
       <c r="AC26" s="8">
-        <f t="shared" si="71"/>
-        <v>0.59</v>
+        <f t="shared" si="68"/>
+        <v>0.6100000000000001</v>
       </c>
       <c r="AD26" s="8">
-        <f t="shared" si="71"/>
-        <v>0.59000000000000008</v>
+        <f t="shared" si="68"/>
+        <v>0.6100000000000001</v>
       </c>
       <c r="AE26" s="8">
-        <f t="shared" si="71"/>
-        <v>0.59000000000000008</v>
+        <f t="shared" si="68"/>
+        <v>0.6100000000000001</v>
       </c>
       <c r="AF26" s="8">
-        <f t="shared" si="71"/>
-        <v>0.59</v>
+        <f t="shared" si="68"/>
+        <v>0.6100000000000001</v>
       </c>
       <c r="AG26" s="8">
-        <f t="shared" si="71"/>
-        <v>0.59</v>
+        <f t="shared" si="68"/>
+        <v>0.6100000000000001</v>
       </c>
       <c r="AH26" s="8">
-        <f t="shared" si="71"/>
-        <v>0.59</v>
+        <f t="shared" si="68"/>
+        <v>0.6100000000000001</v>
       </c>
       <c r="AI26" s="8">
-        <f t="shared" si="71"/>
-        <v>0.59</v>
+        <f t="shared" si="68"/>
+        <v>0.6100000000000001</v>
       </c>
       <c r="AJ26" s="8">
-        <f t="shared" si="71"/>
-        <v>0.59</v>
+        <f t="shared" si="68"/>
+        <v>0.6100000000000001</v>
       </c>
       <c r="AL26" t="s">
         <v>49</v>
       </c>
       <c r="AM26" s="1">
         <f>Main!D8</f>
-        <v>-10908</v>
+        <v>-9603</v>
       </c>
     </row>
     <row r="27" spans="1:146" x14ac:dyDescent="0.3">
@@ -4313,19 +4303,19 @@
         <v>44</v>
       </c>
       <c r="C27" s="8">
-        <f t="shared" ref="C27:F27" si="72">C15/C3</f>
+        <f t="shared" ref="C27:F27" si="69">C15/C3</f>
         <v>0.53667505322237274</v>
       </c>
       <c r="D27" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="69"/>
         <v>0.50900491177005636</v>
       </c>
       <c r="E27" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="69"/>
         <v>0.53370396108408613</v>
       </c>
       <c r="F27" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="69"/>
         <v>0.53102974041602202</v>
       </c>
       <c r="G27" s="8">
@@ -4333,123 +4323,123 @@
         <v>0.49634655532359079</v>
       </c>
       <c r="H27" s="8">
-        <f t="shared" ref="H27:N27" si="73">H15/H3</f>
+        <f t="shared" ref="H27:N27" si="70">H15/H3</f>
         <v>0.59084383474238311</v>
       </c>
       <c r="I27" s="8">
-        <f t="shared" si="73"/>
+        <f t="shared" si="70"/>
         <v>0.57569263737945808</v>
       </c>
       <c r="J27" s="8">
-        <f t="shared" si="73"/>
+        <f t="shared" si="70"/>
         <v>0.50717776420281002</v>
       </c>
       <c r="K27" s="8">
-        <f t="shared" si="73"/>
+        <f t="shared" si="70"/>
         <v>0.56049149338374293</v>
       </c>
       <c r="L27" s="8">
-        <f t="shared" si="73"/>
+        <f t="shared" si="70"/>
         <v>0.56586697313604373</v>
       </c>
       <c r="M27" s="8">
-        <f t="shared" si="73"/>
+        <f t="shared" si="70"/>
         <v>0.52463020762654367</v>
       </c>
       <c r="N27" s="8">
-        <f t="shared" si="73"/>
+        <f t="shared" si="70"/>
         <v>0.51956202430231002</v>
       </c>
       <c r="O27" s="8">
-        <f t="shared" ref="O27:R27" si="74">O15/O3</f>
+        <f t="shared" ref="O27:R27" si="71">O15/O3</f>
         <v>0.55600000000000005</v>
       </c>
       <c r="P27" s="8">
-        <f t="shared" si="74"/>
-        <v>0.54556365054282019</v>
+        <f t="shared" si="71"/>
+        <v>0.57444977253166118</v>
       </c>
       <c r="Q27" s="8">
-        <f t="shared" si="74"/>
-        <v>0.53295688502025862</v>
+        <f t="shared" si="71"/>
+        <v>0.53976466134803691</v>
       </c>
       <c r="R27" s="8">
-        <f t="shared" si="74"/>
-        <v>0.51389613857900696</v>
+        <f t="shared" si="71"/>
+        <v>0.51056321200919241</v>
       </c>
       <c r="T27" s="8">
-        <f t="shared" ref="T27:AJ27" si="75">T15/T3</f>
+        <f t="shared" ref="T27:AJ27" si="72">T15/T3</f>
         <v>0.57637860569803945</v>
       </c>
       <c r="U27" s="8">
-        <f t="shared" si="75"/>
+        <f t="shared" si="72"/>
         <v>0.50715639500686227</v>
       </c>
       <c r="V27" s="8">
-        <f t="shared" si="75"/>
+        <f t="shared" si="72"/>
         <v>0.54580597331073921</v>
       </c>
       <c r="W27" s="8">
-        <f t="shared" si="75"/>
+        <f t="shared" si="72"/>
         <v>0.52758915321311328</v>
       </c>
       <c r="X27" s="8">
-        <f t="shared" si="75"/>
+        <f t="shared" si="72"/>
         <v>0.54342975535899274</v>
       </c>
       <c r="Y27" s="8">
-        <f t="shared" si="75"/>
+        <f t="shared" si="72"/>
         <v>0.54155572123406825</v>
       </c>
       <c r="Z27" s="8">
-        <f t="shared" si="75"/>
-        <v>0.53639179389615532</v>
+        <f t="shared" si="72"/>
+        <v>0.54442087402911776</v>
       </c>
       <c r="AA27" s="8">
-        <f t="shared" si="75"/>
-        <v>0.57825931034482758</v>
+        <f t="shared" si="72"/>
+        <v>0.58790170770249117</v>
       </c>
       <c r="AB27" s="8">
-        <f t="shared" si="75"/>
-        <v>0.5790221706562253</v>
+        <f t="shared" si="72"/>
+        <v>0.5987859781953756</v>
       </c>
       <c r="AC27" s="8">
-        <f t="shared" si="75"/>
-        <v>0.57954329364736734</v>
+        <f t="shared" si="72"/>
+        <v>0.59941273358104663</v>
       </c>
       <c r="AD27" s="8">
-        <f t="shared" si="75"/>
-        <v>0.57994631090108661</v>
+        <f t="shared" si="72"/>
+        <v>0.59981546432619703</v>
       </c>
       <c r="AE27" s="8">
-        <f t="shared" si="75"/>
-        <v>0.58024234944691655</v>
+        <f t="shared" si="72"/>
+        <v>0.60011007381529424</v>
       </c>
       <c r="AF27" s="8">
-        <f t="shared" si="75"/>
-        <v>0.58043924500775268</v>
+        <f t="shared" si="72"/>
+        <v>0.60030434014827139</v>
       </c>
       <c r="AG27" s="8">
-        <f t="shared" si="75"/>
-        <v>0.58063370732877129</v>
+        <f t="shared" si="72"/>
+        <v>0.60049622971910588</v>
       </c>
       <c r="AH27" s="8">
-        <f t="shared" si="75"/>
-        <v>0.58082577522683732</v>
+        <f t="shared" si="72"/>
+        <v>0.60068577989484506</v>
       </c>
       <c r="AI27" s="8">
-        <f t="shared" si="75"/>
-        <v>0.58101548669943348</v>
+        <f t="shared" si="72"/>
+        <v>0.60087302726348657</v>
       </c>
       <c r="AJ27" s="8">
-        <f t="shared" si="75"/>
-        <v>0.58120287894550393</v>
+        <f t="shared" si="72"/>
+        <v>0.60105800765366613</v>
       </c>
       <c r="AL27" t="s">
         <v>50</v>
       </c>
       <c r="AM27" s="1">
         <f>AM25+AM26</f>
-        <v>329462.30530844227</v>
+        <v>354033.47741468163</v>
       </c>
     </row>
     <row r="28" spans="1:146" x14ac:dyDescent="0.3">
@@ -4457,19 +4447,19 @@
         <v>21</v>
       </c>
       <c r="C28" s="8">
-        <f t="shared" ref="C28:F28" si="76">C16/C15</f>
+        <f t="shared" ref="C28:F28" si="73">C16/C15</f>
         <v>5.120807789397764E-2</v>
       </c>
       <c r="D28" s="8">
-        <f t="shared" si="76"/>
+        <f t="shared" si="73"/>
         <v>0.18691922802001429</v>
       </c>
       <c r="E28" s="8">
-        <f t="shared" si="76"/>
+        <f t="shared" si="73"/>
         <v>0.1865234375</v>
       </c>
       <c r="F28" s="8">
-        <f t="shared" si="76"/>
+        <f t="shared" si="73"/>
         <v>0.18258336031078018</v>
       </c>
       <c r="G28" s="8">
@@ -4477,123 +4467,123 @@
         <v>0.17245005257623555</v>
       </c>
       <c r="H28" s="8">
-        <f t="shared" ref="H28:N28" si="77">H16/H15</f>
+        <f t="shared" ref="H28:N28" si="74">H16/H15</f>
         <v>0.23191144708423325</v>
       </c>
       <c r="I28" s="8">
-        <f t="shared" si="77"/>
+        <f t="shared" si="74"/>
         <v>0.14969423025791012</v>
       </c>
       <c r="J28" s="8">
-        <f t="shared" si="77"/>
+        <f t="shared" si="74"/>
         <v>0.15959048479373683</v>
       </c>
       <c r="K28" s="8">
-        <f t="shared" si="77"/>
+        <f t="shared" si="74"/>
         <v>0.1537380550871276</v>
       </c>
       <c r="L28" s="8">
-        <f t="shared" si="77"/>
+        <f t="shared" si="74"/>
         <v>0.17288651942117289</v>
       </c>
       <c r="M28" s="8">
-        <f t="shared" si="77"/>
+        <f t="shared" si="74"/>
         <v>0.15597516813243661</v>
       </c>
       <c r="N28" s="8">
-        <f t="shared" si="77"/>
+        <f t="shared" si="74"/>
         <v>0.14109483423284502</v>
       </c>
       <c r="O28" s="8">
-        <f t="shared" ref="O28:R28" si="78">O16/O15</f>
+        <f t="shared" ref="O28:R28" si="75">O16/O15</f>
         <v>0.18630612751178369</v>
       </c>
       <c r="P28" s="8">
-        <f t="shared" si="78"/>
-        <v>0.15</v>
+        <f t="shared" si="75"/>
+        <v>0.20783390410958905</v>
       </c>
       <c r="Q28" s="8">
-        <f t="shared" si="78"/>
-        <v>0.15</v>
+        <f t="shared" si="75"/>
+        <v>0.18</v>
       </c>
       <c r="R28" s="8">
-        <f t="shared" si="78"/>
-        <v>0.15</v>
+        <f t="shared" si="75"/>
+        <v>0.18</v>
       </c>
       <c r="T28" s="8">
-        <f t="shared" ref="T28:AJ28" si="79">T16/T15</f>
+        <f t="shared" ref="T28:AJ28" si="76">T16/T15</f>
         <v>0.16575891480834445</v>
       </c>
       <c r="U28" s="8">
-        <f t="shared" si="79"/>
+        <f t="shared" si="76"/>
         <v>0.173840206185567</v>
       </c>
       <c r="V28" s="8">
-        <f t="shared" si="79"/>
+        <f t="shared" si="76"/>
         <v>0.15717473561657128</v>
       </c>
       <c r="W28" s="8">
-        <f t="shared" si="79"/>
+        <f t="shared" si="76"/>
         <v>0.15359699965905216</v>
       </c>
       <c r="X28" s="8">
-        <f t="shared" si="79"/>
+        <f t="shared" si="76"/>
         <v>0.17919202287557739</v>
       </c>
       <c r="Y28" s="8">
-        <f t="shared" si="79"/>
+        <f t="shared" si="76"/>
         <v>0.15602464927232201</v>
       </c>
       <c r="Z28" s="8">
-        <f t="shared" si="79"/>
-        <v>0.15865133916168569</v>
+        <f t="shared" si="76"/>
+        <v>0.18883481567969398</v>
       </c>
       <c r="AA28" s="8">
-        <f t="shared" si="79"/>
-        <v>0.16</v>
+        <f t="shared" si="76"/>
+        <v>0.18</v>
       </c>
       <c r="AB28" s="8">
-        <f t="shared" si="79"/>
-        <v>0.16</v>
+        <f t="shared" si="76"/>
+        <v>0.18</v>
       </c>
       <c r="AC28" s="8">
-        <f t="shared" si="79"/>
-        <v>0.16</v>
+        <f t="shared" si="76"/>
+        <v>0.18</v>
       </c>
       <c r="AD28" s="8">
-        <f t="shared" si="79"/>
-        <v>0.16</v>
+        <f t="shared" si="76"/>
+        <v>0.18</v>
       </c>
       <c r="AE28" s="8">
-        <f t="shared" si="79"/>
-        <v>0.16</v>
+        <f t="shared" si="76"/>
+        <v>0.18</v>
       </c>
       <c r="AF28" s="8">
-        <f t="shared" si="79"/>
-        <v>0.16</v>
+        <f t="shared" si="76"/>
+        <v>0.18</v>
       </c>
       <c r="AG28" s="8">
-        <f t="shared" si="79"/>
-        <v>0.16</v>
+        <f t="shared" si="76"/>
+        <v>0.18</v>
       </c>
       <c r="AH28" s="8">
-        <f t="shared" si="79"/>
-        <v>0.16</v>
+        <f t="shared" si="76"/>
+        <v>0.18</v>
       </c>
       <c r="AI28" s="8">
-        <f t="shared" si="79"/>
-        <v>0.16000000000000003</v>
+        <f t="shared" si="76"/>
+        <v>0.17999999999999997</v>
       </c>
       <c r="AJ28" s="8">
-        <f t="shared" si="79"/>
-        <v>0.16</v>
+        <f t="shared" si="76"/>
+        <v>0.18</v>
       </c>
       <c r="AL28" t="s">
         <v>51</v>
       </c>
       <c r="AM28" s="10">
         <f>AM27/AJ18</f>
-        <v>362.80399219077447</v>
+        <v>391.62995289234692</v>
       </c>
     </row>
     <row r="29" spans="1:146" x14ac:dyDescent="0.3">
@@ -4601,19 +4591,19 @@
         <v>45</v>
       </c>
       <c r="C29" s="8">
-        <f t="shared" ref="C29:F29" si="80">C17/C3</f>
+        <f t="shared" ref="C29:F29" si="77">C17/C3</f>
         <v>0.50919295529320685</v>
       </c>
       <c r="D29" s="8">
-        <f t="shared" si="80"/>
+        <f t="shared" si="77"/>
         <v>0.41386210660360195</v>
       </c>
       <c r="E29" s="8">
-        <f t="shared" si="80"/>
+        <f t="shared" si="77"/>
         <v>0.43415566365531622</v>
       </c>
       <c r="F29" s="8">
-        <f t="shared" si="80"/>
+        <f t="shared" si="77"/>
         <v>0.43407254598590339</v>
       </c>
       <c r="G29" s="8">
@@ -4621,123 +4611,123 @@
         <v>0.41075156576200417</v>
       </c>
       <c r="H29" s="8">
-        <f t="shared" ref="H29:N29" si="81">H17/H3</f>
+        <f t="shared" ref="H29:N29" si="78">H17/H3</f>
         <v>0.45382038602647951</v>
       </c>
       <c r="I29" s="8">
-        <f t="shared" si="81"/>
+        <f t="shared" si="78"/>
         <v>0.48951477116179398</v>
       </c>
       <c r="J29" s="8">
-        <f t="shared" si="81"/>
+        <f t="shared" si="78"/>
         <v>0.42623701893708005</v>
       </c>
       <c r="K29" s="8">
-        <f t="shared" si="81"/>
+        <f t="shared" si="78"/>
         <v>0.47432262129804664</v>
       </c>
       <c r="L29" s="8">
-        <f t="shared" si="81"/>
+        <f t="shared" si="78"/>
         <v>0.46803620169515875</v>
       </c>
       <c r="M29" s="8">
-        <f t="shared" si="81"/>
+        <f t="shared" si="78"/>
         <v>0.44280092278463834</v>
       </c>
       <c r="N29" s="8">
-        <f t="shared" si="81"/>
+        <f t="shared" si="78"/>
         <v>0.44625450660969423</v>
       </c>
       <c r="O29" s="8">
-        <f t="shared" ref="O29:R29" si="82">O17/O3</f>
+        <f t="shared" ref="O29:R29" si="79">O17/O3</f>
         <v>0.45241379310344826</v>
       </c>
       <c r="P29" s="8">
-        <f t="shared" si="82"/>
-        <v>0.46372910296139724</v>
+        <f t="shared" si="79"/>
+        <v>0.45505963359154061</v>
       </c>
       <c r="Q29" s="8">
-        <f t="shared" si="82"/>
-        <v>0.45301335226721984</v>
+        <f t="shared" si="79"/>
+        <v>0.44260702230539029</v>
       </c>
       <c r="R29" s="8">
-        <f t="shared" si="82"/>
-        <v>0.43681171779215594</v>
+        <f t="shared" si="79"/>
+        <v>0.4186618338475378</v>
       </c>
       <c r="T29" s="8">
-        <f t="shared" ref="T29:AJ29" si="83">T17/T3</f>
+        <f t="shared" ref="T29:AJ29" si="80">T17/T3</f>
         <v>0.48083871349878576</v>
       </c>
       <c r="U29" s="8">
-        <f t="shared" si="83"/>
+        <f t="shared" si="80"/>
         <v>0.41899222273054049</v>
       </c>
       <c r="V29" s="8">
-        <f t="shared" si="83"/>
+        <f t="shared" si="80"/>
         <v>0.46001906375767848</v>
       </c>
       <c r="W29" s="8">
-        <f t="shared" si="83"/>
+        <f t="shared" si="80"/>
         <v>0.44655304222691911</v>
       </c>
       <c r="X29" s="8">
-        <f t="shared" si="83"/>
+        <f t="shared" si="80"/>
         <v>0.44605147820543467</v>
       </c>
       <c r="Y29" s="8">
-        <f t="shared" si="83"/>
+        <f t="shared" si="80"/>
         <v>0.45705967976710332</v>
       </c>
       <c r="Z29" s="8">
-        <f t="shared" si="83"/>
-        <v>0.45129251747919136</v>
+        <f t="shared" si="80"/>
+        <v>0.4416152586296514</v>
       </c>
       <c r="AA29" s="8">
-        <f t="shared" si="83"/>
-        <v>0.48573782068965515</v>
+        <f t="shared" si="80"/>
+        <v>0.48207940031604274</v>
       </c>
       <c r="AB29" s="8">
-        <f t="shared" si="83"/>
-        <v>0.48637862335122922</v>
+        <f t="shared" si="80"/>
+        <v>0.49100450212020796</v>
       </c>
       <c r="AC29" s="8">
-        <f t="shared" si="83"/>
-        <v>0.48681636666378858</v>
+        <f t="shared" si="80"/>
+        <v>0.49151844153645818</v>
       </c>
       <c r="AD29" s="8">
-        <f t="shared" si="83"/>
-        <v>0.48715490115691273</v>
+        <f t="shared" si="80"/>
+        <v>0.49184868074748156</v>
       </c>
       <c r="AE29" s="8">
-        <f t="shared" si="83"/>
-        <v>0.48740357353540992</v>
+        <f t="shared" si="80"/>
+        <v>0.49209026052854132</v>
       </c>
       <c r="AF29" s="8">
-        <f t="shared" si="83"/>
-        <v>0.48756896580651227</v>
+        <f t="shared" si="80"/>
+        <v>0.49224955892158262</v>
       </c>
       <c r="AG29" s="8">
-        <f t="shared" si="83"/>
-        <v>0.48773231415616791</v>
+        <f t="shared" si="80"/>
+        <v>0.49240690836966683</v>
       </c>
       <c r="AH29" s="8">
-        <f t="shared" si="83"/>
-        <v>0.48789365119054334</v>
+        <f t="shared" si="80"/>
+        <v>0.49256233951377293</v>
       </c>
       <c r="AI29" s="8">
-        <f t="shared" si="83"/>
-        <v>0.48805300882752406</v>
+        <f t="shared" si="80"/>
+        <v>0.49271588235605907</v>
       </c>
       <c r="AJ29" s="8">
-        <f t="shared" si="83"/>
-        <v>0.48821041831422329</v>
+        <f t="shared" si="80"/>
+        <v>0.4928675662760062</v>
       </c>
       <c r="AL29" t="s">
         <v>52</v>
       </c>
       <c r="AM29" s="10">
         <f>Main!D3</f>
-        <v>568.04</v>
+        <v>575.01</v>
       </c>
     </row>
     <row r="30" spans="1:146" x14ac:dyDescent="0.3">
@@ -4746,7 +4736,7 @@
       </c>
       <c r="AM30" s="9">
         <f>AM28/AM29-1</f>
-        <v>-0.36130555561091737</v>
+        <v>-0.3189162746867934</v>
       </c>
     </row>
     <row r="31" spans="1:146" x14ac:dyDescent="0.3">

--- a/Financial Analysis/MA.xlsx
+++ b/Financial Analysis/MA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B9104A0-D0CC-42DE-8F61-5A0CA24CF7C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70CC687C-BAF3-47C9-9A82-EA0D17D2A78E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{5EE3D269-52EC-4F93-A9AE-4AAFACF544BD}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{5EE3D269-52EC-4F93-A9AE-4AAFACF544BD}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -193,9 +193,6 @@
     <t>Consensus</t>
   </si>
   <si>
-    <t>Overvalued</t>
-  </si>
-  <si>
     <t>MA</t>
   </si>
   <si>
@@ -209,6 +206,9 @@
   </si>
   <si>
     <t>Q425</t>
+  </si>
+  <si>
+    <t>Slightly overvalued</t>
   </si>
 </sst>
 </file>
@@ -308,13 +308,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>16</xdr:col>
+      <xdr:col>17</xdr:col>
       <xdr:colOff>15240</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
+      <xdr:col>17</xdr:col>
       <xdr:colOff>15240</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>83820</xdr:rowOff>
@@ -332,7 +332,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10660380" y="0"/>
+          <a:off x="11269980" y="0"/>
           <a:ext cx="0" cy="6118860"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -727,23 +727,23 @@
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B3" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C3" t="s">
         <v>0</v>
       </c>
       <c r="D3" s="10">
-        <v>575.01</v>
+        <v>549.86</v>
       </c>
       <c r="E3" s="3">
-        <v>45869</v>
+        <v>45961</v>
       </c>
       <c r="F3" s="3">
         <f ca="1">TODAY()</f>
-        <v>45869</v>
+        <v>45961</v>
       </c>
       <c r="G3" s="3">
-        <v>45953</v>
+        <v>46057</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -751,8 +751,8 @@
         <v>1</v>
       </c>
       <c r="D4" s="1">
-        <f>897.3+6.7</f>
-        <v>904</v>
+        <f>891.3+6.7</f>
+        <v>898</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>58</v>
@@ -764,7 +764,7 @@
       </c>
       <c r="D5" s="1">
         <f>D3*D4</f>
-        <v>519809.04</v>
+        <v>493774.28</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -772,8 +772,8 @@
         <v>4</v>
       </c>
       <c r="D6" s="1">
-        <f>9031+336</f>
-        <v>9367</v>
+        <f>10313+335</f>
+        <v>10648</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>58</v>
@@ -784,8 +784,8 @@
         <v>5</v>
       </c>
       <c r="D7" s="1">
-        <f>18970</f>
-        <v>18970</v>
+        <f>18983</f>
+        <v>18983</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>58</v>
@@ -797,7 +797,7 @@
       </c>
       <c r="D8" s="1">
         <f>D6-D7</f>
-        <v>-9603</v>
+        <v>-8335</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
@@ -806,7 +806,7 @@
       </c>
       <c r="D9" s="1">
         <f>D5-D8</f>
-        <v>529412.04</v>
+        <v>502109.28</v>
       </c>
     </row>
   </sheetData>
@@ -821,7 +821,7 @@
   <cols>
     <col min="2" max="2" width="21.88671875" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="13" customWidth="1"/>
-    <col min="39" max="39" width="14.109375" customWidth="1"/>
+    <col min="39" max="39" width="16.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:36" x14ac:dyDescent="0.3">
@@ -862,16 +862,16 @@
         <v>37</v>
       </c>
       <c r="O2" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="P2" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="Q2" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="Q2" s="4" t="s">
+      <c r="R2" s="4" t="s">
         <v>59</v>
-      </c>
-      <c r="R2" s="4" t="s">
-        <v>60</v>
       </c>
       <c r="T2">
         <v>2019</v>
@@ -973,12 +973,11 @@
         <v>8133</v>
       </c>
       <c r="Q3" s="7">
-        <f>M3*1.14</f>
-        <v>8400.66</v>
+        <v>8602</v>
       </c>
       <c r="R3" s="7">
-        <f>N3*1.14</f>
-        <v>8537.4599999999991</v>
+        <f>N3*1.16</f>
+        <v>8687.24</v>
       </c>
       <c r="T3" s="7">
         <v>16883</v>
@@ -1003,47 +1002,47 @@
       </c>
       <c r="Z3" s="7">
         <f>SUM(O3:R3)</f>
-        <v>32321.119999999999</v>
+        <v>32672.239999999998</v>
       </c>
       <c r="AA3" s="7">
-        <f>Z3*1.12</f>
-        <v>36199.654399999999</v>
+        <f>Z3*1.13</f>
+        <v>36919.631199999996</v>
       </c>
       <c r="AB3" s="7">
         <f>AA3*1.09</f>
-        <v>39457.623296000005</v>
+        <v>40242.398007999996</v>
       </c>
       <c r="AC3" s="7">
         <f>AB3*1.07</f>
-        <v>42219.65692672001</v>
+        <v>43059.365868560002</v>
       </c>
       <c r="AD3" s="7">
         <f>AC3*1.05</f>
-        <v>44330.639773056013</v>
+        <v>45212.334161988001</v>
       </c>
       <c r="AE3" s="7">
         <f>AD3*1.04</f>
-        <v>46103.865363978257</v>
+        <v>47020.827528467526</v>
       </c>
       <c r="AF3" s="7">
         <f>AE3*1.03</f>
-        <v>47486.981324897606</v>
+        <v>48431.452354321555</v>
       </c>
       <c r="AG3" s="7">
         <f t="shared" ref="AG3:AJ3" si="0">AF3*1.03</f>
-        <v>48911.590764644534</v>
+        <v>49884.395924951205</v>
       </c>
       <c r="AH3" s="7">
         <f t="shared" si="0"/>
-        <v>50378.938487583873</v>
+        <v>51380.927802699742</v>
       </c>
       <c r="AI3" s="7">
         <f t="shared" si="0"/>
-        <v>51890.306642211392</v>
+        <v>52922.355636780732</v>
       </c>
       <c r="AJ3" s="7">
         <f t="shared" si="0"/>
-        <v>53447.015841477732</v>
+        <v>54510.026305884159</v>
       </c>
     </row>
     <row r="4" spans="1:36" x14ac:dyDescent="0.3">
@@ -1093,12 +1092,11 @@
         <v>2766</v>
       </c>
       <c r="Q4" s="1">
-        <f t="shared" ref="Q4" si="1">Q3-Q5</f>
-        <v>3024.2375999999995</v>
+        <v>2923</v>
       </c>
       <c r="R4" s="1">
-        <f t="shared" ref="R4" si="2">R3-R5</f>
-        <v>3158.8602000000001</v>
+        <f t="shared" ref="R4" si="1">R3-R5</f>
+        <v>3127.4063999999998</v>
       </c>
       <c r="T4" s="1">
         <v>5763</v>
@@ -1123,47 +1121,47 @@
       </c>
       <c r="Z4" s="1">
         <f>SUM(O4:R4)</f>
-        <v>11472.0978</v>
+        <v>11339.4064</v>
       </c>
       <c r="AA4" s="1">
-        <f t="shared" ref="AA4:AJ4" si="3">AA3-AA5</f>
-        <v>12669.87904</v>
+        <f t="shared" ref="AA4:AJ4" si="2">AA3-AA5</f>
+        <v>12921.870919999998</v>
       </c>
       <c r="AB4" s="1">
-        <f t="shared" si="3"/>
-        <v>13415.591920639999</v>
+        <f t="shared" si="2"/>
+        <v>13682.415322719997</v>
       </c>
       <c r="AC4" s="1">
-        <f t="shared" si="3"/>
-        <v>14354.683355084802</v>
+        <f t="shared" si="2"/>
+        <v>14640.1843953104</v>
       </c>
       <c r="AD4" s="1">
-        <f t="shared" si="3"/>
-        <v>15072.417522839041</v>
+        <f t="shared" si="2"/>
+        <v>15372.193615075917</v>
       </c>
       <c r="AE4" s="1">
-        <f t="shared" si="3"/>
-        <v>15675.314223752604</v>
+        <f t="shared" si="2"/>
+        <v>15987.081359678956</v>
       </c>
       <c r="AF4" s="1">
-        <f t="shared" si="3"/>
-        <v>16145.573650465183</v>
+        <f t="shared" si="2"/>
+        <v>16466.693800469326</v>
       </c>
       <c r="AG4" s="1">
-        <f t="shared" si="3"/>
-        <v>16629.940859979139</v>
+        <f t="shared" si="2"/>
+        <v>16960.694614483407</v>
       </c>
       <c r="AH4" s="1">
-        <f t="shared" si="3"/>
-        <v>17128.839085778513</v>
+        <f t="shared" si="2"/>
+        <v>17469.515452917913</v>
       </c>
       <c r="AI4" s="1">
-        <f t="shared" si="3"/>
-        <v>17642.704258351871</v>
+        <f t="shared" si="2"/>
+        <v>17993.600916505449</v>
       </c>
       <c r="AJ4" s="1">
-        <f t="shared" si="3"/>
-        <v>18171.985386102424</v>
+        <f t="shared" si="2"/>
+        <v>18533.408944000614</v>
       </c>
     </row>
     <row r="5" spans="1:36" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -1172,136 +1170,136 @@
         <v>12</v>
       </c>
       <c r="C5" s="7">
-        <f t="shared" ref="C5:P5" si="4">C3-C4</f>
+        <f t="shared" ref="C5:R5" si="3">C3-C4</f>
         <v>3323</v>
       </c>
       <c r="D5" s="7">
+        <f t="shared" si="3"/>
+        <v>3550</v>
+      </c>
+      <c r="E5" s="7">
+        <f t="shared" si="3"/>
+        <v>3687</v>
+      </c>
+      <c r="F5" s="7">
+        <f t="shared" si="3"/>
+        <v>3599</v>
+      </c>
+      <c r="G5" s="7">
+        <f t="shared" si="3"/>
+        <v>3705</v>
+      </c>
+      <c r="H5" s="7">
+        <f t="shared" si="3"/>
+        <v>4069</v>
+      </c>
+      <c r="I5" s="7">
+        <f t="shared" si="3"/>
+        <v>4248</v>
+      </c>
+      <c r="J5" s="7">
+        <f t="shared" si="3"/>
+        <v>4149</v>
+      </c>
+      <c r="K5" s="7">
+        <f t="shared" si="3"/>
+        <v>4062</v>
+      </c>
+      <c r="L5" s="7">
+        <f t="shared" si="3"/>
+        <v>4543</v>
+      </c>
+      <c r="M5" s="7">
+        <f t="shared" si="3"/>
+        <v>4625</v>
+      </c>
+      <c r="N5" s="7">
+        <f t="shared" si="3"/>
+        <v>4744</v>
+      </c>
+      <c r="O5" s="7">
+        <f t="shared" si="3"/>
+        <v>4727</v>
+      </c>
+      <c r="P5" s="7">
+        <f t="shared" si="3"/>
+        <v>5367</v>
+      </c>
+      <c r="Q5" s="7">
+        <f t="shared" si="3"/>
+        <v>5679</v>
+      </c>
+      <c r="R5" s="7">
+        <f>R3*0.64</f>
+        <v>5559.8335999999999</v>
+      </c>
+      <c r="T5" s="7">
+        <f t="shared" ref="T5:Z5" si="4">T3-T4</f>
+        <v>11120</v>
+      </c>
+      <c r="U5" s="7">
         <f t="shared" si="4"/>
-        <v>3550</v>
-      </c>
-      <c r="E5" s="7">
+        <v>9391</v>
+      </c>
+      <c r="V5" s="7">
         <f t="shared" si="4"/>
-        <v>3687</v>
-      </c>
-      <c r="F5" s="7">
+        <v>11797</v>
+      </c>
+      <c r="W5" s="7">
         <f t="shared" si="4"/>
-        <v>3599</v>
-      </c>
-      <c r="G5" s="7">
+        <v>14159</v>
+      </c>
+      <c r="X5" s="7">
         <f t="shared" si="4"/>
-        <v>3705</v>
-      </c>
-      <c r="H5" s="7">
+        <v>16171</v>
+      </c>
+      <c r="Y5" s="7">
         <f t="shared" si="4"/>
-        <v>4069</v>
-      </c>
-      <c r="I5" s="7">
+        <v>17974</v>
+      </c>
+      <c r="Z5" s="7">
         <f t="shared" si="4"/>
-        <v>4248</v>
-      </c>
-      <c r="J5" s="7">
-        <f t="shared" si="4"/>
-        <v>4149</v>
-      </c>
-      <c r="K5" s="7">
-        <f t="shared" si="4"/>
-        <v>4062</v>
-      </c>
-      <c r="L5" s="7">
-        <f t="shared" si="4"/>
-        <v>4543</v>
-      </c>
-      <c r="M5" s="7">
-        <f t="shared" si="4"/>
-        <v>4625</v>
-      </c>
-      <c r="N5" s="7">
-        <f t="shared" si="4"/>
-        <v>4744</v>
-      </c>
-      <c r="O5" s="7">
-        <f t="shared" si="4"/>
-        <v>4727</v>
-      </c>
-      <c r="P5" s="7">
-        <f t="shared" si="4"/>
-        <v>5367</v>
-      </c>
-      <c r="Q5" s="7">
-        <f>Q3*0.64</f>
-        <v>5376.4224000000004</v>
-      </c>
-      <c r="R5" s="7">
-        <f>R3*0.63</f>
-        <v>5378.599799999999</v>
-      </c>
-      <c r="T5" s="7">
-        <f t="shared" ref="T5:Z5" si="5">T3-T4</f>
-        <v>11120</v>
-      </c>
-      <c r="U5" s="7">
-        <f t="shared" si="5"/>
-        <v>9391</v>
-      </c>
-      <c r="V5" s="7">
-        <f t="shared" si="5"/>
-        <v>11797</v>
-      </c>
-      <c r="W5" s="7">
-        <f t="shared" si="5"/>
-        <v>14159</v>
-      </c>
-      <c r="X5" s="7">
-        <f t="shared" si="5"/>
-        <v>16171</v>
-      </c>
-      <c r="Y5" s="7">
-        <f t="shared" si="5"/>
-        <v>17974</v>
-      </c>
-      <c r="Z5" s="7">
-        <f t="shared" si="5"/>
-        <v>20849.022199999999</v>
+        <v>21332.833599999998</v>
       </c>
       <c r="AA5" s="7">
         <f>AA3*0.65</f>
-        <v>23529.77536</v>
+        <v>23997.760279999999</v>
       </c>
       <c r="AB5" s="7">
         <f>AB3*0.66</f>
-        <v>26042.031375360006</v>
+        <v>26559.98268528</v>
       </c>
       <c r="AC5" s="7">
-        <f t="shared" ref="AC5:AJ5" si="6">AC3*0.66</f>
-        <v>27864.973571635208</v>
+        <f t="shared" ref="AC5:AJ5" si="5">AC3*0.66</f>
+        <v>28419.181473249602</v>
       </c>
       <c r="AD5" s="7">
-        <f t="shared" si="6"/>
-        <v>29258.222250216972</v>
+        <f t="shared" si="5"/>
+        <v>29840.140546912084</v>
       </c>
       <c r="AE5" s="7">
-        <f t="shared" si="6"/>
-        <v>30428.551140225652</v>
+        <f t="shared" si="5"/>
+        <v>31033.74616878857</v>
       </c>
       <c r="AF5" s="7">
-        <f t="shared" si="6"/>
-        <v>31341.407674432423</v>
+        <f t="shared" si="5"/>
+        <v>31964.758553852229</v>
       </c>
       <c r="AG5" s="7">
-        <f t="shared" si="6"/>
-        <v>32281.649904665395</v>
+        <f t="shared" si="5"/>
+        <v>32923.701310467797</v>
       </c>
       <c r="AH5" s="7">
-        <f t="shared" si="6"/>
-        <v>33250.099401805361</v>
+        <f t="shared" si="5"/>
+        <v>33911.412349781829</v>
       </c>
       <c r="AI5" s="7">
-        <f t="shared" si="6"/>
-        <v>34247.602383859521</v>
+        <f t="shared" si="5"/>
+        <v>34928.754720275283</v>
       </c>
       <c r="AJ5" s="7">
-        <f t="shared" si="6"/>
-        <v>35275.030455375309</v>
+        <f t="shared" si="5"/>
+        <v>35976.617361883546</v>
       </c>
     </row>
     <row r="6" spans="1:36" x14ac:dyDescent="0.3">
@@ -1351,12 +1349,11 @@
         <v>213</v>
       </c>
       <c r="Q6" s="1">
-        <f>Q3*0.03</f>
-        <v>252.01979999999998</v>
+        <v>245</v>
       </c>
       <c r="R6" s="1">
         <f>R3*0.04</f>
-        <v>341.49839999999995</v>
+        <v>347.4896</v>
       </c>
       <c r="T6" s="1">
         <v>934</v>
@@ -1381,47 +1378,47 @@
       </c>
       <c r="Z6" s="1">
         <f>SUM(O6:R6)</f>
-        <v>958.51819999999998</v>
+        <v>957.4896</v>
       </c>
       <c r="AA6" s="1">
-        <f t="shared" ref="AA6:AJ6" si="7">AA3*0.03</f>
-        <v>1085.989632</v>
+        <f t="shared" ref="AA6:AJ6" si="6">AA3*0.03</f>
+        <v>1107.5889359999999</v>
       </c>
       <c r="AB6" s="1">
-        <f t="shared" si="7"/>
-        <v>1183.7286988800001</v>
+        <f t="shared" si="6"/>
+        <v>1207.2719402399998</v>
       </c>
       <c r="AC6" s="1">
-        <f t="shared" si="7"/>
-        <v>1266.5897078016003</v>
+        <f t="shared" si="6"/>
+        <v>1291.7809760568</v>
       </c>
       <c r="AD6" s="1">
-        <f t="shared" si="7"/>
-        <v>1329.9191931916803</v>
+        <f t="shared" si="6"/>
+        <v>1356.3700248596399</v>
       </c>
       <c r="AE6" s="1">
-        <f t="shared" si="7"/>
-        <v>1383.1159609193476</v>
+        <f t="shared" si="6"/>
+        <v>1410.6248258540256</v>
       </c>
       <c r="AF6" s="1">
-        <f t="shared" si="7"/>
-        <v>1424.609439746928</v>
+        <f t="shared" si="6"/>
+        <v>1452.9435706296465</v>
       </c>
       <c r="AG6" s="1">
-        <f t="shared" si="7"/>
-        <v>1467.3477229393359</v>
+        <f t="shared" si="6"/>
+        <v>1496.5318777485361</v>
       </c>
       <c r="AH6" s="1">
-        <f t="shared" si="7"/>
-        <v>1511.3681546275161</v>
+        <f t="shared" si="6"/>
+        <v>1541.4278340809922</v>
       </c>
       <c r="AI6" s="1">
-        <f t="shared" si="7"/>
-        <v>1556.7091992663418</v>
+        <f t="shared" si="6"/>
+        <v>1587.6706691034219</v>
       </c>
       <c r="AJ6" s="1">
-        <f t="shared" si="7"/>
-        <v>1603.410475244332</v>
+        <f t="shared" si="6"/>
+        <v>1635.3007891765246</v>
       </c>
     </row>
     <row r="7" spans="1:36" x14ac:dyDescent="0.3">
@@ -1471,12 +1468,11 @@
         <v>281</v>
       </c>
       <c r="Q7" s="1">
-        <f>M7*1.25</f>
-        <v>281.25</v>
+        <v>290</v>
       </c>
       <c r="R7" s="1">
-        <f>N7*1.25</f>
-        <v>288.75</v>
+        <f>N7*1.27</f>
+        <v>293.37</v>
       </c>
       <c r="T7" s="1">
         <v>522</v>
@@ -1501,7 +1497,7 @@
       </c>
       <c r="Z7" s="1">
         <f>SUM(O7:R7)</f>
-        <v>1126</v>
+        <v>1139.3699999999999</v>
       </c>
       <c r="AA7" s="1"/>
       <c r="AB7" s="1"/>
@@ -1561,12 +1557,11 @@
         <v>96</v>
       </c>
       <c r="Q8" s="1">
-        <f t="shared" ref="Q8" si="8">Q3*0.02</f>
-        <v>168.01320000000001</v>
+        <v>83</v>
       </c>
       <c r="R8" s="1">
         <f>R3*0.04</f>
-        <v>341.49839999999995</v>
+        <v>347.4896</v>
       </c>
       <c r="T8" s="1">
         <v>0</v>
@@ -1591,47 +1586,47 @@
       </c>
       <c r="Z8" s="1">
         <f>SUM(O8:R8)</f>
-        <v>756.51159999999993</v>
+        <v>677.4896</v>
       </c>
       <c r="AA8" s="1">
-        <f t="shared" ref="AA8:AJ8" si="9">AA3*0.02</f>
-        <v>723.99308800000006</v>
+        <f t="shared" ref="AA8:AJ8" si="7">AA3*0.02</f>
+        <v>738.39262399999996</v>
       </c>
       <c r="AB8" s="1">
-        <f t="shared" si="9"/>
-        <v>789.15246592000017</v>
+        <f t="shared" si="7"/>
+        <v>804.84796015999996</v>
       </c>
       <c r="AC8" s="1">
-        <f t="shared" si="9"/>
-        <v>844.39313853440024</v>
+        <f t="shared" si="7"/>
+        <v>861.18731737120004</v>
       </c>
       <c r="AD8" s="1">
-        <f t="shared" si="9"/>
-        <v>886.6127954611203</v>
+        <f t="shared" si="7"/>
+        <v>904.24668323976005</v>
       </c>
       <c r="AE8" s="1">
-        <f t="shared" si="9"/>
-        <v>922.07730727956516</v>
+        <f t="shared" si="7"/>
+        <v>940.41655056935053</v>
       </c>
       <c r="AF8" s="1">
-        <f t="shared" si="9"/>
-        <v>949.73962649795214</v>
+        <f t="shared" si="7"/>
+        <v>968.62904708643111</v>
       </c>
       <c r="AG8" s="1">
-        <f t="shared" si="9"/>
-        <v>978.2318152928907</v>
+        <f t="shared" si="7"/>
+        <v>997.68791849902414</v>
       </c>
       <c r="AH8" s="1">
-        <f t="shared" si="9"/>
-        <v>1007.5787697516774</v>
+        <f t="shared" si="7"/>
+        <v>1027.6185560539948</v>
       </c>
       <c r="AI8" s="1">
-        <f t="shared" si="9"/>
-        <v>1037.8061328442279</v>
+        <f t="shared" si="7"/>
+        <v>1058.4471127356146</v>
       </c>
       <c r="AJ8" s="1">
-        <f t="shared" si="9"/>
-        <v>1068.9403168295546</v>
+        <f t="shared" si="7"/>
+        <v>1090.2005261176832</v>
       </c>
     </row>
     <row r="9" spans="1:36" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -1640,137 +1635,137 @@
         <v>16</v>
       </c>
       <c r="C9" s="7">
-        <f t="shared" ref="C9:K9" si="10">C5-C6-C7-C8</f>
+        <f t="shared" ref="C9:K9" si="8">C5-C6-C7-C8</f>
         <v>2950</v>
       </c>
       <c r="D9" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>3018</v>
       </c>
       <c r="E9" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>3112</v>
       </c>
       <c r="F9" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>3184</v>
       </c>
       <c r="G9" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>3136</v>
       </c>
       <c r="H9" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>3656</v>
       </c>
       <c r="I9" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>3844</v>
       </c>
       <c r="J9" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>3372</v>
       </c>
       <c r="K9" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>3604</v>
       </c>
       <c r="L9" s="7">
-        <f t="shared" ref="L9:R9" si="11">L5-L6-L7-L8</f>
+        <f t="shared" ref="L9:R9" si="9">L5-L6-L7-L8</f>
         <v>4036</v>
       </c>
       <c r="M9" s="7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>4004</v>
       </c>
       <c r="N9" s="7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>3938</v>
       </c>
       <c r="O9" s="7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>4149</v>
       </c>
       <c r="P9" s="7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>4777</v>
       </c>
       <c r="Q9" s="7">
-        <f t="shared" si="11"/>
-        <v>4675.1394</v>
+        <f t="shared" si="9"/>
+        <v>5061</v>
       </c>
       <c r="R9" s="7">
-        <f t="shared" si="11"/>
-        <v>4406.8529999999992</v>
+        <f t="shared" si="9"/>
+        <v>4571.4844000000003</v>
       </c>
       <c r="S9" s="7"/>
       <c r="T9" s="7">
-        <f t="shared" ref="T9:Z9" si="12">T5-T6-T7-T8</f>
+        <f t="shared" ref="T9:Z9" si="10">T5-T6-T7-T8</f>
         <v>9664</v>
       </c>
       <c r="U9" s="7">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>8081</v>
       </c>
       <c r="V9" s="7">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>10082</v>
       </c>
       <c r="W9" s="7">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>12264</v>
       </c>
       <c r="X9" s="7">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>14008</v>
       </c>
       <c r="Y9" s="7">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>15582</v>
       </c>
       <c r="Z9" s="7">
-        <f t="shared" si="12"/>
-        <v>18007.992399999999</v>
+        <f t="shared" si="10"/>
+        <v>18558.484399999998</v>
       </c>
       <c r="AA9" s="7">
-        <f t="shared" ref="AA9:AJ9" si="13">AA5-AA6-AA7-AA8</f>
-        <v>21719.79264</v>
+        <f t="shared" ref="AA9:AJ9" si="11">AA5-AA6-AA7-AA8</f>
+        <v>22151.778719999998</v>
       </c>
       <c r="AB9" s="7">
-        <f t="shared" si="13"/>
-        <v>24069.150210560005</v>
+        <f t="shared" si="11"/>
+        <v>24547.862784879999</v>
       </c>
       <c r="AC9" s="7">
-        <f t="shared" si="13"/>
-        <v>25753.990725299209</v>
+        <f t="shared" si="11"/>
+        <v>26266.2131798216</v>
       </c>
       <c r="AD9" s="7">
-        <f t="shared" si="13"/>
-        <v>27041.69026156417</v>
+        <f t="shared" si="11"/>
+        <v>27579.523838812685</v>
       </c>
       <c r="AE9" s="7">
-        <f t="shared" si="13"/>
-        <v>28123.35787202674</v>
+        <f t="shared" si="11"/>
+        <v>28682.704792365195</v>
       </c>
       <c r="AF9" s="7">
-        <f t="shared" si="13"/>
-        <v>28967.058608187544</v>
+        <f t="shared" si="11"/>
+        <v>29543.185936136153</v>
       </c>
       <c r="AG9" s="7">
-        <f t="shared" si="13"/>
-        <v>29836.07036643317</v>
+        <f t="shared" si="11"/>
+        <v>30429.481514220235</v>
       </c>
       <c r="AH9" s="7">
-        <f t="shared" si="13"/>
-        <v>30731.152477426167</v>
+        <f t="shared" si="11"/>
+        <v>31342.365959646842</v>
       </c>
       <c r="AI9" s="7">
-        <f t="shared" si="13"/>
-        <v>31653.087051748953</v>
+        <f t="shared" si="11"/>
+        <v>32282.636938436248</v>
       </c>
       <c r="AJ9" s="7">
-        <f t="shared" si="13"/>
-        <v>32602.679663301424</v>
+        <f t="shared" si="11"/>
+        <v>33251.116046589341</v>
       </c>
     </row>
     <row r="10" spans="1:36" x14ac:dyDescent="0.3">
@@ -1820,11 +1815,10 @@
         <v>-70</v>
       </c>
       <c r="Q10" s="1">
-        <f t="shared" ref="Q10:R13" si="14">M10*1.02</f>
-        <v>-77.52</v>
+        <v>-81</v>
       </c>
       <c r="R10" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" ref="Q10:R13" si="12">N10*1.02</f>
         <v>-97.92</v>
       </c>
       <c r="T10" s="1">
@@ -1845,52 +1839,52 @@
         <v>-274</v>
       </c>
       <c r="Y10" s="1">
-        <f t="shared" ref="Y10:Y13" si="15">SUM(K10:N10)</f>
+        <f t="shared" ref="Y10:Y13" si="13">SUM(K10:N10)</f>
         <v>-327</v>
       </c>
       <c r="Z10" s="1">
         <f>SUM(O10:R10)</f>
-        <v>-333.44</v>
+        <v>-336.92</v>
       </c>
       <c r="AA10" s="1">
         <f>Z10*1.03</f>
-        <v>-343.44319999999999</v>
+        <v>-347.02760000000001</v>
       </c>
       <c r="AB10" s="1">
-        <f t="shared" ref="AB10:AJ10" si="16">AA10*1.03</f>
-        <v>-353.74649599999998</v>
+        <f t="shared" ref="AB10:AJ10" si="14">AA10*1.03</f>
+        <v>-357.43842800000004</v>
       </c>
       <c r="AC10" s="1">
-        <f t="shared" si="16"/>
-        <v>-364.35889087999999</v>
+        <f t="shared" si="14"/>
+        <v>-368.16158084000006</v>
       </c>
       <c r="AD10" s="1">
-        <f t="shared" si="16"/>
-        <v>-375.2896576064</v>
+        <f t="shared" si="14"/>
+        <v>-379.20642826520009</v>
       </c>
       <c r="AE10" s="1">
-        <f t="shared" si="16"/>
-        <v>-386.54834733459199</v>
+        <f t="shared" si="14"/>
+        <v>-390.58262111315611</v>
       </c>
       <c r="AF10" s="1">
-        <f t="shared" si="16"/>
-        <v>-398.14479775462979</v>
+        <f t="shared" si="14"/>
+        <v>-402.30009974655081</v>
       </c>
       <c r="AG10" s="1">
-        <f t="shared" si="16"/>
-        <v>-410.08914168726869</v>
+        <f t="shared" si="14"/>
+        <v>-414.36910273894733</v>
       </c>
       <c r="AH10" s="1">
-        <f t="shared" si="16"/>
-        <v>-422.39181593788675</v>
+        <f t="shared" si="14"/>
+        <v>-426.80017582111577</v>
       </c>
       <c r="AI10" s="1">
-        <f t="shared" si="16"/>
-        <v>-435.06357041602337</v>
+        <f t="shared" si="14"/>
+        <v>-439.60418109574925</v>
       </c>
       <c r="AJ10" s="1">
-        <f t="shared" si="16"/>
-        <v>-448.11547752850407</v>
+        <f t="shared" si="14"/>
+        <v>-452.79230652862174</v>
       </c>
     </row>
     <row r="11" spans="1:36" x14ac:dyDescent="0.3">
@@ -1940,11 +1934,10 @@
         <v>-4</v>
       </c>
       <c r="Q11" s="1">
-        <f t="shared" si="14"/>
-        <v>63.24</v>
+        <v>-41</v>
       </c>
       <c r="R11" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>-40.799999999999997</v>
       </c>
       <c r="T11" s="1">
@@ -1965,12 +1958,12 @@
         <v>61</v>
       </c>
       <c r="Y11" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>29</v>
       </c>
       <c r="Z11" s="1">
         <f>SUM(O11:R11)</f>
-        <v>47.440000000000012</v>
+        <v>-56.8</v>
       </c>
       <c r="AA11" s="1">
         <v>40</v>
@@ -2050,11 +2043,10 @@
         <v>195</v>
       </c>
       <c r="Q12" s="1">
-        <f t="shared" si="14"/>
-        <v>162.18</v>
+        <v>186</v>
       </c>
       <c r="R12" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>187.68</v>
       </c>
       <c r="T12" s="1">
@@ -2075,52 +2067,52 @@
         <v>575</v>
       </c>
       <c r="Y12" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>646</v>
       </c>
       <c r="Z12" s="1">
         <f>SUM(O12:R12)</f>
-        <v>726.86000000000013</v>
+        <v>750.68000000000006</v>
       </c>
       <c r="AA12" s="1">
         <f>Z12*1.02</f>
-        <v>741.39720000000011</v>
+        <v>765.69360000000006</v>
       </c>
       <c r="AB12" s="1">
-        <f t="shared" ref="AB12:AJ12" si="17">AA12*1.02</f>
-        <v>756.22514400000011</v>
+        <f t="shared" ref="AB12:AJ12" si="15">AA12*1.02</f>
+        <v>781.00747200000012</v>
       </c>
       <c r="AC12" s="1">
-        <f t="shared" si="17"/>
-        <v>771.34964688000014</v>
+        <f t="shared" si="15"/>
+        <v>796.6276214400001</v>
       </c>
       <c r="AD12" s="1">
-        <f t="shared" si="17"/>
-        <v>786.7766398176002</v>
+        <f t="shared" si="15"/>
+        <v>812.56017386880012</v>
       </c>
       <c r="AE12" s="1">
-        <f t="shared" si="17"/>
-        <v>802.5121726139522</v>
+        <f t="shared" si="15"/>
+        <v>828.81137734617619</v>
       </c>
       <c r="AF12" s="1">
-        <f t="shared" si="17"/>
-        <v>818.56241606623121</v>
+        <f t="shared" si="15"/>
+        <v>845.38760489309971</v>
       </c>
       <c r="AG12" s="1">
-        <f t="shared" si="17"/>
-        <v>834.93366438755584</v>
+        <f t="shared" si="15"/>
+        <v>862.29535699096175</v>
       </c>
       <c r="AH12" s="1">
-        <f t="shared" si="17"/>
-        <v>851.63233767530699</v>
+        <f t="shared" si="15"/>
+        <v>879.54126413078097</v>
       </c>
       <c r="AI12" s="1">
-        <f t="shared" si="17"/>
-        <v>868.66498442881311</v>
+        <f t="shared" si="15"/>
+        <v>897.13208941339656</v>
       </c>
       <c r="AJ12" s="1">
-        <f t="shared" si="17"/>
-        <v>886.03828411738937</v>
+        <f t="shared" si="15"/>
+        <v>915.07473120166446</v>
       </c>
     </row>
     <row r="13" spans="1:36" x14ac:dyDescent="0.3">
@@ -2170,11 +2162,10 @@
         <v>-16</v>
       </c>
       <c r="Q13" s="1">
-        <f t="shared" si="14"/>
-        <v>-7.1400000000000006</v>
+        <v>2</v>
       </c>
       <c r="R13" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>-1.02</v>
       </c>
       <c r="T13" s="1">
@@ -2195,12 +2186,12 @@
         <v>7</v>
       </c>
       <c r="Y13" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>-20</v>
       </c>
       <c r="Z13" s="1">
         <f>SUM(O13:R13)</f>
-        <v>-29.16</v>
+        <v>-20.02</v>
       </c>
       <c r="AA13" s="1">
         <v>0</v>
@@ -2238,136 +2229,136 @@
         <v>25</v>
       </c>
       <c r="C14" s="1">
-        <f t="shared" ref="C14:N14" si="18">SUM(C10:C13)</f>
+        <f t="shared" ref="C14:N14" si="16">SUM(C10:C13)</f>
         <v>177</v>
       </c>
       <c r="D14" s="1">
+        <f t="shared" si="16"/>
+        <v>220</v>
+      </c>
+      <c r="E14" s="1">
+        <f t="shared" si="16"/>
+        <v>40</v>
+      </c>
+      <c r="F14" s="1">
+        <f t="shared" si="16"/>
+        <v>95</v>
+      </c>
+      <c r="G14" s="1">
+        <f t="shared" si="16"/>
+        <v>283</v>
+      </c>
+      <c r="H14" s="1">
+        <f t="shared" si="16"/>
+        <v>-48</v>
+      </c>
+      <c r="I14" s="1">
+        <f t="shared" si="16"/>
+        <v>83</v>
+      </c>
+      <c r="J14" s="1">
+        <f t="shared" si="16"/>
+        <v>51</v>
+      </c>
+      <c r="K14" s="1">
+        <f t="shared" si="16"/>
+        <v>46</v>
+      </c>
+      <c r="L14" s="1">
+        <f t="shared" si="16"/>
+        <v>97</v>
+      </c>
+      <c r="M14" s="1">
+        <f t="shared" si="16"/>
+        <v>138</v>
+      </c>
+      <c r="N14" s="1">
+        <f t="shared" si="16"/>
+        <v>47</v>
+      </c>
+      <c r="O14" s="1">
+        <f t="shared" ref="O14:R14" si="17">SUM(O10:O13)</f>
+        <v>118</v>
+      </c>
+      <c r="P14" s="1">
+        <f t="shared" si="17"/>
+        <v>105</v>
+      </c>
+      <c r="Q14" s="1">
+        <f t="shared" si="17"/>
+        <v>66</v>
+      </c>
+      <c r="R14" s="1">
+        <f t="shared" si="17"/>
+        <v>47.940000000000005</v>
+      </c>
+      <c r="T14" s="1">
+        <f t="shared" ref="T14:AJ14" si="18">SUM(T10:T13)</f>
+        <v>-67</v>
+      </c>
+      <c r="U14" s="1">
         <f t="shared" si="18"/>
-        <v>220</v>
-      </c>
-      <c r="E14" s="1">
+        <v>321</v>
+      </c>
+      <c r="V14" s="1">
         <f t="shared" si="18"/>
-        <v>40</v>
-      </c>
-      <c r="F14" s="1">
+        <v>-225</v>
+      </c>
+      <c r="W14" s="1">
         <f t="shared" si="18"/>
-        <v>95</v>
-      </c>
-      <c r="G14" s="1">
+        <v>532</v>
+      </c>
+      <c r="X14" s="1">
         <f t="shared" si="18"/>
-        <v>283</v>
-      </c>
-      <c r="H14" s="1">
+        <v>369</v>
+      </c>
+      <c r="Y14" s="1">
         <f t="shared" si="18"/>
-        <v>-48</v>
-      </c>
-      <c r="I14" s="1">
+        <v>328</v>
+      </c>
+      <c r="Z14" s="1">
         <f t="shared" si="18"/>
-        <v>83</v>
-      </c>
-      <c r="J14" s="1">
+        <v>336.94000000000005</v>
+      </c>
+      <c r="AA14" s="1">
         <f t="shared" si="18"/>
-        <v>51</v>
-      </c>
-      <c r="K14" s="1">
+        <v>458.66600000000005</v>
+      </c>
+      <c r="AB14" s="1">
         <f t="shared" si="18"/>
-        <v>46</v>
-      </c>
-      <c r="L14" s="1">
+        <v>463.56904400000008</v>
+      </c>
+      <c r="AC14" s="1">
         <f t="shared" si="18"/>
-        <v>97</v>
-      </c>
-      <c r="M14" s="1">
+        <v>468.46604060000004</v>
+      </c>
+      <c r="AD14" s="1">
         <f t="shared" si="18"/>
-        <v>138</v>
-      </c>
-      <c r="N14" s="1">
+        <v>473.35374560360003</v>
+      </c>
+      <c r="AE14" s="1">
         <f t="shared" si="18"/>
-        <v>47</v>
-      </c>
-      <c r="O14" s="1">
-        <f t="shared" ref="O14:R14" si="19">SUM(O10:O13)</f>
-        <v>118</v>
-      </c>
-      <c r="P14" s="1">
-        <f t="shared" si="19"/>
-        <v>105</v>
-      </c>
-      <c r="Q14" s="1">
-        <f t="shared" si="19"/>
-        <v>140.76</v>
-      </c>
-      <c r="R14" s="1">
-        <f t="shared" si="19"/>
-        <v>47.940000000000005</v>
-      </c>
-      <c r="T14" s="1">
-        <f t="shared" ref="T14:AJ14" si="20">SUM(T10:T13)</f>
-        <v>-67</v>
-      </c>
-      <c r="U14" s="1">
-        <f t="shared" si="20"/>
-        <v>321</v>
-      </c>
-      <c r="V14" s="1">
-        <f t="shared" si="20"/>
-        <v>-225</v>
-      </c>
-      <c r="W14" s="1">
-        <f t="shared" si="20"/>
-        <v>532</v>
-      </c>
-      <c r="X14" s="1">
-        <f t="shared" si="20"/>
-        <v>369</v>
-      </c>
-      <c r="Y14" s="1">
-        <f t="shared" si="20"/>
-        <v>328</v>
-      </c>
-      <c r="Z14" s="1">
-        <f t="shared" si="20"/>
-        <v>411.7000000000001</v>
-      </c>
-      <c r="AA14" s="1">
-        <f t="shared" si="20"/>
-        <v>437.95400000000012</v>
-      </c>
-      <c r="AB14" s="1">
-        <f t="shared" si="20"/>
-        <v>442.47864800000013</v>
-      </c>
-      <c r="AC14" s="1">
-        <f t="shared" si="20"/>
-        <v>446.99075600000015</v>
-      </c>
-      <c r="AD14" s="1">
-        <f t="shared" si="20"/>
-        <v>451.4869822112002</v>
-      </c>
-      <c r="AE14" s="1">
-        <f t="shared" si="20"/>
-        <v>455.96382527936021</v>
+        <v>478.22875623302008</v>
       </c>
       <c r="AF14" s="1">
-        <f t="shared" si="20"/>
-        <v>460.41761831160142</v>
+        <f t="shared" si="18"/>
+        <v>483.08750514654889</v>
       </c>
       <c r="AG14" s="1">
-        <f t="shared" si="20"/>
-        <v>464.84452270028714</v>
+        <f t="shared" si="18"/>
+        <v>487.92625425201442</v>
       </c>
       <c r="AH14" s="1">
-        <f t="shared" si="20"/>
-        <v>469.24052173742024</v>
+        <f t="shared" si="18"/>
+        <v>492.7410883096652</v>
       </c>
       <c r="AI14" s="1">
-        <f t="shared" si="20"/>
-        <v>473.60141401278975</v>
+        <f t="shared" si="18"/>
+        <v>497.5279083176473</v>
       </c>
       <c r="AJ14" s="1">
-        <f t="shared" si="20"/>
-        <v>477.92280658888529</v>
+        <f t="shared" si="18"/>
+        <v>502.28242467304273</v>
       </c>
     </row>
     <row r="15" spans="1:36" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -2376,136 +2367,136 @@
         <v>20</v>
       </c>
       <c r="C15" s="7">
-        <f t="shared" ref="C15:N15" si="21">C9-C14</f>
+        <f t="shared" ref="C15:N15" si="19">C9-C14</f>
         <v>2773</v>
       </c>
       <c r="D15" s="7">
+        <f t="shared" si="19"/>
+        <v>2798</v>
+      </c>
+      <c r="E15" s="7">
+        <f t="shared" si="19"/>
+        <v>3072</v>
+      </c>
+      <c r="F15" s="7">
+        <f t="shared" si="19"/>
+        <v>3089</v>
+      </c>
+      <c r="G15" s="7">
+        <f t="shared" si="19"/>
+        <v>2853</v>
+      </c>
+      <c r="H15" s="7">
+        <f t="shared" si="19"/>
+        <v>3704</v>
+      </c>
+      <c r="I15" s="7">
+        <f t="shared" si="19"/>
+        <v>3761</v>
+      </c>
+      <c r="J15" s="7">
+        <f t="shared" si="19"/>
+        <v>3321</v>
+      </c>
+      <c r="K15" s="7">
+        <f t="shared" si="19"/>
+        <v>3558</v>
+      </c>
+      <c r="L15" s="7">
+        <f t="shared" si="19"/>
+        <v>3939</v>
+      </c>
+      <c r="M15" s="7">
+        <f t="shared" si="19"/>
+        <v>3866</v>
+      </c>
+      <c r="N15" s="7">
+        <f t="shared" si="19"/>
+        <v>3891</v>
+      </c>
+      <c r="O15" s="7">
+        <f t="shared" ref="O15:R15" si="20">O9-O14</f>
+        <v>4031</v>
+      </c>
+      <c r="P15" s="7">
+        <f t="shared" si="20"/>
+        <v>4672</v>
+      </c>
+      <c r="Q15" s="7">
+        <f t="shared" si="20"/>
+        <v>4995</v>
+      </c>
+      <c r="R15" s="7">
+        <f t="shared" si="20"/>
+        <v>4523.5444000000007</v>
+      </c>
+      <c r="T15" s="7">
+        <f t="shared" ref="T15:AJ15" si="21">T9-T14</f>
+        <v>9731</v>
+      </c>
+      <c r="U15" s="7">
         <f t="shared" si="21"/>
-        <v>2798</v>
-      </c>
-      <c r="E15" s="7">
+        <v>7760</v>
+      </c>
+      <c r="V15" s="7">
         <f t="shared" si="21"/>
-        <v>3072</v>
-      </c>
-      <c r="F15" s="7">
+        <v>10307</v>
+      </c>
+      <c r="W15" s="7">
         <f t="shared" si="21"/>
-        <v>3089</v>
-      </c>
-      <c r="G15" s="7">
+        <v>11732</v>
+      </c>
+      <c r="X15" s="7">
         <f t="shared" si="21"/>
-        <v>2853</v>
-      </c>
-      <c r="H15" s="7">
+        <v>13639</v>
+      </c>
+      <c r="Y15" s="7">
         <f t="shared" si="21"/>
-        <v>3704</v>
-      </c>
-      <c r="I15" s="7">
+        <v>15254</v>
+      </c>
+      <c r="Z15" s="7">
         <f t="shared" si="21"/>
-        <v>3761</v>
-      </c>
-      <c r="J15" s="7">
+        <v>18221.544399999999</v>
+      </c>
+      <c r="AA15" s="7">
         <f t="shared" si="21"/>
-        <v>3321</v>
-      </c>
-      <c r="K15" s="7">
+        <v>21693.112719999997</v>
+      </c>
+      <c r="AB15" s="7">
         <f t="shared" si="21"/>
-        <v>3558</v>
-      </c>
-      <c r="L15" s="7">
+        <v>24084.293740879999</v>
+      </c>
+      <c r="AC15" s="7">
         <f t="shared" si="21"/>
-        <v>3939</v>
-      </c>
-      <c r="M15" s="7">
+        <v>25797.747139221599</v>
+      </c>
+      <c r="AD15" s="7">
         <f t="shared" si="21"/>
-        <v>3866</v>
-      </c>
-      <c r="N15" s="7">
+        <v>27106.170093209086</v>
+      </c>
+      <c r="AE15" s="7">
         <f t="shared" si="21"/>
-        <v>3891</v>
-      </c>
-      <c r="O15" s="7">
-        <f t="shared" ref="O15:R15" si="22">O9-O14</f>
-        <v>4031</v>
-      </c>
-      <c r="P15" s="7">
-        <f t="shared" si="22"/>
-        <v>4672</v>
-      </c>
-      <c r="Q15" s="7">
-        <f t="shared" si="22"/>
-        <v>4534.3793999999998</v>
-      </c>
-      <c r="R15" s="7">
-        <f t="shared" si="22"/>
-        <v>4358.9129999999996</v>
-      </c>
-      <c r="T15" s="7">
-        <f t="shared" ref="T15:AJ15" si="23">T9-T14</f>
-        <v>9731</v>
-      </c>
-      <c r="U15" s="7">
-        <f t="shared" si="23"/>
-        <v>7760</v>
-      </c>
-      <c r="V15" s="7">
-        <f t="shared" si="23"/>
-        <v>10307</v>
-      </c>
-      <c r="W15" s="7">
-        <f t="shared" si="23"/>
-        <v>11732</v>
-      </c>
-      <c r="X15" s="7">
-        <f t="shared" si="23"/>
-        <v>13639</v>
-      </c>
-      <c r="Y15" s="7">
-        <f t="shared" si="23"/>
-        <v>15254</v>
-      </c>
-      <c r="Z15" s="7">
-        <f t="shared" si="23"/>
-        <v>17596.292399999998</v>
-      </c>
-      <c r="AA15" s="7">
-        <f t="shared" si="23"/>
-        <v>21281.838639999998</v>
-      </c>
-      <c r="AB15" s="7">
-        <f t="shared" si="23"/>
-        <v>23626.671562560005</v>
-      </c>
-      <c r="AC15" s="7">
-        <f t="shared" si="23"/>
-        <v>25306.99996929921</v>
-      </c>
-      <c r="AD15" s="7">
-        <f t="shared" si="23"/>
-        <v>26590.203279352969</v>
-      </c>
-      <c r="AE15" s="7">
-        <f t="shared" si="23"/>
-        <v>27667.39404674738</v>
+        <v>28204.476036132175</v>
       </c>
       <c r="AF15" s="7">
-        <f t="shared" si="23"/>
-        <v>28506.640989875945</v>
+        <f t="shared" si="21"/>
+        <v>29060.098430989605</v>
       </c>
       <c r="AG15" s="7">
-        <f t="shared" si="23"/>
-        <v>29371.225843732882</v>
+        <f t="shared" si="21"/>
+        <v>29941.55525996822</v>
       </c>
       <c r="AH15" s="7">
-        <f t="shared" si="23"/>
-        <v>30261.911955688745</v>
+        <f t="shared" si="21"/>
+        <v>30849.624871337179</v>
       </c>
       <c r="AI15" s="7">
-        <f t="shared" si="23"/>
-        <v>31179.485637736165</v>
+        <f t="shared" si="21"/>
+        <v>31785.109030118601</v>
       </c>
       <c r="AJ15" s="7">
-        <f t="shared" si="23"/>
-        <v>32124.756856712538</v>
+        <f t="shared" si="21"/>
+        <v>32748.833621916299</v>
       </c>
     </row>
     <row r="16" spans="1:36" x14ac:dyDescent="0.3">
@@ -2555,12 +2546,11 @@
         <v>971</v>
       </c>
       <c r="Q16" s="1">
-        <f>Q15*0.18</f>
-        <v>816.18829199999993</v>
+        <v>1072</v>
       </c>
       <c r="R16" s="1">
-        <f>R15*0.18</f>
-        <v>784.60433999999987</v>
+        <f>R15*0.2</f>
+        <v>904.70888000000014</v>
       </c>
       <c r="T16" s="1">
         <v>1613</v>
@@ -2585,47 +2575,47 @@
       </c>
       <c r="Z16" s="1">
         <f>SUM(O16:R16)</f>
-        <v>3322.7926319999997</v>
+        <v>3698.7088800000001</v>
       </c>
       <c r="AA16" s="1">
         <f>AA15*0.18</f>
-        <v>3830.7309551999997</v>
+        <v>3904.7602895999994</v>
       </c>
       <c r="AB16" s="1">
-        <f t="shared" ref="AB16:AJ16" si="24">AB15*0.18</f>
-        <v>4252.8008812608005</v>
+        <f t="shared" ref="AB16:AJ16" si="22">AB15*0.18</f>
+        <v>4335.1728733583996</v>
       </c>
       <c r="AC16" s="1">
-        <f t="shared" si="24"/>
-        <v>4555.2599944738577</v>
+        <f t="shared" si="22"/>
+        <v>4643.594485059888</v>
       </c>
       <c r="AD16" s="1">
-        <f t="shared" si="24"/>
-        <v>4786.2365902835345</v>
+        <f t="shared" si="22"/>
+        <v>4879.1106167776352</v>
       </c>
       <c r="AE16" s="1">
-        <f t="shared" si="24"/>
-        <v>4980.1309284145282</v>
+        <f t="shared" si="22"/>
+        <v>5076.8056865037915</v>
       </c>
       <c r="AF16" s="1">
-        <f t="shared" si="24"/>
-        <v>5131.1953781776701</v>
+        <f t="shared" si="22"/>
+        <v>5230.8177175781284</v>
       </c>
       <c r="AG16" s="1">
-        <f t="shared" si="24"/>
-        <v>5286.8206518719189</v>
+        <f t="shared" si="22"/>
+        <v>5389.4799467942794</v>
       </c>
       <c r="AH16" s="1">
-        <f t="shared" si="24"/>
-        <v>5447.1441520239741</v>
+        <f t="shared" si="22"/>
+        <v>5552.9324768406923</v>
       </c>
       <c r="AI16" s="1">
-        <f t="shared" si="24"/>
-        <v>5612.307414792509</v>
+        <f t="shared" si="22"/>
+        <v>5721.3196254213481</v>
       </c>
       <c r="AJ16" s="1">
-        <f t="shared" si="24"/>
-        <v>5782.4562342082563</v>
+        <f t="shared" si="22"/>
+        <v>5894.790051944934</v>
       </c>
     </row>
     <row r="17" spans="1:146" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -2634,576 +2624,576 @@
         <v>22</v>
       </c>
       <c r="C17" s="7">
-        <f t="shared" ref="C17:L17" si="25">C15-C16</f>
+        <f t="shared" ref="C17:L17" si="23">C15-C16</f>
         <v>2631</v>
       </c>
       <c r="D17" s="7">
+        <f t="shared" si="23"/>
+        <v>2275</v>
+      </c>
+      <c r="E17" s="7">
+        <f t="shared" si="23"/>
+        <v>2499</v>
+      </c>
+      <c r="F17" s="7">
+        <f t="shared" si="23"/>
+        <v>2525</v>
+      </c>
+      <c r="G17" s="7">
+        <f t="shared" si="23"/>
+        <v>2361</v>
+      </c>
+      <c r="H17" s="7">
+        <f t="shared" si="23"/>
+        <v>2845</v>
+      </c>
+      <c r="I17" s="7">
+        <f t="shared" si="23"/>
+        <v>3198</v>
+      </c>
+      <c r="J17" s="7">
+        <f t="shared" si="23"/>
+        <v>2791</v>
+      </c>
+      <c r="K17" s="7">
+        <f t="shared" si="23"/>
+        <v>3011</v>
+      </c>
+      <c r="L17" s="7">
+        <f t="shared" si="23"/>
+        <v>3258</v>
+      </c>
+      <c r="M17" s="7">
+        <f t="shared" ref="M17:N17" si="24">M15-M16</f>
+        <v>3263</v>
+      </c>
+      <c r="N17" s="7">
+        <f t="shared" si="24"/>
+        <v>3342</v>
+      </c>
+      <c r="O17" s="7">
+        <f t="shared" ref="O17:R17" si="25">O15-O16</f>
+        <v>3280</v>
+      </c>
+      <c r="P17" s="7">
         <f t="shared" si="25"/>
-        <v>2275</v>
-      </c>
-      <c r="E17" s="7">
+        <v>3701</v>
+      </c>
+      <c r="Q17" s="7">
         <f t="shared" si="25"/>
-        <v>2499</v>
-      </c>
-      <c r="F17" s="7">
+        <v>3923</v>
+      </c>
+      <c r="R17" s="7">
         <f t="shared" si="25"/>
-        <v>2525</v>
-      </c>
-      <c r="G17" s="7">
-        <f t="shared" si="25"/>
-        <v>2361</v>
-      </c>
-      <c r="H17" s="7">
-        <f t="shared" si="25"/>
-        <v>2845</v>
-      </c>
-      <c r="I17" s="7">
-        <f t="shared" si="25"/>
-        <v>3198</v>
-      </c>
-      <c r="J17" s="7">
-        <f t="shared" si="25"/>
-        <v>2791</v>
-      </c>
-      <c r="K17" s="7">
-        <f t="shared" si="25"/>
-        <v>3011</v>
-      </c>
-      <c r="L17" s="7">
-        <f t="shared" si="25"/>
-        <v>3258</v>
-      </c>
-      <c r="M17" s="7">
-        <f t="shared" ref="M17:N17" si="26">M15-M16</f>
-        <v>3263</v>
-      </c>
-      <c r="N17" s="7">
+        <v>3618.8355200000005</v>
+      </c>
+      <c r="T17" s="7">
+        <f t="shared" ref="T17:Z17" si="26">T15-T16</f>
+        <v>8118</v>
+      </c>
+      <c r="U17" s="7">
         <f t="shared" si="26"/>
-        <v>3342</v>
-      </c>
-      <c r="O17" s="7">
-        <f t="shared" ref="O17:R17" si="27">O15-O16</f>
-        <v>3280</v>
-      </c>
-      <c r="P17" s="7">
+        <v>6411</v>
+      </c>
+      <c r="V17" s="7">
+        <f t="shared" si="26"/>
+        <v>8687</v>
+      </c>
+      <c r="W17" s="7">
+        <f t="shared" si="26"/>
+        <v>9930</v>
+      </c>
+      <c r="X17" s="7">
+        <f t="shared" si="26"/>
+        <v>11195</v>
+      </c>
+      <c r="Y17" s="7">
+        <f t="shared" si="26"/>
+        <v>12874</v>
+      </c>
+      <c r="Z17" s="7">
+        <f t="shared" si="26"/>
+        <v>14522.835519999999</v>
+      </c>
+      <c r="AA17" s="7">
+        <f t="shared" ref="AA17:AJ17" si="27">AA15-AA16</f>
+        <v>17788.352430399998</v>
+      </c>
+      <c r="AB17" s="7">
         <f t="shared" si="27"/>
-        <v>3701</v>
-      </c>
-      <c r="Q17" s="7">
+        <v>19749.1208675216</v>
+      </c>
+      <c r="AC17" s="7">
         <f t="shared" si="27"/>
-        <v>3718.191108</v>
-      </c>
-      <c r="R17" s="7">
+        <v>21154.152654161713</v>
+      </c>
+      <c r="AD17" s="7">
         <f t="shared" si="27"/>
-        <v>3574.3086599999997</v>
-      </c>
-      <c r="T17" s="7">
-        <f t="shared" ref="T17:Z17" si="28">T15-T16</f>
-        <v>8118</v>
-      </c>
-      <c r="U17" s="7">
-        <f t="shared" si="28"/>
-        <v>6411</v>
-      </c>
-      <c r="V17" s="7">
-        <f t="shared" si="28"/>
-        <v>8687</v>
-      </c>
-      <c r="W17" s="7">
-        <f t="shared" si="28"/>
-        <v>9930</v>
-      </c>
-      <c r="X17" s="7">
-        <f t="shared" si="28"/>
-        <v>11195</v>
-      </c>
-      <c r="Y17" s="7">
-        <f t="shared" si="28"/>
-        <v>12874</v>
-      </c>
-      <c r="Z17" s="7">
-        <f t="shared" si="28"/>
-        <v>14273.499767999998</v>
-      </c>
-      <c r="AA17" s="7">
-        <f t="shared" ref="AA17:AJ17" si="29">AA15-AA16</f>
-        <v>17451.107684799998</v>
-      </c>
-      <c r="AB17" s="7">
-        <f t="shared" si="29"/>
-        <v>19373.870681299202</v>
-      </c>
-      <c r="AC17" s="7">
-        <f t="shared" si="29"/>
-        <v>20751.739974825352</v>
-      </c>
-      <c r="AD17" s="7">
-        <f t="shared" si="29"/>
-        <v>21803.966689069435</v>
+        <v>22227.059476431452</v>
       </c>
       <c r="AE17" s="7">
-        <f t="shared" si="29"/>
-        <v>22687.263118332852</v>
+        <f t="shared" si="27"/>
+        <v>23127.670349628384</v>
       </c>
       <c r="AF17" s="7">
-        <f t="shared" si="29"/>
-        <v>23375.445611698276</v>
+        <f t="shared" si="27"/>
+        <v>23829.280713411477</v>
       </c>
       <c r="AG17" s="7">
-        <f t="shared" si="29"/>
-        <v>24084.405191860962</v>
+        <f t="shared" si="27"/>
+        <v>24552.07531317394</v>
       </c>
       <c r="AH17" s="7">
-        <f t="shared" si="29"/>
-        <v>24814.76780366477</v>
+        <f t="shared" si="27"/>
+        <v>25296.692394496487</v>
       </c>
       <c r="AI17" s="7">
-        <f t="shared" si="29"/>
-        <v>25567.178222943658</v>
+        <f t="shared" si="27"/>
+        <v>26063.789404697254</v>
       </c>
       <c r="AJ17" s="7">
-        <f t="shared" si="29"/>
-        <v>26342.300622504281</v>
+        <f t="shared" si="27"/>
+        <v>26854.043569971363</v>
       </c>
       <c r="AK17" s="6">
         <f>AJ17+(AJ17*$AM$23)</f>
-        <v>26078.877616279238</v>
+        <v>26585.50313427165</v>
       </c>
       <c r="AL17" s="6">
-        <f t="shared" ref="AL17:CW17" si="30">AK17+(AK17*$AM$23)</f>
-        <v>25818.088840116445</v>
+        <f t="shared" ref="AL17:CW17" si="28">AK17+(AK17*$AM$23)</f>
+        <v>26319.648102928935</v>
       </c>
       <c r="AM17" s="6">
-        <f t="shared" si="30"/>
-        <v>25559.907951715279</v>
+        <f t="shared" si="28"/>
+        <v>26056.451621899647</v>
       </c>
       <c r="AN17" s="6">
-        <f t="shared" si="30"/>
-        <v>25304.308872198126</v>
+        <f t="shared" si="28"/>
+        <v>25795.887105680649</v>
       </c>
       <c r="AO17" s="6">
-        <f t="shared" si="30"/>
-        <v>25051.265783476145</v>
+        <f t="shared" si="28"/>
+        <v>25537.928234623843</v>
       </c>
       <c r="AP17" s="6">
-        <f t="shared" si="30"/>
-        <v>24800.753125641382</v>
+        <f t="shared" si="28"/>
+        <v>25282.548952277604</v>
       </c>
       <c r="AQ17" s="6">
-        <f t="shared" si="30"/>
-        <v>24552.745594384967</v>
+        <f t="shared" si="28"/>
+        <v>25029.723462754828</v>
       </c>
       <c r="AR17" s="6">
-        <f t="shared" si="30"/>
-        <v>24307.218138441116</v>
+        <f t="shared" si="28"/>
+        <v>24779.426228127279</v>
       </c>
       <c r="AS17" s="6">
-        <f t="shared" si="30"/>
-        <v>24064.145957056706</v>
+        <f t="shared" si="28"/>
+        <v>24531.631965846005</v>
       </c>
       <c r="AT17" s="6">
-        <f t="shared" si="30"/>
-        <v>23823.504497486138</v>
+        <f t="shared" si="28"/>
+        <v>24286.315646187544</v>
       </c>
       <c r="AU17" s="6">
-        <f t="shared" si="30"/>
-        <v>23585.269452511275</v>
+        <f t="shared" si="28"/>
+        <v>24043.452489725667</v>
       </c>
       <c r="AV17" s="6">
-        <f t="shared" si="30"/>
-        <v>23349.416757986161</v>
+        <f t="shared" si="28"/>
+        <v>23803.01796482841</v>
       </c>
       <c r="AW17" s="6">
-        <f t="shared" si="30"/>
-        <v>23115.922590406299</v>
+        <f t="shared" si="28"/>
+        <v>23564.987785180125</v>
       </c>
       <c r="AX17" s="6">
-        <f t="shared" si="30"/>
-        <v>22884.763364502236</v>
+        <f t="shared" si="28"/>
+        <v>23329.337907328325</v>
       </c>
       <c r="AY17" s="6">
-        <f t="shared" si="30"/>
-        <v>22655.915730857214</v>
+        <f t="shared" si="28"/>
+        <v>23096.044528255043</v>
       </c>
       <c r="AZ17" s="6">
-        <f t="shared" si="30"/>
-        <v>22429.356573548641</v>
+        <f t="shared" si="28"/>
+        <v>22865.084082972491</v>
       </c>
       <c r="BA17" s="6">
-        <f t="shared" si="30"/>
-        <v>22205.063007813154</v>
+        <f t="shared" si="28"/>
+        <v>22636.433242142768</v>
       </c>
       <c r="BB17" s="6">
-        <f t="shared" si="30"/>
-        <v>21983.012377735024</v>
+        <f t="shared" si="28"/>
+        <v>22410.06890972134</v>
       </c>
       <c r="BC17" s="6">
-        <f t="shared" si="30"/>
-        <v>21763.182253957675</v>
+        <f t="shared" si="28"/>
+        <v>22185.968220624127</v>
       </c>
       <c r="BD17" s="6">
-        <f t="shared" si="30"/>
-        <v>21545.550431418098</v>
+        <f t="shared" si="28"/>
+        <v>21964.108538417884</v>
       </c>
       <c r="BE17" s="6">
-        <f t="shared" si="30"/>
-        <v>21330.094927103917</v>
+        <f t="shared" si="28"/>
+        <v>21744.467453033707</v>
       </c>
       <c r="BF17" s="6">
-        <f t="shared" si="30"/>
-        <v>21116.793977832876</v>
+        <f t="shared" si="28"/>
+        <v>21527.022778503371</v>
       </c>
       <c r="BG17" s="6">
-        <f t="shared" si="30"/>
-        <v>20905.626038054546</v>
+        <f t="shared" si="28"/>
+        <v>21311.752550718338</v>
       </c>
       <c r="BH17" s="6">
-        <f t="shared" si="30"/>
-        <v>20696.569777674002</v>
+        <f t="shared" si="28"/>
+        <v>21098.635025211155</v>
       </c>
       <c r="BI17" s="6">
-        <f t="shared" si="30"/>
-        <v>20489.604079897261</v>
+        <f t="shared" si="28"/>
+        <v>20887.648674959044</v>
       </c>
       <c r="BJ17" s="6">
-        <f t="shared" si="30"/>
-        <v>20284.708039098288</v>
+        <f t="shared" si="28"/>
+        <v>20678.772188209452</v>
       </c>
       <c r="BK17" s="6">
-        <f t="shared" si="30"/>
-        <v>20081.860958707304</v>
+        <f t="shared" si="28"/>
+        <v>20471.984466327358</v>
       </c>
       <c r="BL17" s="6">
-        <f t="shared" si="30"/>
-        <v>19881.042349120231</v>
+        <f t="shared" si="28"/>
+        <v>20267.264621664086</v>
       </c>
       <c r="BM17" s="6">
-        <f t="shared" si="30"/>
-        <v>19682.231925629028</v>
+        <f t="shared" si="28"/>
+        <v>20064.591975447445</v>
       </c>
       <c r="BN17" s="6">
-        <f t="shared" si="30"/>
-        <v>19485.409606372737</v>
+        <f t="shared" si="28"/>
+        <v>19863.94605569297</v>
       </c>
       <c r="BO17" s="6">
-        <f t="shared" si="30"/>
-        <v>19290.555510309012</v>
+        <f t="shared" si="28"/>
+        <v>19665.30659513604</v>
       </c>
       <c r="BP17" s="6">
-        <f t="shared" si="30"/>
-        <v>19097.649955205921</v>
+        <f t="shared" si="28"/>
+        <v>19468.653529184681</v>
       </c>
       <c r="BQ17" s="6">
-        <f t="shared" si="30"/>
-        <v>18906.673455653861</v>
+        <f t="shared" si="28"/>
+        <v>19273.966993892835</v>
       </c>
       <c r="BR17" s="6">
-        <f t="shared" si="30"/>
-        <v>18717.606721097323</v>
+        <f t="shared" si="28"/>
+        <v>19081.227323953906</v>
       </c>
       <c r="BS17" s="6">
-        <f t="shared" si="30"/>
-        <v>18530.430653886349</v>
+        <f t="shared" si="28"/>
+        <v>18890.415050714368</v>
       </c>
       <c r="BT17" s="6">
-        <f t="shared" si="30"/>
-        <v>18345.126347347486</v>
+        <f t="shared" si="28"/>
+        <v>18701.510900207224</v>
       </c>
       <c r="BU17" s="6">
-        <f t="shared" si="30"/>
-        <v>18161.675083874012</v>
+        <f t="shared" si="28"/>
+        <v>18514.49579120515</v>
       </c>
       <c r="BV17" s="6">
-        <f t="shared" si="30"/>
-        <v>17980.058333035271</v>
+        <f t="shared" si="28"/>
+        <v>18329.350833293098</v>
       </c>
       <c r="BW17" s="6">
-        <f t="shared" si="30"/>
-        <v>17800.257749704917</v>
+        <f t="shared" si="28"/>
+        <v>18146.057324960166</v>
       </c>
       <c r="BX17" s="6">
-        <f t="shared" si="30"/>
-        <v>17622.255172207868</v>
+        <f t="shared" si="28"/>
+        <v>17964.596751710564</v>
       </c>
       <c r="BY17" s="6">
-        <f t="shared" si="30"/>
-        <v>17446.032620485788</v>
+        <f t="shared" si="28"/>
+        <v>17784.950784193457</v>
       </c>
       <c r="BZ17" s="6">
-        <f t="shared" si="30"/>
-        <v>17271.57229428093</v>
+        <f t="shared" si="28"/>
+        <v>17607.101276351525</v>
       </c>
       <c r="CA17" s="6">
-        <f t="shared" si="30"/>
-        <v>17098.856571338121</v>
+        <f t="shared" si="28"/>
+        <v>17431.030263588011</v>
       </c>
       <c r="CB17" s="6">
-        <f t="shared" si="30"/>
-        <v>16927.868005624739</v>
+        <f t="shared" si="28"/>
+        <v>17256.71996095213</v>
       </c>
       <c r="CC17" s="6">
-        <f t="shared" si="30"/>
-        <v>16758.589325568493</v>
+        <f t="shared" si="28"/>
+        <v>17084.152761342608</v>
       </c>
       <c r="CD17" s="6">
-        <f t="shared" si="30"/>
-        <v>16591.003432312809</v>
+        <f t="shared" si="28"/>
+        <v>16913.311233729182</v>
       </c>
       <c r="CE17" s="6">
-        <f t="shared" si="30"/>
-        <v>16425.09339798968</v>
+        <f t="shared" si="28"/>
+        <v>16744.178121391891</v>
       </c>
       <c r="CF17" s="6">
-        <f t="shared" si="30"/>
-        <v>16260.842464009784</v>
+        <f t="shared" si="28"/>
+        <v>16576.736340177973</v>
       </c>
       <c r="CG17" s="6">
-        <f t="shared" si="30"/>
-        <v>16098.234039369687</v>
+        <f t="shared" si="28"/>
+        <v>16410.968976776192</v>
       </c>
       <c r="CH17" s="6">
-        <f t="shared" si="30"/>
-        <v>15937.25169897599</v>
+        <f t="shared" si="28"/>
+        <v>16246.85928700843</v>
       </c>
       <c r="CI17" s="6">
-        <f t="shared" si="30"/>
-        <v>15777.879181986229</v>
+        <f t="shared" si="28"/>
+        <v>16084.390694138347</v>
       </c>
       <c r="CJ17" s="6">
-        <f t="shared" si="30"/>
-        <v>15620.100390166366</v>
+        <f t="shared" si="28"/>
+        <v>15923.546787196963</v>
       </c>
       <c r="CK17" s="6">
-        <f t="shared" si="30"/>
-        <v>15463.899386264702</v>
+        <f t="shared" si="28"/>
+        <v>15764.311319324994</v>
       </c>
       <c r="CL17" s="6">
-        <f t="shared" si="30"/>
-        <v>15309.260392402055</v>
+        <f t="shared" si="28"/>
+        <v>15606.668206131744</v>
       </c>
       <c r="CM17" s="6">
-        <f t="shared" si="30"/>
-        <v>15156.167788478035</v>
+        <f t="shared" si="28"/>
+        <v>15450.601524070427</v>
       </c>
       <c r="CN17" s="6">
-        <f t="shared" si="30"/>
-        <v>15004.606110593255</v>
+        <f t="shared" si="28"/>
+        <v>15296.095508829723</v>
       </c>
       <c r="CO17" s="6">
-        <f t="shared" si="30"/>
-        <v>14854.560049487322</v>
+        <f t="shared" si="28"/>
+        <v>15143.134553741425</v>
       </c>
       <c r="CP17" s="6">
-        <f t="shared" si="30"/>
-        <v>14706.014448992448</v>
+        <f t="shared" si="28"/>
+        <v>14991.703208204011</v>
       </c>
       <c r="CQ17" s="6">
-        <f t="shared" si="30"/>
-        <v>14558.954304502524</v>
+        <f t="shared" si="28"/>
+        <v>14841.786176121972</v>
       </c>
       <c r="CR17" s="6">
-        <f t="shared" si="30"/>
-        <v>14413.364761457498</v>
+        <f t="shared" si="28"/>
+        <v>14693.368314360752</v>
       </c>
       <c r="CS17" s="6">
-        <f t="shared" si="30"/>
-        <v>14269.231113842923</v>
+        <f t="shared" si="28"/>
+        <v>14546.434631217146</v>
       </c>
       <c r="CT17" s="6">
-        <f t="shared" si="30"/>
-        <v>14126.538802704494</v>
+        <f t="shared" si="28"/>
+        <v>14400.970284904974</v>
       </c>
       <c r="CU17" s="6">
-        <f t="shared" si="30"/>
-        <v>13985.273414677449</v>
+        <f t="shared" si="28"/>
+        <v>14256.960582055925</v>
       </c>
       <c r="CV17" s="6">
-        <f t="shared" si="30"/>
-        <v>13845.420680530675</v>
+        <f t="shared" si="28"/>
+        <v>14114.390976235365</v>
       </c>
       <c r="CW17" s="6">
-        <f t="shared" si="30"/>
-        <v>13706.966473725368</v>
+        <f t="shared" si="28"/>
+        <v>13973.247066473012</v>
       </c>
       <c r="CX17" s="6">
-        <f t="shared" ref="CX17:EP17" si="31">CW17+(CW17*$AM$23)</f>
-        <v>13569.896808988115</v>
+        <f t="shared" ref="CX17:EP17" si="29">CW17+(CW17*$AM$23)</f>
+        <v>13833.514595808281</v>
       </c>
       <c r="CY17" s="6">
-        <f t="shared" si="31"/>
-        <v>13434.197840898234</v>
+        <f t="shared" si="29"/>
+        <v>13695.179449850199</v>
       </c>
       <c r="CZ17" s="6">
-        <f t="shared" si="31"/>
-        <v>13299.855862489252</v>
+        <f t="shared" si="29"/>
+        <v>13558.227655351697</v>
       </c>
       <c r="DA17" s="6">
-        <f t="shared" si="31"/>
-        <v>13166.857303864359</v>
+        <f t="shared" si="29"/>
+        <v>13422.645378798179</v>
       </c>
       <c r="DB17" s="6">
-        <f t="shared" si="31"/>
-        <v>13035.188730825716</v>
+        <f t="shared" si="29"/>
+        <v>13288.418925010197</v>
       </c>
       <c r="DC17" s="6">
-        <f t="shared" si="31"/>
-        <v>12904.836843517458</v>
+        <f t="shared" si="29"/>
+        <v>13155.534735760095</v>
       </c>
       <c r="DD17" s="6">
-        <f t="shared" si="31"/>
-        <v>12775.788475082283</v>
+        <f t="shared" si="29"/>
+        <v>13023.979388402495</v>
       </c>
       <c r="DE17" s="6">
-        <f t="shared" si="31"/>
-        <v>12648.03059033146</v>
+        <f t="shared" si="29"/>
+        <v>12893.739594518469</v>
       </c>
       <c r="DF17" s="6">
-        <f t="shared" si="31"/>
-        <v>12521.550284428145</v>
+        <f t="shared" si="29"/>
+        <v>12764.802198573285</v>
       </c>
       <c r="DG17" s="6">
-        <f t="shared" si="31"/>
-        <v>12396.334781583864</v>
+        <f t="shared" si="29"/>
+        <v>12637.154176587552</v>
       </c>
       <c r="DH17" s="6">
-        <f t="shared" si="31"/>
-        <v>12272.371433768025</v>
+        <f t="shared" si="29"/>
+        <v>12510.782634821677</v>
       </c>
       <c r="DI17" s="6">
-        <f t="shared" si="31"/>
-        <v>12149.647719430344</v>
+        <f t="shared" si="29"/>
+        <v>12385.674808473461</v>
       </c>
       <c r="DJ17" s="6">
-        <f t="shared" si="31"/>
-        <v>12028.151242236041</v>
+        <f t="shared" si="29"/>
+        <v>12261.818060388727</v>
       </c>
       <c r="DK17" s="6">
-        <f t="shared" si="31"/>
-        <v>11907.869729813681</v>
+        <f t="shared" si="29"/>
+        <v>12139.199879784839</v>
       </c>
       <c r="DL17" s="6">
-        <f t="shared" si="31"/>
-        <v>11788.791032515544</v>
+        <f t="shared" si="29"/>
+        <v>12017.807880986991</v>
       </c>
       <c r="DM17" s="6">
-        <f t="shared" si="31"/>
-        <v>11670.90312219039</v>
+        <f t="shared" si="29"/>
+        <v>11897.629802177122</v>
       </c>
       <c r="DN17" s="6">
-        <f t="shared" si="31"/>
-        <v>11554.194090968485</v>
+        <f t="shared" si="29"/>
+        <v>11778.653504155351</v>
       </c>
       <c r="DO17" s="6">
-        <f t="shared" si="31"/>
-        <v>11438.652150058801</v>
+        <f t="shared" si="29"/>
+        <v>11660.866969113797</v>
       </c>
       <c r="DP17" s="6">
-        <f t="shared" si="31"/>
-        <v>11324.265628558212</v>
+        <f t="shared" si="29"/>
+        <v>11544.258299422658</v>
       </c>
       <c r="DQ17" s="6">
-        <f t="shared" si="31"/>
-        <v>11211.022972272631</v>
+        <f t="shared" si="29"/>
+        <v>11428.815716428431</v>
       </c>
       <c r="DR17" s="6">
-        <f t="shared" si="31"/>
-        <v>11098.912742549905</v>
+        <f t="shared" si="29"/>
+        <v>11314.527559264146</v>
       </c>
       <c r="DS17" s="6">
-        <f t="shared" si="31"/>
-        <v>10987.923615124406</v>
+        <f t="shared" si="29"/>
+        <v>11201.382283671504</v>
       </c>
       <c r="DT17" s="6">
-        <f t="shared" si="31"/>
-        <v>10878.044378973162</v>
+        <f t="shared" si="29"/>
+        <v>11089.368460834788</v>
       </c>
       <c r="DU17" s="6">
-        <f t="shared" si="31"/>
-        <v>10769.26393518343</v>
+        <f t="shared" si="29"/>
+        <v>10978.474776226441</v>
       </c>
       <c r="DV17" s="6">
-        <f t="shared" si="31"/>
-        <v>10661.571295831594</v>
+        <f t="shared" si="29"/>
+        <v>10868.690028464178</v>
       </c>
       <c r="DW17" s="6">
-        <f t="shared" si="31"/>
-        <v>10554.955582873279</v>
+        <f t="shared" si="29"/>
+        <v>10760.003128179536</v>
       </c>
       <c r="DX17" s="6">
-        <f t="shared" si="31"/>
-        <v>10449.406027044546</v>
+        <f t="shared" si="29"/>
+        <v>10652.40309689774</v>
       </c>
       <c r="DY17" s="6">
-        <f t="shared" si="31"/>
-        <v>10344.911966774102</v>
+        <f t="shared" si="29"/>
+        <v>10545.879065928762</v>
       </c>
       <c r="DZ17" s="6">
-        <f t="shared" si="31"/>
-        <v>10241.462847106361</v>
+        <f t="shared" si="29"/>
+        <v>10440.420275269475</v>
       </c>
       <c r="EA17" s="6">
-        <f t="shared" si="31"/>
-        <v>10139.048218635297</v>
+        <f t="shared" si="29"/>
+        <v>10336.016072516781</v>
       </c>
       <c r="EB17" s="6">
-        <f t="shared" si="31"/>
-        <v>10037.657736448944</v>
+        <f t="shared" si="29"/>
+        <v>10232.655911791613</v>
       </c>
       <c r="EC17" s="6">
-        <f t="shared" si="31"/>
-        <v>9937.281159084454</v>
+        <f t="shared" si="29"/>
+        <v>10130.329352673696</v>
       </c>
       <c r="ED17" s="6">
-        <f t="shared" si="31"/>
-        <v>9837.9083474936087</v>
+        <f t="shared" si="29"/>
+        <v>10029.02605914696</v>
       </c>
       <c r="EE17" s="6">
-        <f t="shared" si="31"/>
-        <v>9739.5292640186726</v>
+        <f t="shared" si="29"/>
+        <v>9928.73579855549</v>
       </c>
       <c r="EF17" s="6">
-        <f t="shared" si="31"/>
-        <v>9642.1339713784855</v>
+        <f t="shared" si="29"/>
+        <v>9829.448440569935</v>
       </c>
       <c r="EG17" s="6">
-        <f t="shared" si="31"/>
-        <v>9545.7126316647009</v>
+        <f t="shared" si="29"/>
+        <v>9731.1539561642348</v>
       </c>
       <c r="EH17" s="6">
-        <f t="shared" si="31"/>
-        <v>9450.2555053480537</v>
+        <f t="shared" si="29"/>
+        <v>9633.8424166025925</v>
       </c>
       <c r="EI17" s="6">
-        <f t="shared" si="31"/>
-        <v>9355.7529502945727</v>
+        <f t="shared" si="29"/>
+        <v>9537.5039924365665</v>
       </c>
       <c r="EJ17" s="6">
-        <f t="shared" si="31"/>
-        <v>9262.1954207916278</v>
+        <f t="shared" si="29"/>
+        <v>9442.1289525122011</v>
       </c>
       <c r="EK17" s="6">
-        <f t="shared" si="31"/>
-        <v>9169.5734665837117</v>
+        <f t="shared" si="29"/>
+        <v>9347.7076629870789</v>
       </c>
       <c r="EL17" s="6">
-        <f t="shared" si="31"/>
-        <v>9077.8777319178753</v>
+        <f t="shared" si="29"/>
+        <v>9254.2305863572074</v>
       </c>
       <c r="EM17" s="6">
-        <f t="shared" si="31"/>
-        <v>8987.0989545986959</v>
+        <f t="shared" si="29"/>
+        <v>9161.6882804936358</v>
       </c>
       <c r="EN17" s="6">
-        <f t="shared" si="31"/>
-        <v>8897.2279650527089</v>
+        <f t="shared" si="29"/>
+        <v>9070.0713976887</v>
       </c>
       <c r="EO17" s="6">
-        <f t="shared" si="31"/>
-        <v>8808.2556854021823</v>
+        <f t="shared" si="29"/>
+        <v>8979.3706837118134</v>
       </c>
       <c r="EP17" s="6">
-        <f t="shared" si="31"/>
-        <v>8720.1731285481601</v>
+        <f t="shared" si="29"/>
+        <v>8889.5769768746959</v>
       </c>
     </row>
     <row r="18" spans="1:146" x14ac:dyDescent="0.3">
@@ -3211,43 +3201,43 @@
         <v>1</v>
       </c>
       <c r="C18" s="1">
-        <f t="shared" ref="C18:L18" si="32">922.5+7.1</f>
+        <f t="shared" ref="C18:L18" si="30">922.5+7.1</f>
         <v>929.6</v>
       </c>
       <c r="D18" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>929.6</v>
       </c>
       <c r="E18" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>929.6</v>
       </c>
       <c r="F18" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>929.6</v>
       </c>
       <c r="G18" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>929.6</v>
       </c>
       <c r="H18" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>929.6</v>
       </c>
       <c r="I18" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>929.6</v>
       </c>
       <c r="J18" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>929.6</v>
       </c>
       <c r="K18" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>929.6</v>
       </c>
       <c r="L18" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>929.6</v>
       </c>
       <c r="M18" s="1">
@@ -3267,80 +3257,80 @@
         <v>904</v>
       </c>
       <c r="Q18" s="1">
-        <f>897.3+6.7</f>
-        <v>904</v>
+        <f>891.3+6.7</f>
+        <v>898</v>
       </c>
       <c r="R18" s="1">
-        <f>897.3+6.7</f>
-        <v>904</v>
+        <f>891.3+6.7</f>
+        <v>898</v>
       </c>
       <c r="T18" s="1">
-        <f t="shared" ref="T18:X18" si="33">922.5+7.1</f>
+        <f t="shared" ref="T18:X18" si="31">922.5+7.1</f>
         <v>929.6</v>
       </c>
       <c r="U18" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>929.6</v>
       </c>
       <c r="V18" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>929.6</v>
       </c>
       <c r="W18" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>929.6</v>
       </c>
       <c r="X18" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>929.6</v>
       </c>
       <c r="Y18" s="1">
-        <f t="shared" ref="Y18" si="34">904.9+6.8</f>
+        <f t="shared" ref="Y18" si="32">904.9+6.8</f>
         <v>911.69999999999993</v>
       </c>
       <c r="Z18" s="1">
-        <f t="shared" ref="Z18:AJ18" si="35">897.3+6.7</f>
-        <v>904</v>
+        <f>891.3+6.7</f>
+        <v>898</v>
       </c>
       <c r="AA18" s="1">
-        <f t="shared" si="35"/>
-        <v>904</v>
+        <f>891.3+6.7</f>
+        <v>898</v>
       </c>
       <c r="AB18" s="1">
-        <f t="shared" si="35"/>
-        <v>904</v>
+        <f>891.3+6.7</f>
+        <v>898</v>
       </c>
       <c r="AC18" s="1">
-        <f t="shared" si="35"/>
-        <v>904</v>
+        <f>891.3+6.7</f>
+        <v>898</v>
       </c>
       <c r="AD18" s="1">
-        <f t="shared" si="35"/>
-        <v>904</v>
+        <f>891.3+6.7</f>
+        <v>898</v>
       </c>
       <c r="AE18" s="1">
-        <f t="shared" si="35"/>
-        <v>904</v>
+        <f>891.3+6.7</f>
+        <v>898</v>
       </c>
       <c r="AF18" s="1">
-        <f t="shared" si="35"/>
-        <v>904</v>
+        <f>891.3+6.7</f>
+        <v>898</v>
       </c>
       <c r="AG18" s="1">
-        <f t="shared" si="35"/>
-        <v>904</v>
+        <f>891.3+6.7</f>
+        <v>898</v>
       </c>
       <c r="AH18" s="1">
-        <f t="shared" si="35"/>
-        <v>904</v>
+        <f>891.3+6.7</f>
+        <v>898</v>
       </c>
       <c r="AI18" s="1">
-        <f t="shared" si="35"/>
-        <v>904</v>
+        <f>891.3+6.7</f>
+        <v>898</v>
       </c>
       <c r="AJ18" s="1">
-        <f t="shared" si="35"/>
-        <v>904</v>
+        <f>891.3+6.7</f>
+        <v>898</v>
       </c>
     </row>
     <row r="19" spans="1:146" x14ac:dyDescent="0.3">
@@ -3348,136 +3338,136 @@
         <v>23</v>
       </c>
       <c r="C19" s="5">
-        <f t="shared" ref="C19:L19" si="36">C17/C18</f>
+        <f t="shared" ref="C19:L19" si="33">C17/C18</f>
         <v>2.830249569707401</v>
       </c>
       <c r="D19" s="5">
+        <f t="shared" si="33"/>
+        <v>2.447289156626506</v>
+      </c>
+      <c r="E19" s="5">
+        <f t="shared" si="33"/>
+        <v>2.6882530120481927</v>
+      </c>
+      <c r="F19" s="5">
+        <f t="shared" si="33"/>
+        <v>2.7162220309810672</v>
+      </c>
+      <c r="G19" s="5">
+        <f t="shared" si="33"/>
+        <v>2.5398020654044751</v>
+      </c>
+      <c r="H19" s="5">
+        <f t="shared" si="33"/>
+        <v>3.060456110154905</v>
+      </c>
+      <c r="I19" s="5">
+        <f t="shared" si="33"/>
+        <v>3.4401893287435454</v>
+      </c>
+      <c r="J19" s="5">
+        <f t="shared" si="33"/>
+        <v>3.0023666092943202</v>
+      </c>
+      <c r="K19" s="5">
+        <f t="shared" si="33"/>
+        <v>3.2390275387263339</v>
+      </c>
+      <c r="L19" s="5">
+        <f t="shared" si="33"/>
+        <v>3.5047332185886404</v>
+      </c>
+      <c r="M19" s="5">
+        <f t="shared" ref="M19:N19" si="34">M17/M18</f>
+        <v>3.554853469876893</v>
+      </c>
+      <c r="N19" s="5">
+        <f t="shared" si="34"/>
+        <v>3.6656794998354725</v>
+      </c>
+      <c r="O19" s="5">
+        <f t="shared" ref="O19:R19" si="35">O17/O18</f>
+        <v>3.6119370113423637</v>
+      </c>
+      <c r="P19" s="5">
+        <f t="shared" si="35"/>
+        <v>4.0940265486725664</v>
+      </c>
+      <c r="Q19" s="5">
+        <f t="shared" si="35"/>
+        <v>4.3685968819599106</v>
+      </c>
+      <c r="R19" s="5">
+        <f t="shared" si="35"/>
+        <v>4.0298836525612476</v>
+      </c>
+      <c r="T19" s="5">
+        <f t="shared" ref="T19:Z19" si="36">T17/T18</f>
+        <v>8.7327882960413081</v>
+      </c>
+      <c r="U19" s="5">
         <f t="shared" si="36"/>
-        <v>2.447289156626506</v>
-      </c>
-      <c r="E19" s="5">
+        <v>6.8965146299483644</v>
+      </c>
+      <c r="V19" s="5">
         <f t="shared" si="36"/>
-        <v>2.6882530120481927</v>
-      </c>
-      <c r="F19" s="5">
+        <v>9.3448795180722897</v>
+      </c>
+      <c r="W19" s="5">
         <f t="shared" si="36"/>
-        <v>2.7162220309810672</v>
-      </c>
-      <c r="G19" s="5">
+        <v>10.682013769363166</v>
+      </c>
+      <c r="X19" s="5">
         <f t="shared" si="36"/>
-        <v>2.5398020654044751</v>
-      </c>
-      <c r="H19" s="5">
+        <v>12.042814113597245</v>
+      </c>
+      <c r="Y19" s="5">
         <f t="shared" si="36"/>
-        <v>3.060456110154905</v>
-      </c>
-      <c r="I19" s="5">
+        <v>14.120873094219592</v>
+      </c>
+      <c r="Z19" s="5">
         <f t="shared" si="36"/>
-        <v>3.4401893287435454</v>
-      </c>
-      <c r="J19" s="5">
-        <f t="shared" si="36"/>
-        <v>3.0023666092943202</v>
-      </c>
-      <c r="K19" s="5">
-        <f t="shared" si="36"/>
-        <v>3.2390275387263339</v>
-      </c>
-      <c r="L19" s="5">
-        <f t="shared" si="36"/>
-        <v>3.5047332185886404</v>
-      </c>
-      <c r="M19" s="5">
-        <f t="shared" ref="M19:N19" si="37">M17/M18</f>
-        <v>3.554853469876893</v>
-      </c>
-      <c r="N19" s="5">
+        <v>16.17242262806236</v>
+      </c>
+      <c r="AA19" s="5">
+        <f t="shared" ref="AA19:AJ19" si="37">AA17/AA18</f>
+        <v>19.808855713140311</v>
+      </c>
+      <c r="AB19" s="5">
         <f t="shared" si="37"/>
-        <v>3.6656794998354725</v>
-      </c>
-      <c r="O19" s="5">
-        <f t="shared" ref="O19:R19" si="38">O17/O18</f>
-        <v>3.6119370113423637</v>
-      </c>
-      <c r="P19" s="5">
-        <f t="shared" si="38"/>
-        <v>4.0940265486725664</v>
-      </c>
-      <c r="Q19" s="5">
-        <f t="shared" si="38"/>
-        <v>4.1130432610619465</v>
-      </c>
-      <c r="R19" s="5">
-        <f t="shared" si="38"/>
-        <v>3.9538812610619467</v>
-      </c>
-      <c r="T19" s="5">
-        <f t="shared" ref="T19:Z19" si="39">T17/T18</f>
-        <v>8.7327882960413081</v>
-      </c>
-      <c r="U19" s="5">
-        <f t="shared" si="39"/>
-        <v>6.8965146299483644</v>
-      </c>
-      <c r="V19" s="5">
-        <f t="shared" si="39"/>
-        <v>9.3448795180722897</v>
-      </c>
-      <c r="W19" s="5">
-        <f t="shared" si="39"/>
-        <v>10.682013769363166</v>
-      </c>
-      <c r="X19" s="5">
-        <f t="shared" si="39"/>
-        <v>12.042814113597245</v>
-      </c>
-      <c r="Y19" s="5">
-        <f t="shared" si="39"/>
-        <v>14.120873094219592</v>
-      </c>
-      <c r="Z19" s="5">
-        <f t="shared" si="39"/>
-        <v>15.789269654867255</v>
-      </c>
-      <c r="AA19" s="5">
-        <f t="shared" ref="AA19:AJ19" si="40">AA17/AA18</f>
-        <v>19.30432266017699</v>
-      </c>
-      <c r="AB19" s="5">
-        <f t="shared" si="40"/>
-        <v>21.431272877543364</v>
+        <v>21.992339496126505</v>
       </c>
       <c r="AC19" s="5">
-        <f t="shared" si="40"/>
-        <v>22.955464573921848</v>
+        <f t="shared" si="37"/>
+        <v>23.556962866549792</v>
       </c>
       <c r="AD19" s="5">
-        <f t="shared" si="40"/>
-        <v>24.119432178174154</v>
+        <f t="shared" si="37"/>
+        <v>24.751736610725448</v>
       </c>
       <c r="AE19" s="5">
-        <f t="shared" si="40"/>
-        <v>25.096529998155809</v>
+        <f t="shared" si="37"/>
+        <v>25.754644041902434</v>
       </c>
       <c r="AF19" s="5">
-        <f t="shared" si="40"/>
-        <v>25.857793818250308</v>
+        <f t="shared" si="37"/>
+        <v>26.535947342329038</v>
       </c>
       <c r="AG19" s="5">
-        <f t="shared" si="40"/>
-        <v>26.642041141439119</v>
+        <f t="shared" si="37"/>
+        <v>27.340841105984342</v>
       </c>
       <c r="AH19" s="5">
-        <f t="shared" si="40"/>
-        <v>27.449964384584923</v>
+        <f t="shared" si="37"/>
+        <v>28.170036074049541</v>
       </c>
       <c r="AI19" s="5">
-        <f t="shared" si="40"/>
-        <v>28.282276795291658</v>
+        <f t="shared" si="37"/>
+        <v>29.024264370486922</v>
       </c>
       <c r="AJ19" s="5">
-        <f t="shared" si="40"/>
-        <v>29.139713077991463</v>
+        <f t="shared" si="37"/>
+        <v>29.904280144734258</v>
       </c>
     </row>
     <row r="21" spans="1:146" x14ac:dyDescent="0.3">
@@ -3493,48 +3483,48 @@
         <v>0.11244435842848843</v>
       </c>
       <c r="H21" s="8">
-        <f t="shared" ref="H21:N21" si="41">H3/D3-1</f>
+        <f t="shared" ref="H21:N21" si="38">H3/D3-1</f>
         <v>0.14044024013098055</v>
       </c>
       <c r="I21" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="38"/>
         <v>0.13498957609451012</v>
       </c>
       <c r="J21" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="38"/>
         <v>0.12566615093690903</v>
       </c>
       <c r="K21" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="38"/>
         <v>0.10438413361169108</v>
       </c>
       <c r="L21" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="38"/>
         <v>0.11038443132876052</v>
       </c>
       <c r="M21" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="38"/>
         <v>0.1279657125363538</v>
       </c>
       <c r="N21" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="38"/>
         <v>0.14370800244349424</v>
       </c>
       <c r="O21" s="8">
-        <f t="shared" ref="O21" si="42">O3/K3-1</f>
+        <f t="shared" ref="O21" si="39">O3/K3-1</f>
         <v>0.14209199747952117</v>
       </c>
       <c r="P21" s="8">
-        <f t="shared" ref="P21" si="43">P3/L3-1</f>
+        <f t="shared" ref="P21" si="40">P3/L3-1</f>
         <v>0.1683666139922424</v>
       </c>
       <c r="Q21" s="8">
-        <f t="shared" ref="Q21" si="44">Q3/M3-1</f>
-        <v>0.1399999999999999</v>
+        <f t="shared" ref="Q21" si="41">Q3/M3-1</f>
+        <v>0.16732256751255248</v>
       </c>
       <c r="R21" s="8">
-        <f t="shared" ref="R21" si="45">R3/N3-1</f>
-        <v>0.1399999999999999</v>
+        <f t="shared" ref="R21" si="42">R3/N3-1</f>
+        <v>0.15999999999999992</v>
       </c>
       <c r="T21" s="8"/>
       <c r="U21" s="8">
@@ -3542,63 +3532,63 @@
         <v>-9.3703725641177571E-2</v>
       </c>
       <c r="V21" s="8">
-        <f t="shared" ref="V21:AJ21" si="46">V3/U3-1</f>
+        <f t="shared" ref="V21:AJ21" si="43">V3/U3-1</f>
         <v>0.23416770145742105</v>
       </c>
       <c r="W21" s="8">
-        <f t="shared" si="46"/>
+        <f t="shared" si="43"/>
         <v>0.17755772082185972</v>
       </c>
       <c r="X21" s="8">
-        <f t="shared" si="46"/>
+        <f t="shared" si="43"/>
         <v>0.1286594414714215</v>
       </c>
       <c r="Y21" s="8">
-        <f t="shared" si="46"/>
+        <f t="shared" si="43"/>
         <v>0.12228065981353087</v>
       </c>
       <c r="Z21" s="8">
-        <f t="shared" si="46"/>
-        <v>0.14748180494905383</v>
+        <f t="shared" si="43"/>
+        <v>0.15994745624312134</v>
       </c>
       <c r="AA21" s="8">
-        <f t="shared" si="46"/>
-        <v>0.12000000000000011</v>
+        <f t="shared" si="43"/>
+        <v>0.12999999999999989</v>
       </c>
       <c r="AB21" s="8">
-        <f t="shared" si="46"/>
+        <f t="shared" si="43"/>
         <v>9.000000000000008E-2</v>
       </c>
       <c r="AC21" s="8">
-        <f t="shared" si="46"/>
+        <f t="shared" si="43"/>
         <v>7.0000000000000062E-2</v>
       </c>
       <c r="AD21" s="8">
-        <f t="shared" si="46"/>
+        <f t="shared" si="43"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AE21" s="8">
-        <f t="shared" si="46"/>
+        <f t="shared" si="43"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AF21" s="8">
-        <f t="shared" si="46"/>
+        <f t="shared" si="43"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AG21" s="8">
-        <f t="shared" si="46"/>
+        <f t="shared" si="43"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AH21" s="8">
-        <f t="shared" si="46"/>
+        <f t="shared" si="43"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AI21" s="8">
-        <f t="shared" si="46"/>
+        <f t="shared" si="43"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AJ21" s="8">
-        <f t="shared" si="46"/>
+        <f t="shared" si="43"/>
         <v>3.0000000000000027E-2</v>
       </c>
     </row>
@@ -3607,19 +3597,19 @@
         <v>39</v>
       </c>
       <c r="C22" s="8">
-        <f t="shared" ref="C22:F22" si="47">C5/C3</f>
+        <f t="shared" ref="C22:F22" si="44">C5/C3</f>
         <v>0.64311979872266301</v>
       </c>
       <c r="D22" s="8">
-        <f t="shared" si="47"/>
+        <f t="shared" si="44"/>
         <v>0.64580680371111521</v>
       </c>
       <c r="E22" s="8">
-        <f t="shared" si="47"/>
+        <f t="shared" si="44"/>
         <v>0.64054899235580265</v>
       </c>
       <c r="F22" s="8">
-        <f t="shared" si="47"/>
+        <f t="shared" si="44"/>
         <v>0.61870379920921437</v>
       </c>
       <c r="G22" s="8">
@@ -3627,116 +3617,116 @@
         <v>0.64457202505219202</v>
       </c>
       <c r="H22" s="8">
-        <f t="shared" ref="H22:N22" si="48">H5/H3</f>
+        <f t="shared" ref="H22:N22" si="45">H5/H3</f>
         <v>0.64906683681607913</v>
       </c>
       <c r="I22" s="8">
-        <f t="shared" si="48"/>
+        <f t="shared" si="45"/>
         <v>0.65023725700290835</v>
       </c>
       <c r="J22" s="8">
-        <f t="shared" si="48"/>
+        <f t="shared" si="45"/>
         <v>0.63362858888210138</v>
       </c>
       <c r="K22" s="8">
-        <f t="shared" si="48"/>
+        <f t="shared" si="45"/>
         <v>0.63988657844990549</v>
       </c>
       <c r="L22" s="8">
-        <f t="shared" si="48"/>
+        <f t="shared" si="45"/>
         <v>0.65263611550064649</v>
       </c>
       <c r="M22" s="8">
-        <f t="shared" si="48"/>
+        <f t="shared" si="45"/>
         <v>0.62762925770118061</v>
       </c>
       <c r="N22" s="8">
-        <f t="shared" si="48"/>
+        <f t="shared" si="45"/>
         <v>0.63346241153692084</v>
       </c>
       <c r="O22" s="8">
-        <f t="shared" ref="O22:R22" si="49">O5/O3</f>
+        <f t="shared" ref="O22:R22" si="46">O5/O3</f>
         <v>0.65200000000000002</v>
       </c>
       <c r="P22" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="46"/>
         <v>0.65990409443009956</v>
       </c>
       <c r="Q22" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="46"/>
+        <v>0.66019530341780985</v>
+      </c>
+      <c r="R22" s="8">
+        <f t="shared" si="46"/>
         <v>0.64</v>
       </c>
-      <c r="R22" s="8">
-        <f t="shared" si="49"/>
-        <v>0.63</v>
-      </c>
       <c r="T22" s="8">
-        <f t="shared" ref="T22:AJ22" si="50">T5/T3</f>
+        <f t="shared" ref="T22:AJ22" si="47">T5/T3</f>
         <v>0.65865071373571049</v>
       </c>
       <c r="U22" s="8">
-        <f t="shared" si="50"/>
+        <f t="shared" si="47"/>
         <v>0.61375073524606238</v>
       </c>
       <c r="V22" s="8">
-        <f t="shared" si="50"/>
+        <f t="shared" si="47"/>
         <v>0.62470874814657906</v>
       </c>
       <c r="W22" s="8">
-        <f t="shared" si="50"/>
+        <f t="shared" si="47"/>
         <v>0.63673157350362009</v>
       </c>
       <c r="X22" s="8">
-        <f t="shared" si="50"/>
+        <f t="shared" si="47"/>
         <v>0.64431428799107504</v>
       </c>
       <c r="Y22" s="8">
-        <f t="shared" si="50"/>
+        <f t="shared" si="47"/>
         <v>0.63812262576774237</v>
       </c>
       <c r="Z22" s="8">
-        <f t="shared" si="50"/>
-        <v>0.64505877890370134</v>
+        <f t="shared" si="47"/>
+        <v>0.65293452790503492</v>
       </c>
       <c r="AA22" s="8">
-        <f t="shared" si="50"/>
+        <f t="shared" si="47"/>
         <v>0.65</v>
       </c>
       <c r="AB22" s="8">
-        <f t="shared" si="50"/>
+        <f t="shared" si="47"/>
         <v>0.66</v>
       </c>
       <c r="AC22" s="8">
-        <f t="shared" si="50"/>
+        <f t="shared" si="47"/>
         <v>0.66</v>
       </c>
       <c r="AD22" s="8">
-        <f t="shared" si="50"/>
+        <f t="shared" si="47"/>
         <v>0.66</v>
       </c>
       <c r="AE22" s="8">
-        <f t="shared" si="50"/>
+        <f t="shared" si="47"/>
         <v>0.66</v>
       </c>
       <c r="AF22" s="8">
-        <f t="shared" si="50"/>
+        <f t="shared" si="47"/>
         <v>0.66</v>
       </c>
       <c r="AG22" s="8">
-        <f t="shared" si="50"/>
+        <f t="shared" si="47"/>
         <v>0.66</v>
       </c>
       <c r="AH22" s="8">
-        <f t="shared" si="50"/>
-        <v>0.66000000000000014</v>
+        <f t="shared" si="47"/>
+        <v>0.66</v>
       </c>
       <c r="AI22" s="8">
-        <f t="shared" si="50"/>
+        <f t="shared" si="47"/>
         <v>0.66</v>
       </c>
       <c r="AJ22" s="8">
-        <f t="shared" si="50"/>
-        <v>0.66000000000000014</v>
+        <f t="shared" si="47"/>
+        <v>0.66</v>
       </c>
     </row>
     <row r="23" spans="1:146" x14ac:dyDescent="0.3">
@@ -3744,19 +3734,19 @@
         <v>40</v>
       </c>
       <c r="C23" s="8">
-        <f t="shared" ref="C23:F23" si="51">C6/C3</f>
+        <f t="shared" ref="C23:F23" si="48">C6/C3</f>
         <v>3.5029998064640994E-2</v>
       </c>
       <c r="D23" s="8">
-        <f t="shared" si="51"/>
+        <f t="shared" si="48"/>
         <v>3.8202655994178644E-2</v>
       </c>
       <c r="E23" s="8">
-        <f t="shared" si="51"/>
+        <f t="shared" si="48"/>
         <v>3.1619179986101462E-2</v>
       </c>
       <c r="F23" s="8">
-        <f t="shared" si="51"/>
+        <f t="shared" si="48"/>
         <v>3.7132542547705004E-2</v>
       </c>
       <c r="G23" s="8">
@@ -3764,116 +3754,116 @@
         <v>2.9053583855254E-2</v>
       </c>
       <c r="H23" s="8">
-        <f t="shared" ref="H23:N23" si="52">H6/H3</f>
+        <f t="shared" ref="H23:N23" si="49">H6/H3</f>
         <v>3.2062529909076411E-2</v>
       </c>
       <c r="I23" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="49"/>
         <v>2.9542323587938159E-2</v>
       </c>
       <c r="J23" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="49"/>
         <v>4.0317654245571169E-2</v>
       </c>
       <c r="K23" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="49"/>
         <v>1.8273471959672338E-2</v>
       </c>
       <c r="L23" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="49"/>
         <v>2.6432983766700186E-2</v>
       </c>
       <c r="M23" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="49"/>
         <v>2.9854797123083185E-2</v>
       </c>
       <c r="N23" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="49"/>
         <v>3.9391106956870078E-2</v>
       </c>
       <c r="O23" s="8">
-        <f t="shared" ref="O23:R23" si="53">O6/O3</f>
+        <f t="shared" ref="O23:R23" si="50">O6/O3</f>
         <v>2.0965517241379312E-2</v>
       </c>
       <c r="P23" s="8">
-        <f t="shared" si="53"/>
+        <f t="shared" si="50"/>
         <v>2.6189597934341571E-2</v>
       </c>
       <c r="Q23" s="8">
-        <f t="shared" si="53"/>
+        <f t="shared" si="50"/>
+        <v>2.8481748430597534E-2</v>
+      </c>
+      <c r="R23" s="8">
+        <f t="shared" si="50"/>
+        <v>0.04</v>
+      </c>
+      <c r="T23" s="8">
+        <f t="shared" ref="T23:AJ23" si="51">T6/T3</f>
+        <v>5.5321921459456261E-2</v>
+      </c>
+      <c r="U23" s="8">
+        <f t="shared" si="51"/>
+        <v>4.2938370041173776E-2</v>
+      </c>
+      <c r="V23" s="8">
+        <f t="shared" si="51"/>
+        <v>4.7394619783944082E-2</v>
+      </c>
+      <c r="W23" s="8">
+        <f t="shared" si="51"/>
+        <v>3.5481404865764267E-2</v>
+      </c>
+      <c r="X23" s="8">
+        <f t="shared" si="51"/>
+        <v>3.2871145111164235E-2</v>
+      </c>
+      <c r="Y23" s="8">
+        <f t="shared" si="51"/>
+        <v>2.893456882167075E-2</v>
+      </c>
+      <c r="Z23" s="8">
+        <f t="shared" si="51"/>
+        <v>2.9305906176007524E-2</v>
+      </c>
+      <c r="AA23" s="8">
+        <f t="shared" si="51"/>
         <v>0.03</v>
       </c>
-      <c r="R23" s="8">
-        <f t="shared" si="53"/>
-        <v>0.04</v>
-      </c>
-      <c r="T23" s="8">
-        <f t="shared" ref="T23:AJ23" si="54">T6/T3</f>
-        <v>5.5321921459456261E-2</v>
-      </c>
-      <c r="U23" s="8">
-        <f t="shared" si="54"/>
-        <v>4.2938370041173776E-2</v>
-      </c>
-      <c r="V23" s="8">
-        <f t="shared" si="54"/>
-        <v>4.7394619783944082E-2</v>
-      </c>
-      <c r="W23" s="8">
-        <f t="shared" si="54"/>
-        <v>3.5481404865764267E-2</v>
-      </c>
-      <c r="X23" s="8">
-        <f t="shared" si="54"/>
-        <v>3.2871145111164235E-2</v>
-      </c>
-      <c r="Y23" s="8">
-        <f t="shared" si="54"/>
-        <v>2.893456882167075E-2</v>
-      </c>
-      <c r="Z23" s="8">
-        <f t="shared" si="54"/>
-        <v>2.9656094838297682E-2</v>
-      </c>
-      <c r="AA23" s="8">
-        <f t="shared" si="54"/>
-        <v>3.0000000000000002E-2</v>
-      </c>
       <c r="AB23" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="51"/>
         <v>0.03</v>
       </c>
       <c r="AC23" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="51"/>
         <v>0.03</v>
       </c>
       <c r="AD23" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="51"/>
+        <v>2.9999999999999995E-2</v>
+      </c>
+      <c r="AE23" s="8">
+        <f t="shared" si="51"/>
+        <v>2.9999999999999995E-2</v>
+      </c>
+      <c r="AF23" s="8">
+        <f t="shared" si="51"/>
         <v>0.03</v>
       </c>
-      <c r="AE23" s="8">
-        <f t="shared" si="54"/>
-        <v>2.9999999999999995E-2</v>
-      </c>
-      <c r="AF23" s="8">
-        <f t="shared" si="54"/>
-        <v>2.9999999999999995E-2</v>
-      </c>
       <c r="AG23" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="51"/>
         <v>0.03</v>
       </c>
       <c r="AH23" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="51"/>
         <v>0.03</v>
       </c>
       <c r="AI23" s="8">
-        <f t="shared" si="54"/>
-        <v>3.0000000000000002E-2</v>
+        <f t="shared" si="51"/>
+        <v>0.03</v>
       </c>
       <c r="AJ23" s="8">
-        <f t="shared" si="54"/>
-        <v>3.0000000000000002E-2</v>
+        <f t="shared" si="51"/>
+        <v>0.03</v>
       </c>
       <c r="AL23" t="s">
         <v>46</v>
@@ -3895,48 +3885,48 @@
         <v>-5.2083333333333703E-3</v>
       </c>
       <c r="H24" s="8">
-        <f t="shared" ref="H24:N24" si="55">H7/D7-1</f>
+        <f t="shared" ref="H24:N24" si="52">H7/D7-1</f>
         <v>1.5873015873015817E-2</v>
       </c>
       <c r="I24" s="8">
-        <f t="shared" si="55"/>
+        <f t="shared" si="52"/>
         <v>0.14054054054054044</v>
       </c>
       <c r="J24" s="8">
-        <f t="shared" si="55"/>
+        <f t="shared" si="52"/>
         <v>0.11413043478260865</v>
       </c>
       <c r="K24" s="8">
-        <f t="shared" si="55"/>
+        <f t="shared" si="52"/>
         <v>0.13089005235602102</v>
       </c>
       <c r="L24" s="8">
-        <f t="shared" si="55"/>
+        <f t="shared" si="52"/>
         <v>0.171875</v>
       </c>
       <c r="M24" s="8">
-        <f t="shared" si="55"/>
+        <f t="shared" si="52"/>
         <v>6.6350710900473953E-2</v>
       </c>
       <c r="N24" s="8">
-        <f t="shared" si="55"/>
+        <f t="shared" si="52"/>
         <v>0.12682926829268282</v>
       </c>
       <c r="O24" s="8">
-        <f t="shared" ref="O24" si="56">O7/K7-1</f>
+        <f t="shared" ref="O24" si="53">O7/K7-1</f>
         <v>0.27314814814814814</v>
       </c>
       <c r="P24" s="8">
-        <f t="shared" ref="P24" si="57">P7/L7-1</f>
+        <f t="shared" ref="P24" si="54">P7/L7-1</f>
         <v>0.24888888888888894</v>
       </c>
       <c r="Q24" s="8">
-        <f t="shared" ref="Q24" si="58">Q7/M7-1</f>
-        <v>0.25</v>
+        <f t="shared" ref="Q24" si="55">Q7/M7-1</f>
+        <v>0.28888888888888897</v>
       </c>
       <c r="R24" s="8">
-        <f t="shared" ref="R24" si="59">R7/N7-1</f>
-        <v>0.25</v>
+        <f t="shared" ref="R24" si="56">R7/N7-1</f>
+        <v>0.27</v>
       </c>
       <c r="T24" s="8"/>
       <c r="U24" s="8">
@@ -3944,65 +3934,35 @@
         <v>0.11111111111111116</v>
       </c>
       <c r="V24" s="8">
-        <f t="shared" ref="V24:AJ24" si="60">V7/U7-1</f>
+        <f t="shared" ref="V24:AJ24" si="57">V7/U7-1</f>
         <v>0.25172413793103443</v>
       </c>
       <c r="W24" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="57"/>
         <v>3.3057851239669311E-2</v>
       </c>
       <c r="X24" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="57"/>
         <v>6.5333333333333243E-2</v>
       </c>
       <c r="Y24" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="57"/>
         <v>0.12265331664580725</v>
       </c>
       <c r="Z24" s="8">
-        <f t="shared" si="60"/>
-        <v>0.25529542920847259</v>
-      </c>
-      <c r="AA24" s="8">
-        <f t="shared" si="60"/>
-        <v>-1</v>
-      </c>
-      <c r="AB24" s="8" t="e">
-        <f t="shared" si="60"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC24" s="8" t="e">
-        <f t="shared" si="60"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD24" s="8" t="e">
-        <f t="shared" si="60"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE24" s="8" t="e">
-        <f t="shared" si="60"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AF24" s="8" t="e">
-        <f t="shared" si="60"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AG24" s="8" t="e">
-        <f t="shared" si="60"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH24" s="8" t="e">
-        <f t="shared" si="60"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AI24" s="8" t="e">
-        <f t="shared" si="60"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AJ24" s="8" t="e">
-        <f t="shared" si="60"/>
-        <v>#DIV/0!</v>
-      </c>
+        <f t="shared" si="57"/>
+        <v>0.27020066889632099</v>
+      </c>
+      <c r="AA24" s="8"/>
+      <c r="AB24" s="8"/>
+      <c r="AC24" s="8"/>
+      <c r="AD24" s="8"/>
+      <c r="AE24" s="8"/>
+      <c r="AF24" s="8"/>
+      <c r="AG24" s="8"/>
+      <c r="AH24" s="8"/>
+      <c r="AI24" s="8"/>
+      <c r="AJ24" s="8"/>
       <c r="AL24" t="s">
         <v>47</v>
       </c>
@@ -4015,19 +3975,19 @@
         <v>42</v>
       </c>
       <c r="C25" s="8">
-        <f t="shared" ref="C25:F25" si="61">C8/C3</f>
+        <f t="shared" ref="C25:F25" si="58">C8/C3</f>
         <v>0</v>
       </c>
       <c r="D25" s="8">
-        <f t="shared" si="61"/>
+        <f t="shared" si="58"/>
         <v>2.4195015462979808E-2</v>
       </c>
       <c r="E25" s="8">
-        <f t="shared" si="61"/>
+        <f t="shared" si="58"/>
         <v>3.6136205698401667E-2</v>
       </c>
       <c r="F25" s="8">
-        <f t="shared" si="61"/>
+        <f t="shared" si="58"/>
         <v>2.5786487880350697E-3</v>
       </c>
       <c r="G25" s="8">
@@ -4035,115 +3995,115 @@
         <v>3.6708420320111346E-2</v>
       </c>
       <c r="H25" s="8">
-        <f t="shared" ref="H25:N25" si="62">H8/H3</f>
+        <f t="shared" ref="H25:N25" si="59">H8/H3</f>
         <v>3.1903014834901897E-3</v>
       </c>
       <c r="I25" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="J25" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="59"/>
         <v>4.7037263286499695E-2</v>
       </c>
       <c r="K25" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="59"/>
         <v>1.9848771266540641E-2</v>
       </c>
       <c r="L25" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="59"/>
         <v>1.4078437006177273E-2</v>
       </c>
       <c r="M25" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="59"/>
         <v>2.388383769846655E-2</v>
       </c>
       <c r="N25" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="59"/>
         <v>3.7388169314995327E-2</v>
       </c>
       <c r="O25" s="8">
-        <f t="shared" ref="O25:R25" si="63">O8/O3</f>
+        <f t="shared" ref="O25:R25" si="60">O8/O3</f>
         <v>2.0827586206896551E-2</v>
       </c>
       <c r="P25" s="8">
-        <f t="shared" si="63"/>
+        <f t="shared" si="60"/>
         <v>1.1803762449280709E-2</v>
       </c>
       <c r="Q25" s="8">
-        <f t="shared" si="63"/>
+        <f t="shared" si="60"/>
+        <v>9.6489188560799806E-3</v>
+      </c>
+      <c r="R25" s="8">
+        <f t="shared" si="60"/>
+        <v>0.04</v>
+      </c>
+      <c r="T25" s="8">
+        <f t="shared" ref="T25:AJ25" si="61">T8/T3</f>
+        <v>0</v>
+      </c>
+      <c r="U25" s="8">
+        <f t="shared" si="61"/>
+        <v>4.7709300045748644E-3</v>
+      </c>
+      <c r="V25" s="8">
+        <f t="shared" si="61"/>
+        <v>4.977758949375132E-3</v>
+      </c>
+      <c r="W25" s="8">
+        <f t="shared" si="61"/>
+        <v>1.6009353779736474E-2</v>
+      </c>
+      <c r="X25" s="8">
+        <f t="shared" si="61"/>
+        <v>2.1475814805960634E-2</v>
+      </c>
+      <c r="Y25" s="8">
+        <f t="shared" si="61"/>
+        <v>2.4141726133418539E-2</v>
+      </c>
+      <c r="Z25" s="8">
+        <f t="shared" si="61"/>
+        <v>2.073593974579031E-2</v>
+      </c>
+      <c r="AA25" s="8">
+        <f t="shared" si="61"/>
         <v>0.02</v>
       </c>
-      <c r="R25" s="8">
-        <f t="shared" si="63"/>
-        <v>0.04</v>
-      </c>
-      <c r="T25" s="8">
-        <f t="shared" ref="T25:AJ25" si="64">T8/T3</f>
-        <v>0</v>
-      </c>
-      <c r="U25" s="8">
-        <f t="shared" si="64"/>
-        <v>4.7709300045748644E-3</v>
-      </c>
-      <c r="V25" s="8">
-        <f t="shared" si="64"/>
-        <v>4.977758949375132E-3</v>
-      </c>
-      <c r="W25" s="8">
-        <f t="shared" si="64"/>
-        <v>1.6009353779736474E-2</v>
-      </c>
-      <c r="X25" s="8">
-        <f t="shared" si="64"/>
-        <v>2.1475814805960634E-2</v>
-      </c>
-      <c r="Y25" s="8">
-        <f t="shared" si="64"/>
-        <v>2.4141726133418539E-2</v>
-      </c>
-      <c r="Z25" s="8">
-        <f t="shared" si="64"/>
-        <v>2.340610721410644E-2</v>
-      </c>
-      <c r="AA25" s="8">
-        <f t="shared" si="64"/>
+      <c r="AB25" s="8">
+        <f t="shared" si="61"/>
         <v>0.02</v>
       </c>
-      <c r="AB25" s="8">
-        <f t="shared" si="64"/>
+      <c r="AC25" s="8">
+        <f t="shared" si="61"/>
         <v>0.02</v>
       </c>
-      <c r="AC25" s="8">
-        <f t="shared" si="64"/>
+      <c r="AD25" s="8">
+        <f t="shared" si="61"/>
         <v>0.02</v>
       </c>
-      <c r="AD25" s="8">
-        <f t="shared" si="64"/>
+      <c r="AE25" s="8">
+        <f t="shared" si="61"/>
         <v>0.02</v>
       </c>
-      <c r="AE25" s="8">
-        <f t="shared" si="64"/>
+      <c r="AF25" s="8">
+        <f t="shared" si="61"/>
         <v>0.02</v>
       </c>
-      <c r="AF25" s="8">
-        <f t="shared" si="64"/>
+      <c r="AG25" s="8">
+        <f t="shared" si="61"/>
         <v>0.02</v>
       </c>
-      <c r="AG25" s="8">
-        <f t="shared" si="64"/>
+      <c r="AH25" s="8">
+        <f t="shared" si="61"/>
         <v>0.02</v>
       </c>
-      <c r="AH25" s="8">
-        <f t="shared" si="64"/>
+      <c r="AI25" s="8">
+        <f t="shared" si="61"/>
         <v>0.02</v>
       </c>
-      <c r="AI25" s="8">
-        <f t="shared" si="64"/>
-        <v>0.02</v>
-      </c>
       <c r="AJ25" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="61"/>
         <v>0.02</v>
       </c>
       <c r="AL25" t="s">
@@ -4151,7 +4111,7 @@
       </c>
       <c r="AM25" s="1">
         <f>NPV(AM24,Z17:EP17)</f>
-        <v>363636.47741468163</v>
+        <v>370670.2266774532</v>
       </c>
     </row>
     <row r="26" spans="1:146" x14ac:dyDescent="0.3">
@@ -4159,19 +4119,19 @@
         <v>43</v>
       </c>
       <c r="C26" s="8">
-        <f t="shared" ref="C26:F26" si="65">C9/C3</f>
+        <f t="shared" ref="C26:F26" si="62">C9/C3</f>
         <v>0.57093090768337529</v>
       </c>
       <c r="D26" s="8">
-        <f t="shared" si="65"/>
+        <f t="shared" si="62"/>
         <v>0.54902674185919598</v>
       </c>
       <c r="E26" s="8">
-        <f t="shared" si="65"/>
+        <f t="shared" si="62"/>
         <v>0.54065323141070187</v>
       </c>
       <c r="F26" s="8">
-        <f t="shared" si="65"/>
+        <f t="shared" si="62"/>
         <v>0.54736118274024415</v>
       </c>
       <c r="G26" s="8">
@@ -4179,115 +4139,115 @@
         <v>0.54558107167710512</v>
       </c>
       <c r="H26" s="8">
-        <f t="shared" ref="H26:N26" si="66">H9/H3</f>
+        <f t="shared" ref="H26:N26" si="63">H9/H3</f>
         <v>0.58318711118200672</v>
       </c>
       <c r="I26" s="8">
-        <f t="shared" si="66"/>
+        <f t="shared" si="63"/>
         <v>0.58839736721261293</v>
       </c>
       <c r="J26" s="8">
-        <f t="shared" si="66"/>
+        <f t="shared" si="63"/>
         <v>0.51496640195479537</v>
       </c>
       <c r="K26" s="8">
-        <f t="shared" si="66"/>
+        <f t="shared" si="63"/>
         <v>0.56773787019533717</v>
       </c>
       <c r="L26" s="8">
-        <f t="shared" si="66"/>
+        <f t="shared" si="63"/>
         <v>0.57980175262174971</v>
       </c>
       <c r="M26" s="8">
-        <f t="shared" si="66"/>
+        <f t="shared" si="63"/>
         <v>0.54335730764011403</v>
       </c>
       <c r="N26" s="8">
-        <f t="shared" si="66"/>
+        <f t="shared" si="63"/>
         <v>0.52583789558018423</v>
       </c>
       <c r="O26" s="8">
-        <f t="shared" ref="O26:R26" si="67">O9/O3</f>
+        <f t="shared" ref="O26:R26" si="64">O9/O3</f>
         <v>0.57227586206896552</v>
       </c>
       <c r="P26" s="8">
-        <f t="shared" si="67"/>
+        <f t="shared" si="64"/>
         <v>0.58736013771056195</v>
       </c>
       <c r="Q26" s="8">
-        <f t="shared" si="67"/>
-        <v>0.55652048767596829</v>
+        <f t="shared" si="64"/>
+        <v>0.58835154615205765</v>
       </c>
       <c r="R26" s="8">
-        <f t="shared" si="67"/>
-        <v>0.51617846525781663</v>
+        <f t="shared" si="64"/>
+        <v>0.52622978068983939</v>
       </c>
       <c r="T26" s="8">
-        <f t="shared" ref="T26:AJ26" si="68">T9/T3</f>
+        <f t="shared" ref="T26:AJ26" si="65">T9/T3</f>
         <v>0.57241011668542319</v>
       </c>
       <c r="U26" s="8">
-        <f t="shared" si="68"/>
+        <f t="shared" si="65"/>
         <v>0.52813541598588332</v>
       </c>
       <c r="V26" s="8">
-        <f t="shared" si="68"/>
+        <f t="shared" si="65"/>
         <v>0.53389112476170308</v>
       </c>
       <c r="W26" s="8">
-        <f t="shared" si="68"/>
+        <f t="shared" si="65"/>
         <v>0.55151324369294419</v>
       </c>
       <c r="X26" s="8">
-        <f t="shared" si="68"/>
+        <f t="shared" si="65"/>
         <v>0.55813212208144081</v>
       </c>
       <c r="Y26" s="8">
-        <f t="shared" si="68"/>
+        <f t="shared" si="65"/>
         <v>0.55320055383959954</v>
       </c>
       <c r="Z26" s="8">
-        <f t="shared" si="68"/>
-        <v>0.55715867519442397</v>
+        <f t="shared" si="65"/>
+        <v>0.56801995822753504</v>
       </c>
       <c r="AA26" s="8">
-        <f t="shared" si="68"/>
+        <f t="shared" si="65"/>
         <v>0.6</v>
       </c>
       <c r="AB26" s="8">
-        <f t="shared" si="68"/>
+        <f t="shared" si="65"/>
         <v>0.61</v>
       </c>
       <c r="AC26" s="8">
-        <f t="shared" si="68"/>
+        <f t="shared" si="65"/>
+        <v>0.61</v>
+      </c>
+      <c r="AD26" s="8">
+        <f t="shared" si="65"/>
         <v>0.6100000000000001</v>
       </c>
-      <c r="AD26" s="8">
-        <f t="shared" si="68"/>
+      <c r="AE26" s="8">
+        <f t="shared" si="65"/>
         <v>0.6100000000000001</v>
       </c>
-      <c r="AE26" s="8">
-        <f t="shared" si="68"/>
+      <c r="AF26" s="8">
+        <f t="shared" si="65"/>
         <v>0.6100000000000001</v>
       </c>
-      <c r="AF26" s="8">
-        <f t="shared" si="68"/>
-        <v>0.6100000000000001</v>
-      </c>
       <c r="AG26" s="8">
-        <f t="shared" si="68"/>
-        <v>0.6100000000000001</v>
+        <f t="shared" si="65"/>
+        <v>0.61</v>
       </c>
       <c r="AH26" s="8">
-        <f t="shared" si="68"/>
-        <v>0.6100000000000001</v>
+        <f t="shared" si="65"/>
+        <v>0.61</v>
       </c>
       <c r="AI26" s="8">
-        <f t="shared" si="68"/>
-        <v>0.6100000000000001</v>
+        <f t="shared" si="65"/>
+        <v>0.61</v>
       </c>
       <c r="AJ26" s="8">
-        <f t="shared" si="68"/>
+        <f t="shared" si="65"/>
         <v>0.6100000000000001</v>
       </c>
       <c r="AL26" t="s">
@@ -4295,7 +4255,7 @@
       </c>
       <c r="AM26" s="1">
         <f>Main!D8</f>
-        <v>-9603</v>
+        <v>-8335</v>
       </c>
     </row>
     <row r="27" spans="1:146" x14ac:dyDescent="0.3">
@@ -4303,19 +4263,19 @@
         <v>44</v>
       </c>
       <c r="C27" s="8">
-        <f t="shared" ref="C27:F27" si="69">C15/C3</f>
+        <f t="shared" ref="C27:F27" si="66">C15/C3</f>
         <v>0.53667505322237274</v>
       </c>
       <c r="D27" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="66"/>
         <v>0.50900491177005636</v>
       </c>
       <c r="E27" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="66"/>
         <v>0.53370396108408613</v>
       </c>
       <c r="F27" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="66"/>
         <v>0.53102974041602202</v>
       </c>
       <c r="G27" s="8">
@@ -4323,123 +4283,123 @@
         <v>0.49634655532359079</v>
       </c>
       <c r="H27" s="8">
-        <f t="shared" ref="H27:N27" si="70">H15/H3</f>
+        <f t="shared" ref="H27:N27" si="67">H15/H3</f>
         <v>0.59084383474238311</v>
       </c>
       <c r="I27" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="67"/>
         <v>0.57569263737945808</v>
       </c>
       <c r="J27" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="67"/>
         <v>0.50717776420281002</v>
       </c>
       <c r="K27" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="67"/>
         <v>0.56049149338374293</v>
       </c>
       <c r="L27" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="67"/>
         <v>0.56586697313604373</v>
       </c>
       <c r="M27" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="67"/>
         <v>0.52463020762654367</v>
       </c>
       <c r="N27" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="67"/>
         <v>0.51956202430231002</v>
       </c>
       <c r="O27" s="8">
-        <f t="shared" ref="O27:R27" si="71">O15/O3</f>
+        <f t="shared" ref="O27:R27" si="68">O15/O3</f>
         <v>0.55600000000000005</v>
       </c>
       <c r="P27" s="8">
-        <f t="shared" si="71"/>
+        <f t="shared" si="68"/>
         <v>0.57444977253166118</v>
       </c>
       <c r="Q27" s="8">
-        <f t="shared" si="71"/>
-        <v>0.53976466134803691</v>
+        <f t="shared" si="68"/>
+        <v>0.58067891188095788</v>
       </c>
       <c r="R27" s="8">
-        <f t="shared" si="71"/>
-        <v>0.51056321200919241</v>
+        <f t="shared" si="68"/>
+        <v>0.52071134215239834</v>
       </c>
       <c r="T27" s="8">
-        <f t="shared" ref="T27:AJ27" si="72">T15/T3</f>
+        <f t="shared" ref="T27:AJ27" si="69">T15/T3</f>
         <v>0.57637860569803945</v>
       </c>
       <c r="U27" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="69"/>
         <v>0.50715639500686227</v>
       </c>
       <c r="V27" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="69"/>
         <v>0.54580597331073921</v>
       </c>
       <c r="W27" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="69"/>
         <v>0.52758915321311328</v>
       </c>
       <c r="X27" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="69"/>
         <v>0.54342975535899274</v>
       </c>
       <c r="Y27" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="69"/>
         <v>0.54155572123406825</v>
       </c>
       <c r="Z27" s="8">
-        <f t="shared" si="72"/>
-        <v>0.54442087402911776</v>
+        <f t="shared" si="69"/>
+        <v>0.5577072279096873</v>
       </c>
       <c r="AA27" s="8">
-        <f t="shared" si="72"/>
-        <v>0.58790170770249117</v>
+        <f t="shared" si="69"/>
+        <v>0.58757663646434255</v>
       </c>
       <c r="AB27" s="8">
-        <f t="shared" si="72"/>
-        <v>0.5987859781953756</v>
+        <f t="shared" si="69"/>
+        <v>0.59848058100543999</v>
       </c>
       <c r="AC27" s="8">
-        <f t="shared" si="72"/>
-        <v>0.59941273358104663</v>
+        <f t="shared" si="69"/>
+        <v>0.59912046122485851</v>
       </c>
       <c r="AD27" s="8">
-        <f t="shared" si="72"/>
-        <v>0.59981546432619703</v>
+        <f t="shared" si="69"/>
+        <v>0.59953042893322761</v>
       </c>
       <c r="AE27" s="8">
-        <f t="shared" si="72"/>
-        <v>0.60011007381529424</v>
+        <f t="shared" si="69"/>
+        <v>0.59982942705669129</v>
       </c>
       <c r="AF27" s="8">
-        <f t="shared" si="72"/>
-        <v>0.60030434014827139</v>
+        <f t="shared" si="69"/>
+        <v>0.60002533515591672</v>
       </c>
       <c r="AG27" s="8">
-        <f t="shared" si="72"/>
-        <v>0.60049622971910588</v>
+        <f t="shared" si="69"/>
+        <v>0.60021886012239023</v>
       </c>
       <c r="AH27" s="8">
-        <f t="shared" si="72"/>
-        <v>0.60068577989484506</v>
+        <f t="shared" si="69"/>
+        <v>0.60041003910630486</v>
       </c>
       <c r="AI27" s="8">
-        <f t="shared" si="72"/>
-        <v>0.60087302726348657</v>
+        <f t="shared" si="69"/>
+        <v>0.60059890848902675</v>
       </c>
       <c r="AJ27" s="8">
-        <f t="shared" si="72"/>
-        <v>0.60105800765366613</v>
+        <f t="shared" si="69"/>
+        <v>0.60078550390244778</v>
       </c>
       <c r="AL27" t="s">
         <v>50</v>
       </c>
       <c r="AM27" s="1">
         <f>AM25+AM26</f>
-        <v>354033.47741468163</v>
+        <v>362335.2266774532</v>
       </c>
     </row>
     <row r="28" spans="1:146" x14ac:dyDescent="0.3">
@@ -4447,19 +4407,19 @@
         <v>21</v>
       </c>
       <c r="C28" s="8">
-        <f t="shared" ref="C28:F28" si="73">C16/C15</f>
+        <f t="shared" ref="C28:F28" si="70">C16/C15</f>
         <v>5.120807789397764E-2</v>
       </c>
       <c r="D28" s="8">
-        <f t="shared" si="73"/>
+        <f t="shared" si="70"/>
         <v>0.18691922802001429</v>
       </c>
       <c r="E28" s="8">
-        <f t="shared" si="73"/>
+        <f t="shared" si="70"/>
         <v>0.1865234375</v>
       </c>
       <c r="F28" s="8">
-        <f t="shared" si="73"/>
+        <f t="shared" si="70"/>
         <v>0.18258336031078018</v>
       </c>
       <c r="G28" s="8">
@@ -4467,115 +4427,115 @@
         <v>0.17245005257623555</v>
       </c>
       <c r="H28" s="8">
-        <f t="shared" ref="H28:N28" si="74">H16/H15</f>
+        <f t="shared" ref="H28:N28" si="71">H16/H15</f>
         <v>0.23191144708423325</v>
       </c>
       <c r="I28" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="71"/>
         <v>0.14969423025791012</v>
       </c>
       <c r="J28" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="71"/>
         <v>0.15959048479373683</v>
       </c>
       <c r="K28" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="71"/>
         <v>0.1537380550871276</v>
       </c>
       <c r="L28" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="71"/>
         <v>0.17288651942117289</v>
       </c>
       <c r="M28" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="71"/>
         <v>0.15597516813243661</v>
       </c>
       <c r="N28" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="71"/>
         <v>0.14109483423284502</v>
       </c>
       <c r="O28" s="8">
-        <f t="shared" ref="O28:R28" si="75">O16/O15</f>
+        <f t="shared" ref="O28:R28" si="72">O16/O15</f>
         <v>0.18630612751178369</v>
       </c>
       <c r="P28" s="8">
-        <f t="shared" si="75"/>
+        <f t="shared" si="72"/>
         <v>0.20783390410958905</v>
       </c>
       <c r="Q28" s="8">
-        <f t="shared" si="75"/>
+        <f t="shared" si="72"/>
+        <v>0.21461461461461462</v>
+      </c>
+      <c r="R28" s="8">
+        <f t="shared" si="72"/>
+        <v>0.2</v>
+      </c>
+      <c r="T28" s="8">
+        <f t="shared" ref="T28:AJ28" si="73">T16/T15</f>
+        <v>0.16575891480834445</v>
+      </c>
+      <c r="U28" s="8">
+        <f t="shared" si="73"/>
+        <v>0.173840206185567</v>
+      </c>
+      <c r="V28" s="8">
+        <f t="shared" si="73"/>
+        <v>0.15717473561657128</v>
+      </c>
+      <c r="W28" s="8">
+        <f t="shared" si="73"/>
+        <v>0.15359699965905216</v>
+      </c>
+      <c r="X28" s="8">
+        <f t="shared" si="73"/>
+        <v>0.17919202287557739</v>
+      </c>
+      <c r="Y28" s="8">
+        <f t="shared" si="73"/>
+        <v>0.15602464927232201</v>
+      </c>
+      <c r="Z28" s="8">
+        <f t="shared" si="73"/>
+        <v>0.20298547690611782</v>
+      </c>
+      <c r="AA28" s="8">
+        <f t="shared" si="73"/>
         <v>0.18</v>
       </c>
-      <c r="R28" s="8">
-        <f t="shared" si="75"/>
+      <c r="AB28" s="8">
+        <f t="shared" si="73"/>
         <v>0.18</v>
       </c>
-      <c r="T28" s="8">
-        <f t="shared" ref="T28:AJ28" si="76">T16/T15</f>
-        <v>0.16575891480834445</v>
-      </c>
-      <c r="U28" s="8">
-        <f t="shared" si="76"/>
-        <v>0.173840206185567</v>
-      </c>
-      <c r="V28" s="8">
-        <f t="shared" si="76"/>
-        <v>0.15717473561657128</v>
-      </c>
-      <c r="W28" s="8">
-        <f t="shared" si="76"/>
-        <v>0.15359699965905216</v>
-      </c>
-      <c r="X28" s="8">
-        <f t="shared" si="76"/>
-        <v>0.17919202287557739</v>
-      </c>
-      <c r="Y28" s="8">
-        <f t="shared" si="76"/>
-        <v>0.15602464927232201</v>
-      </c>
-      <c r="Z28" s="8">
-        <f t="shared" si="76"/>
-        <v>0.18883481567969398</v>
-      </c>
-      <c r="AA28" s="8">
-        <f t="shared" si="76"/>
+      <c r="AC28" s="8">
+        <f t="shared" si="73"/>
         <v>0.18</v>
       </c>
-      <c r="AB28" s="8">
-        <f t="shared" si="76"/>
+      <c r="AD28" s="8">
+        <f t="shared" si="73"/>
         <v>0.18</v>
       </c>
-      <c r="AC28" s="8">
-        <f t="shared" si="76"/>
+      <c r="AE28" s="8">
+        <f t="shared" si="73"/>
         <v>0.18</v>
       </c>
-      <c r="AD28" s="8">
-        <f t="shared" si="76"/>
+      <c r="AF28" s="8">
+        <f t="shared" si="73"/>
         <v>0.18</v>
       </c>
-      <c r="AE28" s="8">
-        <f t="shared" si="76"/>
+      <c r="AG28" s="8">
+        <f t="shared" si="73"/>
         <v>0.18</v>
       </c>
-      <c r="AF28" s="8">
-        <f t="shared" si="76"/>
+      <c r="AH28" s="8">
+        <f t="shared" si="73"/>
         <v>0.18</v>
       </c>
-      <c r="AG28" s="8">
-        <f t="shared" si="76"/>
+      <c r="AI28" s="8">
+        <f t="shared" si="73"/>
         <v>0.18</v>
       </c>
-      <c r="AH28" s="8">
-        <f t="shared" si="76"/>
-        <v>0.18</v>
-      </c>
-      <c r="AI28" s="8">
-        <f t="shared" si="76"/>
-        <v>0.17999999999999997</v>
-      </c>
       <c r="AJ28" s="8">
-        <f t="shared" si="76"/>
+        <f t="shared" si="73"/>
         <v>0.18</v>
       </c>
       <c r="AL28" t="s">
@@ -4583,7 +4543,7 @@
       </c>
       <c r="AM28" s="10">
         <f>AM27/AJ18</f>
-        <v>391.62995289234692</v>
+        <v>403.49134373881202</v>
       </c>
     </row>
     <row r="29" spans="1:146" x14ac:dyDescent="0.3">
@@ -4591,19 +4551,19 @@
         <v>45</v>
       </c>
       <c r="C29" s="8">
-        <f t="shared" ref="C29:F29" si="77">C17/C3</f>
+        <f t="shared" ref="C29:F29" si="74">C17/C3</f>
         <v>0.50919295529320685</v>
       </c>
       <c r="D29" s="8">
-        <f t="shared" si="77"/>
+        <f t="shared" si="74"/>
         <v>0.41386210660360195</v>
       </c>
       <c r="E29" s="8">
-        <f t="shared" si="77"/>
+        <f t="shared" si="74"/>
         <v>0.43415566365531622</v>
       </c>
       <c r="F29" s="8">
-        <f t="shared" si="77"/>
+        <f t="shared" si="74"/>
         <v>0.43407254598590339</v>
       </c>
       <c r="G29" s="8">
@@ -4611,123 +4571,123 @@
         <v>0.41075156576200417</v>
       </c>
       <c r="H29" s="8">
-        <f t="shared" ref="H29:N29" si="78">H17/H3</f>
+        <f t="shared" ref="H29:N29" si="75">H17/H3</f>
         <v>0.45382038602647951</v>
       </c>
       <c r="I29" s="8">
-        <f t="shared" si="78"/>
+        <f t="shared" si="75"/>
         <v>0.48951477116179398</v>
       </c>
       <c r="J29" s="8">
-        <f t="shared" si="78"/>
+        <f t="shared" si="75"/>
         <v>0.42623701893708005</v>
       </c>
       <c r="K29" s="8">
-        <f t="shared" si="78"/>
+        <f t="shared" si="75"/>
         <v>0.47432262129804664</v>
       </c>
       <c r="L29" s="8">
-        <f t="shared" si="78"/>
+        <f t="shared" si="75"/>
         <v>0.46803620169515875</v>
       </c>
       <c r="M29" s="8">
-        <f t="shared" si="78"/>
+        <f t="shared" si="75"/>
         <v>0.44280092278463834</v>
       </c>
       <c r="N29" s="8">
-        <f t="shared" si="78"/>
+        <f t="shared" si="75"/>
         <v>0.44625450660969423</v>
       </c>
       <c r="O29" s="8">
-        <f t="shared" ref="O29:R29" si="79">O17/O3</f>
+        <f t="shared" ref="O29:R29" si="76">O17/O3</f>
         <v>0.45241379310344826</v>
       </c>
       <c r="P29" s="8">
-        <f t="shared" si="79"/>
+        <f t="shared" si="76"/>
         <v>0.45505963359154061</v>
       </c>
       <c r="Q29" s="8">
-        <f t="shared" si="79"/>
-        <v>0.44260702230539029</v>
+        <f t="shared" si="76"/>
+        <v>0.45605673099279237</v>
       </c>
       <c r="R29" s="8">
-        <f t="shared" si="79"/>
-        <v>0.4186618338475378</v>
+        <f t="shared" si="76"/>
+        <v>0.41656907372191865</v>
       </c>
       <c r="T29" s="8">
-        <f t="shared" ref="T29:AJ29" si="80">T17/T3</f>
+        <f t="shared" ref="T29:AJ29" si="77">T17/T3</f>
         <v>0.48083871349878576</v>
       </c>
       <c r="U29" s="8">
-        <f t="shared" si="80"/>
+        <f t="shared" si="77"/>
         <v>0.41899222273054049</v>
       </c>
       <c r="V29" s="8">
-        <f t="shared" si="80"/>
+        <f t="shared" si="77"/>
         <v>0.46001906375767848</v>
       </c>
       <c r="W29" s="8">
-        <f t="shared" si="80"/>
+        <f t="shared" si="77"/>
         <v>0.44655304222691911</v>
       </c>
       <c r="X29" s="8">
-        <f t="shared" si="80"/>
+        <f t="shared" si="77"/>
         <v>0.44605147820543467</v>
       </c>
       <c r="Y29" s="8">
-        <f t="shared" si="80"/>
+        <f t="shared" si="77"/>
         <v>0.45705967976710332</v>
       </c>
       <c r="Z29" s="8">
-        <f t="shared" si="80"/>
-        <v>0.4416152586296514</v>
+        <f t="shared" si="77"/>
+        <v>0.44450076027845042</v>
       </c>
       <c r="AA29" s="8">
-        <f t="shared" si="80"/>
-        <v>0.48207940031604274</v>
+        <f t="shared" si="77"/>
+        <v>0.4818128419007609</v>
       </c>
       <c r="AB29" s="8">
-        <f t="shared" si="80"/>
-        <v>0.49100450212020796</v>
+        <f t="shared" si="77"/>
+        <v>0.49075407642446084</v>
       </c>
       <c r="AC29" s="8">
-        <f t="shared" si="80"/>
-        <v>0.49151844153645818</v>
+        <f t="shared" si="77"/>
+        <v>0.49127877820438404</v>
       </c>
       <c r="AD29" s="8">
-        <f t="shared" si="80"/>
-        <v>0.49184868074748156</v>
+        <f t="shared" si="77"/>
+        <v>0.49161495172524666</v>
       </c>
       <c r="AE29" s="8">
-        <f t="shared" si="80"/>
-        <v>0.49209026052854132</v>
+        <f t="shared" si="77"/>
+        <v>0.49186013018648689</v>
       </c>
       <c r="AF29" s="8">
-        <f t="shared" si="80"/>
-        <v>0.49224955892158262</v>
+        <f t="shared" si="77"/>
+        <v>0.49202077482785178</v>
       </c>
       <c r="AG29" s="8">
-        <f t="shared" si="80"/>
-        <v>0.49240690836966683</v>
+        <f t="shared" si="77"/>
+        <v>0.49217946530036</v>
       </c>
       <c r="AH29" s="8">
-        <f t="shared" si="80"/>
-        <v>0.49256233951377293</v>
+        <f t="shared" si="77"/>
+        <v>0.49233623206716998</v>
       </c>
       <c r="AI29" s="8">
-        <f t="shared" si="80"/>
-        <v>0.49271588235605907</v>
+        <f t="shared" si="77"/>
+        <v>0.49249110496100196</v>
       </c>
       <c r="AJ29" s="8">
-        <f t="shared" si="80"/>
-        <v>0.4928675662760062</v>
+        <f t="shared" si="77"/>
+        <v>0.49264411320000717</v>
       </c>
       <c r="AL29" t="s">
         <v>52</v>
       </c>
       <c r="AM29" s="10">
         <f>Main!D3</f>
-        <v>575.01</v>
+        <v>549.86</v>
       </c>
     </row>
     <row r="30" spans="1:146" x14ac:dyDescent="0.3">
@@ -4736,7 +4696,7 @@
       </c>
       <c r="AM30" s="9">
         <f>AM28/AM29-1</f>
-        <v>-0.3189162746867934</v>
+        <v>-0.26619258767902376</v>
       </c>
     </row>
     <row r="31" spans="1:146" x14ac:dyDescent="0.3">
@@ -4744,7 +4704,7 @@
         <v>54</v>
       </c>
       <c r="AM31" s="4" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
